--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118218643</v>
+        <v>118218695</v>
       </c>
       <c r="B4" t="n">
-        <v>96807</v>
+        <v>91779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834110</v>
+        <v>834494</v>
       </c>
       <c r="R4" t="n">
-        <v>7347872</v>
+        <v>7347841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +970,18 @@
           <t>2024-07-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118218695</v>
+        <v>118218643</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>96807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,37 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834494</v>
+        <v>834110</v>
       </c>
       <c r="R5" t="n">
-        <v>7347841</v>
+        <v>7347872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,18 +1078,12 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118218682</v>
+        <v>118218642</v>
       </c>
       <c r="B18" t="n">
-        <v>97763</v>
+        <v>96807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834395</v>
+        <v>834549</v>
       </c>
       <c r="R18" t="n">
-        <v>7347996</v>
+        <v>7347756</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118218642</v>
+        <v>118218641</v>
       </c>
       <c r="B19" t="n">
         <v>96807</v>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>834549</v>
+        <v>834575</v>
       </c>
       <c r="R19" t="n">
-        <v>7347756</v>
+        <v>7347740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118218641</v>
+        <v>118218682</v>
       </c>
       <c r="B20" t="n">
-        <v>96807</v>
+        <v>97763</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>834575</v>
+        <v>834395</v>
       </c>
       <c r="R20" t="n">
-        <v>7347740</v>
+        <v>7347996</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118218660</v>
+        <v>118218639</v>
       </c>
       <c r="B22" t="n">
-        <v>91771</v>
+        <v>96807</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2860,41 +2860,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834137</v>
+        <v>834595</v>
       </c>
       <c r="R22" t="n">
-        <v>7348053</v>
+        <v>7347728</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,18 +2926,12 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2959,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118218690</v>
+        <v>118218660</v>
       </c>
       <c r="B23" t="n">
-        <v>79102</v>
+        <v>91771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,34 +2966,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>834643</v>
+        <v>834137</v>
       </c>
       <c r="R23" t="n">
-        <v>7347692</v>
+        <v>7348053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,12 +3031,18 @@
           <t>2024-07-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118218639</v>
+        <v>118218690</v>
       </c>
       <c r="B24" t="n">
-        <v>96807</v>
+        <v>79102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3073,25 +3073,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834595</v>
+        <v>834643</v>
       </c>
       <c r="R24" t="n">
-        <v>7347728</v>
+        <v>7347692</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -2848,10 +2848,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118218639</v>
+        <v>118218660</v>
       </c>
       <c r="B22" t="n">
-        <v>96807</v>
+        <v>91771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2860,38 +2860,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834595</v>
+        <v>834137</v>
       </c>
       <c r="R22" t="n">
-        <v>7347728</v>
+        <v>7348053</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,12 +2929,18 @@
           <t>2024-07-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2950,10 +2959,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118218660</v>
+        <v>118218690</v>
       </c>
       <c r="B23" t="n">
-        <v>91771</v>
+        <v>79102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,37 +2975,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>834137</v>
+        <v>834643</v>
       </c>
       <c r="R23" t="n">
-        <v>7348053</v>
+        <v>7347692</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,18 +3037,12 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Gick att artidentifiera efter genomskärning.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118218690</v>
+        <v>118218639</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
+        <v>96807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3073,25 +3073,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834643</v>
+        <v>834595</v>
       </c>
       <c r="R24" t="n">
-        <v>7347692</v>
+        <v>7347728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626507</v>
+        <v>119626430</v>
       </c>
       <c r="B41" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4916,21 +4916,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834277</v>
+        <v>834295</v>
       </c>
       <c r="R41" t="n">
-        <v>7347848</v>
+        <v>7348032</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626486</v>
+        <v>119626507</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,25 +5018,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834186</v>
+        <v>834277</v>
       </c>
       <c r="R42" t="n">
-        <v>7347942</v>
+        <v>7347848</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626545</v>
+        <v>119626486</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5124,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834320</v>
+        <v>834186</v>
       </c>
       <c r="R43" t="n">
-        <v>7347855</v>
+        <v>7347942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119626430</v>
+        <v>119626545</v>
       </c>
       <c r="B44" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>834295</v>
+        <v>834320</v>
       </c>
       <c r="R44" t="n">
-        <v>7348032</v>
+        <v>7347855</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119626455</v>
+        <v>119626420</v>
       </c>
       <c r="B45" t="n">
-        <v>91463</v>
+        <v>89275</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,25 +5336,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>6286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>834288</v>
+        <v>834252</v>
       </c>
       <c r="R45" t="n">
-        <v>7347877</v>
+        <v>7347884</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119626499</v>
+        <v>119626455</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>834153</v>
+        <v>834288</v>
       </c>
       <c r="R46" t="n">
-        <v>7347952</v>
+        <v>7347877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119626533</v>
+        <v>119626499</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5579,7 +5579,7 @@
         <v>834153</v>
       </c>
       <c r="R47" t="n">
-        <v>7347932</v>
+        <v>7347952</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119626551</v>
+        <v>119626533</v>
       </c>
       <c r="B48" t="n">
         <v>91834</v>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>834249</v>
+        <v>834153</v>
       </c>
       <c r="R48" t="n">
-        <v>7347880</v>
+        <v>7347932</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119626542</v>
+        <v>119626551</v>
       </c>
       <c r="B49" t="n">
         <v>91834</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>834148</v>
+        <v>834249</v>
       </c>
       <c r="R49" t="n">
         <v>7347880</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626420</v>
+        <v>119626542</v>
       </c>
       <c r="B50" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5866,25 +5866,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>834252</v>
+        <v>834148</v>
       </c>
       <c r="R50" t="n">
-        <v>7347884</v>
+        <v>7347880</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7762,10 +7762,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119626406</v>
+        <v>119626452</v>
       </c>
       <c r="B68" t="n">
-        <v>89633</v>
+        <v>91828</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7774,25 +7774,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>834121</v>
+        <v>834454</v>
       </c>
       <c r="R68" t="n">
-        <v>7348010</v>
+        <v>7347892</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7840,18 +7840,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7874,10 +7868,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119626452</v>
+        <v>119626406</v>
       </c>
       <c r="B69" t="n">
-        <v>91828</v>
+        <v>89633</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7886,25 +7880,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>149</v>
+        <v>1962</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7914,10 +7908,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>834454</v>
+        <v>834121</v>
       </c>
       <c r="R69" t="n">
-        <v>7347892</v>
+        <v>7348010</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7952,12 +7946,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8510,10 +8510,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119626538</v>
+        <v>119626509</v>
       </c>
       <c r="B75" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8526,21 +8526,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8550,10 +8550,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>834292</v>
+        <v>834244</v>
       </c>
       <c r="R75" t="n">
-        <v>7347968</v>
+        <v>7347889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8616,10 +8616,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119626543</v>
+        <v>119626467</v>
       </c>
       <c r="B76" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8632,21 +8632,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>834275</v>
+        <v>834310</v>
       </c>
       <c r="R76" t="n">
-        <v>7347856</v>
+        <v>7347899</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119626509</v>
+        <v>119626538</v>
       </c>
       <c r="B77" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8738,21 +8738,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>834244</v>
+        <v>834292</v>
       </c>
       <c r="R77" t="n">
-        <v>7347889</v>
+        <v>7347968</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8828,10 +8828,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119626467</v>
+        <v>119626543</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8844,21 +8844,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>834310</v>
+        <v>834275</v>
       </c>
       <c r="R78" t="n">
-        <v>7347899</v>
+        <v>7347856</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9464,10 +9464,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626434</v>
+        <v>119626479</v>
       </c>
       <c r="B84" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9480,21 +9480,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834189</v>
+        <v>834177</v>
       </c>
       <c r="R84" t="n">
-        <v>7347957</v>
+        <v>7347881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626479</v>
+        <v>119626434</v>
       </c>
       <c r="B85" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9586,21 +9586,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834177</v>
+        <v>834189</v>
       </c>
       <c r="R85" t="n">
-        <v>7347881</v>
+        <v>7347957</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9888,10 +9888,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119626412</v>
+        <v>119626442</v>
       </c>
       <c r="B88" t="n">
-        <v>89275</v>
+        <v>91463</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9900,25 +9900,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>834267</v>
+        <v>834160</v>
       </c>
       <c r="R88" t="n">
-        <v>7347984</v>
+        <v>7347864</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9994,10 +9994,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119626463</v>
+        <v>119626412</v>
       </c>
       <c r="B89" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10006,25 +10006,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>834272</v>
+        <v>834267</v>
       </c>
       <c r="R89" t="n">
-        <v>7347885</v>
+        <v>7347984</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119626442</v>
+        <v>119626463</v>
       </c>
       <c r="B90" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10116,21 +10116,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10140,10 +10140,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>834160</v>
+        <v>834272</v>
       </c>
       <c r="R90" t="n">
-        <v>7347864</v>
+        <v>7347885</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119626404</v>
+        <v>119626554</v>
       </c>
       <c r="B111" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,21 +12342,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12366,10 +12366,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>834430</v>
+        <v>834433</v>
       </c>
       <c r="R111" t="n">
-        <v>7347886</v>
+        <v>7347878</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12410,7 +12410,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12433,10 +12432,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119626405</v>
+        <v>119626553</v>
       </c>
       <c r="B112" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12449,21 +12448,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12473,10 +12472,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>834216</v>
+        <v>834388</v>
       </c>
       <c r="R112" t="n">
-        <v>7347860</v>
+        <v>7347909</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12539,7 +12538,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119626554</v>
+        <v>119626536</v>
       </c>
       <c r="B113" t="n">
         <v>91834</v>
@@ -12579,10 +12578,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>834433</v>
+        <v>834190</v>
       </c>
       <c r="R113" t="n">
-        <v>7347878</v>
+        <v>7347950</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12645,10 +12644,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119626553</v>
+        <v>119626501</v>
       </c>
       <c r="B114" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,21 +12660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12685,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>834388</v>
+        <v>834207</v>
       </c>
       <c r="R114" t="n">
-        <v>7347909</v>
+        <v>7347898</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,7 +12750,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119626536</v>
+        <v>119626535</v>
       </c>
       <c r="B115" t="n">
         <v>91834</v>
@@ -12791,10 +12790,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>834190</v>
+        <v>834187</v>
       </c>
       <c r="R115" t="n">
-        <v>7347950</v>
+        <v>7347944</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12857,10 +12856,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119626501</v>
+        <v>119626540</v>
       </c>
       <c r="B116" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12873,21 +12872,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12897,10 +12896,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>834207</v>
+        <v>834166</v>
       </c>
       <c r="R116" t="n">
-        <v>7347898</v>
+        <v>7347884</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12963,10 +12962,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119626535</v>
+        <v>119626525</v>
       </c>
       <c r="B117" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12975,25 +12974,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13003,10 +13002,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>834187</v>
+        <v>834253</v>
       </c>
       <c r="R117" t="n">
-        <v>7347944</v>
+        <v>7347885</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13069,7 +13068,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626540</v>
+        <v>119626539</v>
       </c>
       <c r="B118" t="n">
         <v>91834</v>
@@ -13109,10 +13108,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834166</v>
+        <v>834204</v>
       </c>
       <c r="R118" t="n">
-        <v>7347884</v>
+        <v>7347896</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13175,10 +13174,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626525</v>
+        <v>119626416</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13187,25 +13186,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13215,10 +13214,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834253</v>
+        <v>834434</v>
       </c>
       <c r="R119" t="n">
-        <v>7347885</v>
+        <v>7347883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13281,10 +13280,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626539</v>
+        <v>119626404</v>
       </c>
       <c r="B120" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13297,21 +13296,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13321,10 +13320,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834204</v>
+        <v>834430</v>
       </c>
       <c r="R120" t="n">
-        <v>7347896</v>
+        <v>7347886</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13365,6 +13364,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119626416</v>
+        <v>119626405</v>
       </c>
       <c r="B121" t="n">
-        <v>89275</v>
+        <v>86412</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13399,25 +13399,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>834434</v>
+        <v>834216</v>
       </c>
       <c r="R121" t="n">
-        <v>7347883</v>
+        <v>7347860</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119626510</v>
+        <v>119626473</v>
       </c>
       <c r="B124" t="n">
-        <v>57421</v>
+        <v>91856</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13717,25 +13717,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103031</v>
+        <v>2059</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>834118</v>
+        <v>834384</v>
       </c>
       <c r="R124" t="n">
-        <v>7347885</v>
+        <v>7347916</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119626473</v>
+        <v>119626500</v>
       </c>
       <c r="B125" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13827,21 +13827,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13851,13 +13851,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>834384</v>
+        <v>834227</v>
       </c>
       <c r="R125" t="n">
-        <v>7347916</v>
+        <v>7347892</v>
       </c>
       <c r="S125" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13917,10 +13917,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626500</v>
+        <v>119626526</v>
       </c>
       <c r="B126" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13929,25 +13929,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834227</v>
+        <v>834382</v>
       </c>
       <c r="R126" t="n">
-        <v>7347892</v>
+        <v>7347924</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626526</v>
+        <v>119626503</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14035,25 +14035,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834382</v>
+        <v>834159</v>
       </c>
       <c r="R127" t="n">
-        <v>7347924</v>
+        <v>7347856</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14129,10 +14129,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119626503</v>
+        <v>119626510</v>
       </c>
       <c r="B128" t="n">
-        <v>91832</v>
+        <v>57421</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14141,25 +14141,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4361</v>
+        <v>103031</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>834159</v>
+        <v>834118</v>
       </c>
       <c r="R128" t="n">
-        <v>7347856</v>
+        <v>7347885</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119646305</v>
+        <v>119646271</v>
       </c>
       <c r="B147" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16159,21 +16159,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>834295</v>
+        <v>834478</v>
       </c>
       <c r="R147" t="n">
-        <v>7348050</v>
+        <v>7347964</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16249,10 +16249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119646281</v>
+        <v>119646305</v>
       </c>
       <c r="B148" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16265,21 +16265,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>834185</v>
+        <v>834295</v>
       </c>
       <c r="R148" t="n">
-        <v>7347860</v>
+        <v>7348050</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16355,10 +16355,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119646387</v>
+        <v>119646281</v>
       </c>
       <c r="B149" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16371,21 +16371,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>834581</v>
+        <v>834185</v>
       </c>
       <c r="R149" t="n">
-        <v>7347739</v>
+        <v>7347860</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16461,10 +16461,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119646278</v>
+        <v>119646387</v>
       </c>
       <c r="B150" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16477,21 +16477,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>834144</v>
+        <v>834581</v>
       </c>
       <c r="R150" t="n">
-        <v>7348044</v>
+        <v>7347739</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646271</v>
+        <v>119646278</v>
       </c>
       <c r="B151" t="n">
-        <v>91826</v>
+        <v>91463</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16583,21 +16583,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834478</v>
+        <v>834144</v>
       </c>
       <c r="R151" t="n">
-        <v>7347964</v>
+        <v>7348044</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646375</v>
+        <v>119646272</v>
       </c>
       <c r="B152" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16689,21 +16689,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834313</v>
+        <v>834136</v>
       </c>
       <c r="R152" t="n">
-        <v>7347844</v>
+        <v>7348051</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646362</v>
+        <v>119646273</v>
       </c>
       <c r="B153" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16795,21 +16795,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834150</v>
+        <v>834143</v>
       </c>
       <c r="R153" t="n">
-        <v>7347951</v>
+        <v>7348014</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,10 +16885,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646335</v>
+        <v>119646375</v>
       </c>
       <c r="B154" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16897,25 +16897,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834188</v>
+        <v>834313</v>
       </c>
       <c r="R154" t="n">
-        <v>7347887</v>
+        <v>7347844</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16991,10 +16991,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119646340</v>
+        <v>119646362</v>
       </c>
       <c r="B155" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17003,25 +17003,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>834444</v>
+        <v>834150</v>
       </c>
       <c r="R155" t="n">
-        <v>7347855</v>
+        <v>7347951</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119646371</v>
+        <v>119646335</v>
       </c>
       <c r="B156" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17109,25 +17109,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17137,10 +17137,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>834172</v>
+        <v>834188</v>
       </c>
       <c r="R156" t="n">
-        <v>7347857</v>
+        <v>7347887</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17203,10 +17203,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119646357</v>
+        <v>119646340</v>
       </c>
       <c r="B157" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17215,25 +17215,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>834118</v>
+        <v>834444</v>
       </c>
       <c r="R157" t="n">
-        <v>7348065</v>
+        <v>7347855</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17309,10 +17309,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119646272</v>
+        <v>119646371</v>
       </c>
       <c r="B158" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17325,21 +17325,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>834136</v>
+        <v>834172</v>
       </c>
       <c r="R158" t="n">
-        <v>7348051</v>
+        <v>7347857</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17415,10 +17415,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119646273</v>
+        <v>119646357</v>
       </c>
       <c r="B159" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17431,21 +17431,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17455,10 +17455,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>834143</v>
+        <v>834118</v>
       </c>
       <c r="R159" t="n">
-        <v>7348014</v>
+        <v>7348065</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20595,10 +20595,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119646289</v>
+        <v>119646295</v>
       </c>
       <c r="B189" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20611,21 +20611,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>834286</v>
+        <v>834273</v>
       </c>
       <c r="R189" t="n">
-        <v>7348064</v>
+        <v>7348017</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20701,10 +20701,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119646267</v>
+        <v>119646380</v>
       </c>
       <c r="B190" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20713,25 +20713,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20741,10 +20741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>834333</v>
+        <v>834492</v>
       </c>
       <c r="R190" t="n">
-        <v>7347848</v>
+        <v>7347839</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20807,10 +20807,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119646286</v>
+        <v>119646289</v>
       </c>
       <c r="B191" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20819,25 +20819,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>834520</v>
+        <v>834286</v>
       </c>
       <c r="R191" t="n">
-        <v>7347876</v>
+        <v>7348064</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20913,10 +20913,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119646263</v>
+        <v>119646267</v>
       </c>
       <c r="B192" t="n">
-        <v>86412</v>
+        <v>89275</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20925,25 +20925,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20953,10 +20953,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>834530</v>
+        <v>834333</v>
       </c>
       <c r="R192" t="n">
-        <v>7347888</v>
+        <v>7347848</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21019,10 +21019,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119646295</v>
+        <v>119646286</v>
       </c>
       <c r="B193" t="n">
-        <v>91856</v>
+        <v>91828</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21031,25 +21031,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21059,10 +21059,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>834273</v>
+        <v>834520</v>
       </c>
       <c r="R193" t="n">
-        <v>7348017</v>
+        <v>7347876</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21125,10 +21125,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119646380</v>
+        <v>119646263</v>
       </c>
       <c r="B194" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21141,21 +21141,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21165,10 +21165,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>834492</v>
+        <v>834530</v>
       </c>
       <c r="R194" t="n">
-        <v>7347839</v>
+        <v>7347888</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646396</v>
+        <v>119646261</v>
       </c>
       <c r="B200" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834563</v>
+        <v>834404</v>
       </c>
       <c r="R200" t="n">
-        <v>7347883</v>
+        <v>7347982</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,7 +21867,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646372</v>
+        <v>119646396</v>
       </c>
       <c r="B201" t="n">
         <v>91834</v>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834274</v>
+        <v>834563</v>
       </c>
       <c r="R201" t="n">
-        <v>7347868</v>
+        <v>7347883</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21973,10 +21973,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119646259</v>
+        <v>119646372</v>
       </c>
       <c r="B202" t="n">
-        <v>91836</v>
+        <v>91834</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21985,25 +21985,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4363</v>
+        <v>4362</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22013,10 +22013,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>834292</v>
+        <v>834274</v>
       </c>
       <c r="R202" t="n">
-        <v>7348037</v>
+        <v>7347868</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22079,10 +22079,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119646315</v>
+        <v>119646259</v>
       </c>
       <c r="B203" t="n">
-        <v>91832</v>
+        <v>91836</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22091,25 +22091,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4361</v>
+        <v>4363</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>834573</v>
+        <v>834292</v>
       </c>
       <c r="R203" t="n">
-        <v>7347882</v>
+        <v>7348037</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22185,7 +22185,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119646320</v>
+        <v>119646315</v>
       </c>
       <c r="B204" t="n">
         <v>91832</v>
@@ -22225,10 +22225,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>834545</v>
+        <v>834573</v>
       </c>
       <c r="R204" t="n">
-        <v>7347891</v>
+        <v>7347882</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119646261</v>
+        <v>119646320</v>
       </c>
       <c r="B205" t="n">
-        <v>79115</v>
+        <v>91832</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22307,21 +22307,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>834404</v>
+        <v>834545</v>
       </c>
       <c r="R205" t="n">
-        <v>7347982</v>
+        <v>7347891</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -7762,10 +7762,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119626452</v>
+        <v>119626406</v>
       </c>
       <c r="B68" t="n">
-        <v>91828</v>
+        <v>89633</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7774,25 +7774,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>149</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>834454</v>
+        <v>834121</v>
       </c>
       <c r="R68" t="n">
-        <v>7347892</v>
+        <v>7348010</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7840,12 +7840,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7868,10 +7874,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119626406</v>
+        <v>119626452</v>
       </c>
       <c r="B69" t="n">
-        <v>89633</v>
+        <v>91828</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7880,25 +7886,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7908,10 +7914,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>834121</v>
+        <v>834454</v>
       </c>
       <c r="R69" t="n">
-        <v>7348010</v>
+        <v>7347892</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7946,18 +7952,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9464,10 +9464,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626479</v>
+        <v>119626434</v>
       </c>
       <c r="B84" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9480,21 +9480,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834177</v>
+        <v>834189</v>
       </c>
       <c r="R84" t="n">
-        <v>7347881</v>
+        <v>7347957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626434</v>
+        <v>119626479</v>
       </c>
       <c r="B85" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9586,21 +9586,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834189</v>
+        <v>834177</v>
       </c>
       <c r="R85" t="n">
-        <v>7347957</v>
+        <v>7347881</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10206,10 +10206,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119626450</v>
+        <v>119626517</v>
       </c>
       <c r="B91" t="n">
-        <v>91828</v>
+        <v>91825</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10218,25 +10218,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>149</v>
+        <v>1968</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>834442</v>
+        <v>834243</v>
       </c>
       <c r="R91" t="n">
-        <v>7347873</v>
+        <v>7347862</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119626517</v>
+        <v>119626460</v>
       </c>
       <c r="B92" t="n">
-        <v>91825</v>
+        <v>91884</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1968</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>834243</v>
+        <v>834295</v>
       </c>
       <c r="R92" t="n">
-        <v>7347862</v>
+        <v>7347970</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10418,10 +10418,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119626504</v>
+        <v>119626423</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>56522</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10430,25 +10430,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10458,10 +10458,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>834309</v>
+        <v>834319</v>
       </c>
       <c r="R93" t="n">
-        <v>7347875</v>
+        <v>7347861</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10524,10 +10524,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119626508</v>
+        <v>119626450</v>
       </c>
       <c r="B94" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10536,25 +10536,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>834325</v>
+        <v>834442</v>
       </c>
       <c r="R94" t="n">
-        <v>7347870</v>
+        <v>7347873</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10630,10 +10630,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119626528</v>
+        <v>119626504</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10642,25 +10642,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>834454</v>
+        <v>834309</v>
       </c>
       <c r="R95" t="n">
-        <v>7347886</v>
+        <v>7347875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10736,10 +10736,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119626522</v>
+        <v>119626508</v>
       </c>
       <c r="B96" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10748,25 +10748,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>834086</v>
+        <v>834325</v>
       </c>
       <c r="R96" t="n">
-        <v>7347878</v>
+        <v>7347870</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119626436</v>
+        <v>119626528</v>
       </c>
       <c r="B97" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10854,25 +10854,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>834236</v>
+        <v>834454</v>
       </c>
       <c r="R97" t="n">
-        <v>7347993</v>
+        <v>7347886</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10948,10 +10948,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119626460</v>
+        <v>119626522</v>
       </c>
       <c r="B98" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10960,25 +10960,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>834295</v>
+        <v>834086</v>
       </c>
       <c r="R98" t="n">
-        <v>7347970</v>
+        <v>7347878</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11054,10 +11054,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119626423</v>
+        <v>119626436</v>
       </c>
       <c r="B99" t="n">
-        <v>56522</v>
+        <v>91463</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11066,25 +11066,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>834319</v>
+        <v>834236</v>
       </c>
       <c r="R99" t="n">
-        <v>7347861</v>
+        <v>7347993</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646261</v>
+        <v>119646396</v>
       </c>
       <c r="B200" t="n">
-        <v>79115</v>
+        <v>91834</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834404</v>
+        <v>834563</v>
       </c>
       <c r="R200" t="n">
-        <v>7347982</v>
+        <v>7347883</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,7 +21867,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646396</v>
+        <v>119646372</v>
       </c>
       <c r="B201" t="n">
         <v>91834</v>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834563</v>
+        <v>834274</v>
       </c>
       <c r="R201" t="n">
-        <v>7347883</v>
+        <v>7347868</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21973,10 +21973,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119646372</v>
+        <v>119646259</v>
       </c>
       <c r="B202" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21985,25 +21985,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4362</v>
+        <v>4363</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22013,10 +22013,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>834274</v>
+        <v>834292</v>
       </c>
       <c r="R202" t="n">
-        <v>7347868</v>
+        <v>7348037</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22079,10 +22079,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119646259</v>
+        <v>119646315</v>
       </c>
       <c r="B203" t="n">
-        <v>91836</v>
+        <v>91832</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22091,25 +22091,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>834292</v>
+        <v>834573</v>
       </c>
       <c r="R203" t="n">
-        <v>7348037</v>
+        <v>7347882</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22185,7 +22185,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119646315</v>
+        <v>119646320</v>
       </c>
       <c r="B204" t="n">
         <v>91832</v>
@@ -22225,10 +22225,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>834573</v>
+        <v>834545</v>
       </c>
       <c r="R204" t="n">
-        <v>7347882</v>
+        <v>7347891</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119646320</v>
+        <v>119646261</v>
       </c>
       <c r="B205" t="n">
-        <v>91832</v>
+        <v>79115</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22307,21 +22307,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>834545</v>
+        <v>834404</v>
       </c>
       <c r="R205" t="n">
-        <v>7347891</v>
+        <v>7347982</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -3734,7 +3734,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119626481</v>
+        <v>119626479</v>
       </c>
       <c r="B30" t="n">
         <v>91856</v>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>834455</v>
+        <v>834177</v>
       </c>
       <c r="R30" t="n">
-        <v>7347890</v>
+        <v>7347881</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119626519</v>
+        <v>119626517</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91825</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3852,25 +3852,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>834148</v>
+        <v>834243</v>
       </c>
       <c r="R31" t="n">
-        <v>7347973</v>
+        <v>7347862</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119626548</v>
+        <v>119626436</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>834151</v>
+        <v>834236</v>
       </c>
       <c r="R32" t="n">
-        <v>7347881</v>
+        <v>7347993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119626527</v>
+        <v>119626444</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>834435</v>
+        <v>834154</v>
       </c>
       <c r="R33" t="n">
-        <v>7347869</v>
+        <v>7347884</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119626433</v>
+        <v>119626545</v>
       </c>
       <c r="B34" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>834169</v>
+        <v>834320</v>
       </c>
       <c r="R34" t="n">
-        <v>7347940</v>
+        <v>7347855</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119626557</v>
+        <v>119626526</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>834308</v>
+        <v>834382</v>
       </c>
       <c r="R35" t="n">
-        <v>7347903</v>
+        <v>7347924</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626537</v>
+        <v>119626557</v>
       </c>
       <c r="B36" t="n">
         <v>91834</v>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>834282</v>
+        <v>834308</v>
       </c>
       <c r="R36" t="n">
-        <v>7347983</v>
+        <v>7347903</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119626428</v>
+        <v>119626521</v>
       </c>
       <c r="B38" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>834149</v>
+        <v>834220</v>
       </c>
       <c r="R38" t="n">
-        <v>7347970</v>
+        <v>7347890</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119626462</v>
+        <v>119626481</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4704,21 +4704,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>834252</v>
+        <v>834455</v>
       </c>
       <c r="R39" t="n">
-        <v>7347832</v>
+        <v>7347890</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119626421</v>
+        <v>119626537</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,25 +4806,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>834160</v>
+        <v>834282</v>
       </c>
       <c r="R40" t="n">
-        <v>7347850</v>
+        <v>7347983</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626430</v>
+        <v>119626442</v>
       </c>
       <c r="B41" t="n">
-        <v>91826</v>
+        <v>91463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4916,21 +4916,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834295</v>
+        <v>834160</v>
       </c>
       <c r="R41" t="n">
-        <v>7348032</v>
+        <v>7347864</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626507</v>
+        <v>119626440</v>
       </c>
       <c r="B42" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834277</v>
+        <v>834041</v>
       </c>
       <c r="R42" t="n">
-        <v>7347848</v>
+        <v>7347837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626486</v>
+        <v>119626456</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5124,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834186</v>
+        <v>834204</v>
       </c>
       <c r="R43" t="n">
-        <v>7347942</v>
+        <v>7347855</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119626545</v>
+        <v>119626510</v>
       </c>
       <c r="B44" t="n">
-        <v>91834</v>
+        <v>57421</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5230,25 +5230,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>834320</v>
+        <v>834118</v>
       </c>
       <c r="R44" t="n">
-        <v>7347855</v>
+        <v>7347885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119626420</v>
+        <v>119626405</v>
       </c>
       <c r="B45" t="n">
-        <v>89275</v>
+        <v>86412</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5336,25 +5336,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>834252</v>
+        <v>834216</v>
       </c>
       <c r="R45" t="n">
-        <v>7347884</v>
+        <v>7347860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119626455</v>
+        <v>119626473</v>
       </c>
       <c r="B46" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>834288</v>
+        <v>834384</v>
       </c>
       <c r="R46" t="n">
-        <v>7347877</v>
+        <v>7347916</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119626499</v>
+        <v>119626535</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>834153</v>
+        <v>834187</v>
       </c>
       <c r="R47" t="n">
-        <v>7347952</v>
+        <v>7347944</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119626533</v>
+        <v>119626504</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>834153</v>
+        <v>834309</v>
       </c>
       <c r="R48" t="n">
-        <v>7347932</v>
+        <v>7347875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119626551</v>
+        <v>119626533</v>
       </c>
       <c r="B49" t="n">
         <v>91834</v>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>834249</v>
+        <v>834153</v>
       </c>
       <c r="R49" t="n">
-        <v>7347880</v>
+        <v>7347932</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626542</v>
+        <v>119626437</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5870,21 +5870,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>834148</v>
+        <v>834288</v>
       </c>
       <c r="R50" t="n">
-        <v>7347880</v>
+        <v>7347985</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5960,10 +5960,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626550</v>
+        <v>119626507</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5976,21 +5976,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>834212</v>
+        <v>834277</v>
       </c>
       <c r="R51" t="n">
-        <v>7347855</v>
+        <v>7347848</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119626439</v>
+        <v>119626503</v>
       </c>
       <c r="B52" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6082,21 +6082,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>834018</v>
+        <v>834159</v>
       </c>
       <c r="R52" t="n">
-        <v>7347852</v>
+        <v>7347856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119626523</v>
+        <v>119626408</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6184,25 +6184,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>834210</v>
+        <v>834123</v>
       </c>
       <c r="R53" t="n">
-        <v>7347853</v>
+        <v>7347975</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119626506</v>
+        <v>119626416</v>
       </c>
       <c r="B54" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6290,25 +6290,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>834322</v>
+        <v>834434</v>
       </c>
       <c r="R54" t="n">
-        <v>7347857</v>
+        <v>7347883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6384,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119626414</v>
+        <v>119626463</v>
       </c>
       <c r="B55" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6396,25 +6396,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>834252</v>
+        <v>834272</v>
       </c>
       <c r="R55" t="n">
-        <v>7347893</v>
+        <v>7347885</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6490,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119626515</v>
+        <v>119626452</v>
       </c>
       <c r="B56" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6502,25 +6502,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1968</v>
+        <v>149</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>834243</v>
+        <v>834454</v>
       </c>
       <c r="R56" t="n">
-        <v>7348008</v>
+        <v>7347892</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119626520</v>
+        <v>119626505</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6608,25 +6608,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>834276</v>
+        <v>834329</v>
       </c>
       <c r="R57" t="n">
-        <v>7347908</v>
+        <v>7347858</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119626453</v>
+        <v>119626551</v>
       </c>
       <c r="B58" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6718,21 +6718,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>834124</v>
+        <v>834249</v>
       </c>
       <c r="R58" t="n">
-        <v>7347874</v>
+        <v>7347880</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6808,10 +6808,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119626532</v>
+        <v>119626539</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6820,25 +6820,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>834192</v>
+        <v>834204</v>
       </c>
       <c r="R59" t="n">
-        <v>7347888</v>
+        <v>7347896</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119626443</v>
+        <v>119626446</v>
       </c>
       <c r="B60" t="n">
         <v>91463</v>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>834325</v>
+        <v>834267</v>
       </c>
       <c r="R60" t="n">
-        <v>7347874</v>
+        <v>7347889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119626498</v>
+        <v>119626555</v>
       </c>
       <c r="B61" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7032,25 +7032,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>834053</v>
+        <v>834442</v>
       </c>
       <c r="R61" t="n">
-        <v>7347834</v>
+        <v>7347879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119626497</v>
+        <v>119626522</v>
       </c>
       <c r="B62" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7142,21 +7142,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>834121</v>
+        <v>834086</v>
       </c>
       <c r="R62" t="n">
-        <v>7347872</v>
+        <v>7347878</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119626432</v>
+        <v>119626433</v>
       </c>
       <c r="B63" t="n">
-        <v>91826</v>
+        <v>91463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7248,21 +7248,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>834167</v>
+        <v>834169</v>
       </c>
       <c r="R63" t="n">
-        <v>7348024</v>
+        <v>7347940</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119626444</v>
+        <v>119626439</v>
       </c>
       <c r="B64" t="n">
         <v>91463</v>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>834154</v>
+        <v>834018</v>
       </c>
       <c r="R64" t="n">
-        <v>7347884</v>
+        <v>7347852</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7444,10 +7444,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119626544</v>
+        <v>119626500</v>
       </c>
       <c r="B65" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7460,21 +7460,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>834331</v>
+        <v>834227</v>
       </c>
       <c r="R65" t="n">
-        <v>7347868</v>
+        <v>7347892</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7550,7 +7550,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119626521</v>
+        <v>119626531</v>
       </c>
       <c r="B66" t="n">
         <v>91840</v>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>834220</v>
+        <v>834282</v>
       </c>
       <c r="R66" t="n">
-        <v>7347890</v>
+        <v>7347898</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7656,10 +7656,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119626495</v>
+        <v>119626483</v>
       </c>
       <c r="B67" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7672,21 +7672,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>834287</v>
+        <v>834080</v>
       </c>
       <c r="R67" t="n">
-        <v>7347954</v>
+        <v>7347837</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7762,10 +7762,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119626406</v>
+        <v>119626525</v>
       </c>
       <c r="B68" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7774,25 +7774,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>834121</v>
+        <v>834253</v>
       </c>
       <c r="R68" t="n">
-        <v>7348010</v>
+        <v>7347885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7840,18 +7840,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7874,10 +7868,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119626452</v>
+        <v>119626404</v>
       </c>
       <c r="B69" t="n">
-        <v>91828</v>
+        <v>86412</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7886,25 +7880,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>149</v>
+        <v>3690</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7914,10 +7908,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>834454</v>
+        <v>834430</v>
       </c>
       <c r="R69" t="n">
-        <v>7347892</v>
+        <v>7347886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,6 +7952,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7980,7 +7975,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119626440</v>
+        <v>119626453</v>
       </c>
       <c r="B70" t="n">
         <v>91463</v>
@@ -8020,10 +8015,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>834041</v>
+        <v>834124</v>
       </c>
       <c r="R70" t="n">
-        <v>7347837</v>
+        <v>7347874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8086,10 +8081,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119626556</v>
+        <v>119626495</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8098,25 +8093,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8126,10 +8121,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>834453</v>
+        <v>834287</v>
       </c>
       <c r="R71" t="n">
-        <v>7347884</v>
+        <v>7347954</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8192,10 +8187,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119626531</v>
+        <v>119626516</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91825</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8204,25 +8199,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8232,10 +8227,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>834282</v>
+        <v>834083</v>
       </c>
       <c r="R72" t="n">
-        <v>7347898</v>
+        <v>7347877</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8298,10 +8293,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119626483</v>
+        <v>119626542</v>
       </c>
       <c r="B73" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8310,25 +8305,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8338,10 +8333,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>834080</v>
+        <v>834148</v>
       </c>
       <c r="R73" t="n">
-        <v>7347837</v>
+        <v>7347880</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8404,10 +8399,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119626534</v>
+        <v>119626420</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8416,25 +8411,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8444,10 +8439,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>834168</v>
+        <v>834252</v>
       </c>
       <c r="R74" t="n">
-        <v>7347939</v>
+        <v>7347884</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8510,10 +8505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119626509</v>
+        <v>119626423</v>
       </c>
       <c r="B75" t="n">
-        <v>91863</v>
+        <v>56522</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8522,25 +8517,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8550,10 +8545,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>834244</v>
+        <v>834319</v>
       </c>
       <c r="R75" t="n">
-        <v>7347889</v>
+        <v>7347861</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8616,7 +8611,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119626467</v>
+        <v>119626460</v>
       </c>
       <c r="B76" t="n">
         <v>91884</v>
@@ -8656,10 +8651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>834310</v>
+        <v>834295</v>
       </c>
       <c r="R76" t="n">
-        <v>7347899</v>
+        <v>7347970</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8722,10 +8717,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119626538</v>
+        <v>119626465</v>
       </c>
       <c r="B77" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8738,21 +8733,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8762,10 +8757,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>834292</v>
+        <v>834267</v>
       </c>
       <c r="R77" t="n">
-        <v>7347968</v>
+        <v>7347889</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8828,10 +8823,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119626543</v>
+        <v>119626409</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8840,25 +8835,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8868,10 +8863,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>834275</v>
+        <v>834121</v>
       </c>
       <c r="R78" t="n">
-        <v>7347856</v>
+        <v>7348010</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8934,10 +8929,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119626547</v>
+        <v>119626497</v>
       </c>
       <c r="B79" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8946,25 +8941,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8974,10 +8969,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>834115</v>
+        <v>834121</v>
       </c>
       <c r="R79" t="n">
-        <v>7347875</v>
+        <v>7347872</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9040,10 +9035,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119626549</v>
+        <v>119626520</v>
       </c>
       <c r="B80" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9052,25 +9047,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9080,10 +9075,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>834196</v>
+        <v>834276</v>
       </c>
       <c r="R80" t="n">
-        <v>7347874</v>
+        <v>7347908</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9146,10 +9141,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119626465</v>
+        <v>119626528</v>
       </c>
       <c r="B81" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9158,25 +9153,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9186,10 +9181,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>834267</v>
+        <v>834454</v>
       </c>
       <c r="R81" t="n">
-        <v>7347889</v>
+        <v>7347886</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9252,10 +9247,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119626411</v>
+        <v>119626556</v>
       </c>
       <c r="B82" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9264,25 +9259,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9292,10 +9287,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>834141</v>
+        <v>834453</v>
       </c>
       <c r="R82" t="n">
-        <v>7348021</v>
+        <v>7347884</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9358,10 +9353,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119626448</v>
+        <v>119626523</v>
       </c>
       <c r="B83" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9370,25 +9365,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9398,10 +9393,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>834184</v>
+        <v>834210</v>
       </c>
       <c r="R83" t="n">
-        <v>7347877</v>
+        <v>7347853</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9464,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626434</v>
+        <v>119626532</v>
       </c>
       <c r="B84" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9476,25 +9471,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9504,10 +9499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834189</v>
+        <v>834192</v>
       </c>
       <c r="R84" t="n">
-        <v>7347957</v>
+        <v>7347888</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9570,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626479</v>
+        <v>119626501</v>
       </c>
       <c r="B85" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9586,21 +9581,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9610,10 +9605,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834177</v>
+        <v>834207</v>
       </c>
       <c r="R85" t="n">
-        <v>7347881</v>
+        <v>7347898</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9676,10 +9671,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119626418</v>
+        <v>119626519</v>
       </c>
       <c r="B86" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9688,25 +9683,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9716,10 +9711,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>834185</v>
+        <v>834148</v>
       </c>
       <c r="R86" t="n">
-        <v>7347878</v>
+        <v>7347973</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9782,10 +9777,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119626409</v>
+        <v>119626553</v>
       </c>
       <c r="B87" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9794,25 +9789,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9822,10 +9817,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>834121</v>
+        <v>834388</v>
       </c>
       <c r="R87" t="n">
-        <v>7348010</v>
+        <v>7347909</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9888,10 +9883,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119626442</v>
+        <v>119626540</v>
       </c>
       <c r="B88" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9904,21 +9899,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9928,10 +9923,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>834160</v>
+        <v>834166</v>
       </c>
       <c r="R88" t="n">
-        <v>7347864</v>
+        <v>7347884</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9994,10 +9989,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119626412</v>
+        <v>119626527</v>
       </c>
       <c r="B89" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10006,25 +10001,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10034,10 +10029,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>834267</v>
+        <v>834435</v>
       </c>
       <c r="R89" t="n">
-        <v>7347984</v>
+        <v>7347869</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10100,10 +10095,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119626463</v>
+        <v>119626434</v>
       </c>
       <c r="B90" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10116,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10140,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>834272</v>
+        <v>834189</v>
       </c>
       <c r="R90" t="n">
-        <v>7347885</v>
+        <v>7347957</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10206,10 +10201,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119626517</v>
+        <v>119626455</v>
       </c>
       <c r="B91" t="n">
-        <v>91825</v>
+        <v>91463</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10222,21 +10217,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1968</v>
+        <v>4745</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10246,10 +10241,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>834243</v>
+        <v>834288</v>
       </c>
       <c r="R91" t="n">
-        <v>7347862</v>
+        <v>7347877</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10312,10 +10307,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119626460</v>
+        <v>119626430</v>
       </c>
       <c r="B92" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10328,21 +10323,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10355,7 +10350,7 @@
         <v>834295</v>
       </c>
       <c r="R92" t="n">
-        <v>7347970</v>
+        <v>7348032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10418,10 +10413,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119626423</v>
+        <v>119626428</v>
       </c>
       <c r="B93" t="n">
-        <v>56522</v>
+        <v>91826</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10430,25 +10425,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>3100</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10458,10 +10453,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>834319</v>
+        <v>834149</v>
       </c>
       <c r="R93" t="n">
-        <v>7347861</v>
+        <v>7347970</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10524,10 +10519,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119626450</v>
+        <v>119626475</v>
       </c>
       <c r="B94" t="n">
-        <v>91828</v>
+        <v>91856</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10536,25 +10531,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10564,10 +10559,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>834442</v>
+        <v>834243</v>
       </c>
       <c r="R94" t="n">
-        <v>7347873</v>
+        <v>7348008</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10630,10 +10625,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119626504</v>
+        <v>119626554</v>
       </c>
       <c r="B95" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10646,21 +10641,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10670,10 +10665,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>834309</v>
+        <v>834433</v>
       </c>
       <c r="R95" t="n">
-        <v>7347875</v>
+        <v>7347878</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10736,10 +10731,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119626508</v>
+        <v>119626550</v>
       </c>
       <c r="B96" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10752,21 +10747,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10776,10 +10771,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>834325</v>
+        <v>834212</v>
       </c>
       <c r="R96" t="n">
-        <v>7347870</v>
+        <v>7347855</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10842,10 +10837,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119626528</v>
+        <v>119626534</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10854,25 +10849,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10882,10 +10877,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>834454</v>
+        <v>834168</v>
       </c>
       <c r="R97" t="n">
-        <v>7347886</v>
+        <v>7347939</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10948,10 +10943,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119626522</v>
+        <v>119626549</v>
       </c>
       <c r="B98" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10960,25 +10955,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10988,10 +10983,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>834086</v>
+        <v>834196</v>
       </c>
       <c r="R98" t="n">
-        <v>7347878</v>
+        <v>7347874</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11054,10 +11049,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119626436</v>
+        <v>119626432</v>
       </c>
       <c r="B99" t="n">
-        <v>91463</v>
+        <v>91826</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11070,21 +11065,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11094,10 +11089,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>834236</v>
+        <v>834167</v>
       </c>
       <c r="R99" t="n">
-        <v>7347993</v>
+        <v>7348024</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11160,10 +11155,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119626456</v>
+        <v>119626509</v>
       </c>
       <c r="B100" t="n">
-        <v>91883</v>
+        <v>91863</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11176,21 +11171,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11200,10 +11195,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>834204</v>
+        <v>834244</v>
       </c>
       <c r="R100" t="n">
-        <v>7347855</v>
+        <v>7347889</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11266,10 +11261,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119626477</v>
+        <v>119626412</v>
       </c>
       <c r="B101" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11278,25 +11273,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11306,10 +11301,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>834287</v>
+        <v>834267</v>
       </c>
       <c r="R101" t="n">
-        <v>7348033</v>
+        <v>7347984</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11372,10 +11367,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119626529</v>
+        <v>119626458</v>
       </c>
       <c r="B102" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11384,25 +11379,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11412,10 +11407,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>834467</v>
+        <v>834214</v>
       </c>
       <c r="R102" t="n">
-        <v>7347889</v>
+        <v>7347853</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11478,10 +11473,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119626446</v>
+        <v>119626462</v>
       </c>
       <c r="B103" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11494,21 +11489,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11518,10 +11513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>834267</v>
+        <v>834252</v>
       </c>
       <c r="R103" t="n">
-        <v>7347889</v>
+        <v>7347832</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11584,10 +11579,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119626408</v>
+        <v>119626529</v>
       </c>
       <c r="B104" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11596,25 +11591,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11624,10 +11619,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>834123</v>
+        <v>834467</v>
       </c>
       <c r="R104" t="n">
-        <v>7347975</v>
+        <v>7347889</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11690,10 +11685,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119626516</v>
+        <v>119626411</v>
       </c>
       <c r="B105" t="n">
-        <v>91825</v>
+        <v>89275</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11702,25 +11697,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1968</v>
+        <v>6286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11730,10 +11725,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>834083</v>
+        <v>834141</v>
       </c>
       <c r="R105" t="n">
-        <v>7347877</v>
+        <v>7348021</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11796,10 +11791,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119626475</v>
+        <v>119626414</v>
       </c>
       <c r="B106" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11808,25 +11803,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11836,10 +11831,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>834243</v>
+        <v>834252</v>
       </c>
       <c r="R106" t="n">
-        <v>7348008</v>
+        <v>7347893</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11902,10 +11897,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626530</v>
+        <v>119626448</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11914,25 +11909,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11942,10 +11937,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>834170</v>
+        <v>834184</v>
       </c>
       <c r="R107" t="n">
-        <v>7347895</v>
+        <v>7347877</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12008,10 +12003,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626505</v>
+        <v>119626406</v>
       </c>
       <c r="B108" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12024,21 +12019,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12048,10 +12043,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>834329</v>
+        <v>834121</v>
       </c>
       <c r="R108" t="n">
-        <v>7347858</v>
+        <v>7348010</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12086,12 +12081,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12114,10 +12115,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119626437</v>
+        <v>119626543</v>
       </c>
       <c r="B109" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12130,21 +12131,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12154,10 +12155,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>834288</v>
+        <v>834275</v>
       </c>
       <c r="R109" t="n">
-        <v>7347985</v>
+        <v>7347856</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12220,10 +12221,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119626458</v>
+        <v>119626486</v>
       </c>
       <c r="B110" t="n">
-        <v>91883</v>
+        <v>91852</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12232,25 +12233,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12260,10 +12261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>834214</v>
+        <v>834186</v>
       </c>
       <c r="R110" t="n">
-        <v>7347853</v>
+        <v>7347942</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12326,10 +12327,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119626554</v>
+        <v>119626515</v>
       </c>
       <c r="B111" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,21 +12343,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12366,10 +12367,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>834433</v>
+        <v>834243</v>
       </c>
       <c r="R111" t="n">
-        <v>7347878</v>
+        <v>7348008</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12432,7 +12433,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119626553</v>
+        <v>119626548</v>
       </c>
       <c r="B112" t="n">
         <v>91834</v>
@@ -12472,10 +12473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>834388</v>
+        <v>834151</v>
       </c>
       <c r="R112" t="n">
-        <v>7347909</v>
+        <v>7347881</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12538,7 +12539,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119626536</v>
+        <v>119626538</v>
       </c>
       <c r="B113" t="n">
         <v>91834</v>
@@ -12578,10 +12579,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>834190</v>
+        <v>834292</v>
       </c>
       <c r="R113" t="n">
-        <v>7347950</v>
+        <v>7347968</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12644,10 +12645,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119626501</v>
+        <v>119626530</v>
       </c>
       <c r="B114" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12656,25 +12657,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12684,10 +12685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>834207</v>
+        <v>834170</v>
       </c>
       <c r="R114" t="n">
-        <v>7347898</v>
+        <v>7347895</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12750,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119626535</v>
+        <v>119626508</v>
       </c>
       <c r="B115" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12766,21 +12767,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12790,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>834187</v>
+        <v>834325</v>
       </c>
       <c r="R115" t="n">
-        <v>7347944</v>
+        <v>7347870</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12856,7 +12857,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119626540</v>
+        <v>119626547</v>
       </c>
       <c r="B116" t="n">
         <v>91834</v>
@@ -12896,10 +12897,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>834166</v>
+        <v>834115</v>
       </c>
       <c r="R116" t="n">
-        <v>7347884</v>
+        <v>7347875</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12962,10 +12963,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119626525</v>
+        <v>119626421</v>
       </c>
       <c r="B117" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12978,21 +12979,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13002,10 +13003,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>834253</v>
+        <v>834160</v>
       </c>
       <c r="R117" t="n">
-        <v>7347885</v>
+        <v>7347850</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13068,10 +13069,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626539</v>
+        <v>119626477</v>
       </c>
       <c r="B118" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13084,21 +13085,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13108,10 +13109,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834204</v>
+        <v>834287</v>
       </c>
       <c r="R118" t="n">
-        <v>7347896</v>
+        <v>7348033</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13174,10 +13175,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626416</v>
+        <v>119626536</v>
       </c>
       <c r="B119" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13186,25 +13187,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13214,10 +13215,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834434</v>
+        <v>834190</v>
       </c>
       <c r="R119" t="n">
-        <v>7347883</v>
+        <v>7347950</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13280,10 +13281,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626404</v>
+        <v>119626450</v>
       </c>
       <c r="B120" t="n">
-        <v>86412</v>
+        <v>91828</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13292,25 +13293,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3690</v>
+        <v>149</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13320,10 +13321,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834430</v>
+        <v>834442</v>
       </c>
       <c r="R120" t="n">
-        <v>7347886</v>
+        <v>7347873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13364,7 +13365,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119626405</v>
+        <v>119626506</v>
       </c>
       <c r="B121" t="n">
-        <v>86412</v>
+        <v>91832</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13403,21 +13403,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>834216</v>
+        <v>834322</v>
       </c>
       <c r="R121" t="n">
-        <v>7347860</v>
+        <v>7347857</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119626431</v>
+        <v>119626418</v>
       </c>
       <c r="B122" t="n">
-        <v>91826</v>
+        <v>89275</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>834318</v>
+        <v>834185</v>
       </c>
       <c r="R122" t="n">
-        <v>7347852</v>
+        <v>7347878</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119626555</v>
+        <v>119626467</v>
       </c>
       <c r="B123" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13615,21 +13615,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13639,10 +13639,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>834442</v>
+        <v>834310</v>
       </c>
       <c r="R123" t="n">
-        <v>7347879</v>
+        <v>7347899</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119626473</v>
+        <v>119626443</v>
       </c>
       <c r="B124" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13721,21 +13721,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>834384</v>
+        <v>834325</v>
       </c>
       <c r="R124" t="n">
-        <v>7347916</v>
+        <v>7347874</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119626500</v>
+        <v>119626431</v>
       </c>
       <c r="B125" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13827,21 +13827,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>834227</v>
+        <v>834318</v>
       </c>
       <c r="R125" t="n">
-        <v>7347892</v>
+        <v>7347852</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13917,10 +13917,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626526</v>
+        <v>119626499</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13929,25 +13929,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834382</v>
+        <v>834153</v>
       </c>
       <c r="R126" t="n">
-        <v>7347924</v>
+        <v>7347952</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626503</v>
+        <v>119626544</v>
       </c>
       <c r="B127" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14039,21 +14039,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834159</v>
+        <v>834331</v>
       </c>
       <c r="R127" t="n">
-        <v>7347856</v>
+        <v>7347868</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14129,10 +14129,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119626510</v>
+        <v>119626498</v>
       </c>
       <c r="B128" t="n">
-        <v>57421</v>
+        <v>96868</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14145,21 +14145,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>834118</v>
+        <v>834053</v>
       </c>
       <c r="R128" t="n">
-        <v>7347885</v>
+        <v>7347834</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119646313</v>
+        <v>119646394</v>
       </c>
       <c r="B129" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14251,21 +14251,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>834549</v>
+        <v>834555</v>
       </c>
       <c r="R129" t="n">
-        <v>7347855</v>
+        <v>7347854</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,10 +14341,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119646394</v>
+        <v>119646276</v>
       </c>
       <c r="B130" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14357,21 +14357,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14381,10 +14381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>834555</v>
+        <v>834519</v>
       </c>
       <c r="R130" t="n">
-        <v>7347854</v>
+        <v>7347875</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119646269</v>
+        <v>119646286</v>
       </c>
       <c r="B131" t="n">
-        <v>89275</v>
+        <v>91828</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14463,21 +14463,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6286</v>
+        <v>149</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>834531</v>
+        <v>834520</v>
       </c>
       <c r="R131" t="n">
-        <v>7347887</v>
+        <v>7347876</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14553,10 +14553,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119646328</v>
+        <v>119646296</v>
       </c>
       <c r="B132" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14565,25 +14565,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>834265</v>
+        <v>834546</v>
       </c>
       <c r="R132" t="n">
-        <v>7348012</v>
+        <v>7347860</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14659,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119646296</v>
+        <v>119646362</v>
       </c>
       <c r="B133" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14675,21 +14675,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>834546</v>
+        <v>834150</v>
       </c>
       <c r="R133" t="n">
-        <v>7347860</v>
+        <v>7347951</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14765,10 +14765,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119646306</v>
+        <v>119646343</v>
       </c>
       <c r="B134" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14777,25 +14777,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14805,10 +14805,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>834178</v>
+        <v>834547</v>
       </c>
       <c r="R134" t="n">
-        <v>7348061</v>
+        <v>7347878</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14871,7 +14871,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119646356</v>
+        <v>119646387</v>
       </c>
       <c r="B135" t="n">
         <v>91834</v>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>834132</v>
+        <v>834581</v>
       </c>
       <c r="R135" t="n">
-        <v>7348055</v>
+        <v>7347739</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14977,7 +14977,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119646276</v>
+        <v>119646272</v>
       </c>
       <c r="B136" t="n">
         <v>91826</v>
@@ -15017,10 +15017,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>834519</v>
+        <v>834136</v>
       </c>
       <c r="R136" t="n">
-        <v>7347875</v>
+        <v>7348051</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15083,10 +15083,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119646275</v>
+        <v>119646267</v>
       </c>
       <c r="B137" t="n">
-        <v>91826</v>
+        <v>89275</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15095,25 +15095,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>834351</v>
+        <v>834333</v>
       </c>
       <c r="R137" t="n">
-        <v>7347847</v>
+        <v>7347848</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119646343</v>
+        <v>119646279</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15201,25 +15201,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>834547</v>
+        <v>834196</v>
       </c>
       <c r="R138" t="n">
-        <v>7347878</v>
+        <v>7347922</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119646385</v>
+        <v>119646391</v>
       </c>
       <c r="B139" t="n">
         <v>91834</v>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>834545</v>
+        <v>834547</v>
       </c>
       <c r="R139" t="n">
-        <v>7347772</v>
+        <v>7347853</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15401,10 +15401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119646351</v>
+        <v>119646326</v>
       </c>
       <c r="B140" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>834272</v>
+        <v>834160</v>
       </c>
       <c r="R140" t="n">
-        <v>7348066</v>
+        <v>7347971</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119646391</v>
+        <v>119646374</v>
       </c>
       <c r="B141" t="n">
         <v>91834</v>
@@ -15547,10 +15547,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>834547</v>
+        <v>834296</v>
       </c>
       <c r="R141" t="n">
-        <v>7347853</v>
+        <v>7347848</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,10 +15613,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119646330</v>
+        <v>119646398</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15625,25 +15625,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>834475</v>
+        <v>834549</v>
       </c>
       <c r="R142" t="n">
-        <v>7347966</v>
+        <v>7347890</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15719,7 +15719,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119646378</v>
+        <v>119646384</v>
       </c>
       <c r="B143" t="n">
         <v>91834</v>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>834385</v>
+        <v>834524</v>
       </c>
       <c r="R143" t="n">
-        <v>7347840</v>
+        <v>7347806</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119646354</v>
+        <v>119646261</v>
       </c>
       <c r="B144" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>834171</v>
+        <v>834404</v>
       </c>
       <c r="R144" t="n">
-        <v>7348044</v>
+        <v>7347982</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119646369</v>
+        <v>119646283</v>
       </c>
       <c r="B145" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15943,25 +15943,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>834190</v>
+        <v>834500</v>
       </c>
       <c r="R145" t="n">
-        <v>7347887</v>
+        <v>7347836</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16037,10 +16037,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119646303</v>
+        <v>119646382</v>
       </c>
       <c r="B146" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16053,21 +16053,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>834528</v>
+        <v>834509</v>
       </c>
       <c r="R146" t="n">
-        <v>7347966</v>
+        <v>7347828</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119646271</v>
+        <v>119646306</v>
       </c>
       <c r="B147" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16159,21 +16159,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>834478</v>
+        <v>834178</v>
       </c>
       <c r="R147" t="n">
-        <v>7347964</v>
+        <v>7348061</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16249,10 +16249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119646305</v>
+        <v>119646351</v>
       </c>
       <c r="B148" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16265,21 +16265,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>834295</v>
+        <v>834272</v>
       </c>
       <c r="R148" t="n">
-        <v>7348050</v>
+        <v>7348066</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16355,10 +16355,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119646281</v>
+        <v>119646360</v>
       </c>
       <c r="B149" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16371,21 +16371,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>834185</v>
+        <v>834135</v>
       </c>
       <c r="R149" t="n">
-        <v>7347860</v>
+        <v>7347955</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119646387</v>
+        <v>119646359</v>
       </c>
       <c r="B150" t="n">
         <v>91834</v>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>834581</v>
+        <v>834110</v>
       </c>
       <c r="R150" t="n">
-        <v>7347739</v>
+        <v>7348050</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646278</v>
+        <v>119646268</v>
       </c>
       <c r="B151" t="n">
-        <v>91463</v>
+        <v>89275</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16579,25 +16579,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4745</v>
+        <v>6286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834144</v>
+        <v>834339</v>
       </c>
       <c r="R151" t="n">
-        <v>7348044</v>
+        <v>7347842</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646272</v>
+        <v>119646341</v>
       </c>
       <c r="B152" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834136</v>
+        <v>834561</v>
       </c>
       <c r="R152" t="n">
-        <v>7348051</v>
+        <v>7347875</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646273</v>
+        <v>119646396</v>
       </c>
       <c r="B153" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16795,21 +16795,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834143</v>
+        <v>834563</v>
       </c>
       <c r="R153" t="n">
-        <v>7348014</v>
+        <v>7347883</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646375</v>
+        <v>119646356</v>
       </c>
       <c r="B154" t="n">
         <v>91834</v>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834313</v>
+        <v>834132</v>
       </c>
       <c r="R154" t="n">
-        <v>7347844</v>
+        <v>7348055</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16991,10 +16991,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119646362</v>
+        <v>119646271</v>
       </c>
       <c r="B155" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17007,21 +17007,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>834150</v>
+        <v>834478</v>
       </c>
       <c r="R155" t="n">
-        <v>7347951</v>
+        <v>7347964</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17097,10 +17097,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119646335</v>
+        <v>119646350</v>
       </c>
       <c r="B156" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17109,25 +17109,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17137,10 +17137,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>834188</v>
+        <v>834516</v>
       </c>
       <c r="R156" t="n">
-        <v>7347887</v>
+        <v>7347965</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17203,10 +17203,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119646340</v>
+        <v>119646293</v>
       </c>
       <c r="B157" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17215,25 +17215,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>834444</v>
+        <v>834278</v>
       </c>
       <c r="R157" t="n">
-        <v>7347855</v>
+        <v>7347848</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17309,10 +17309,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119646371</v>
+        <v>119646305</v>
       </c>
       <c r="B158" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17325,21 +17325,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>834172</v>
+        <v>834295</v>
       </c>
       <c r="R158" t="n">
-        <v>7347857</v>
+        <v>7348050</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17415,10 +17415,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119646357</v>
+        <v>119646315</v>
       </c>
       <c r="B159" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17431,21 +17431,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17455,10 +17455,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>834118</v>
+        <v>834573</v>
       </c>
       <c r="R159" t="n">
-        <v>7348065</v>
+        <v>7347882</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17521,10 +17521,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119646326</v>
+        <v>119646320</v>
       </c>
       <c r="B160" t="n">
-        <v>91825</v>
+        <v>91832</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17537,21 +17537,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17561,10 +17561,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>834160</v>
+        <v>834545</v>
       </c>
       <c r="R160" t="n">
-        <v>7347971</v>
+        <v>7347891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17627,10 +17627,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119646262</v>
+        <v>119646354</v>
       </c>
       <c r="B161" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17643,21 +17643,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17667,10 +17667,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>834493</v>
+        <v>834171</v>
       </c>
       <c r="R161" t="n">
-        <v>7347964</v>
+        <v>7348044</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119646338</v>
+        <v>119646357</v>
       </c>
       <c r="B162" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17745,25 +17745,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>834346</v>
+        <v>834118</v>
       </c>
       <c r="R162" t="n">
-        <v>7347844</v>
+        <v>7348065</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17839,10 +17839,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119646293</v>
+        <v>119646316</v>
       </c>
       <c r="B163" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17851,25 +17851,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>834278</v>
+        <v>834547</v>
       </c>
       <c r="R163" t="n">
-        <v>7347848</v>
+        <v>7347865</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17945,10 +17945,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119646331</v>
+        <v>119646378</v>
       </c>
       <c r="B164" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17957,25 +17957,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17985,10 +17985,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>834170</v>
+        <v>834385</v>
       </c>
       <c r="R164" t="n">
-        <v>7348003</v>
+        <v>7347840</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18051,10 +18051,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119646310</v>
+        <v>119646273</v>
       </c>
       <c r="B165" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18067,21 +18067,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>834330</v>
+        <v>834143</v>
       </c>
       <c r="R165" t="n">
-        <v>7347843</v>
+        <v>7348014</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18157,10 +18157,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119646288</v>
+        <v>119646301</v>
       </c>
       <c r="B166" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18169,25 +18169,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18197,10 +18197,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>834457</v>
+        <v>834209</v>
       </c>
       <c r="R166" t="n">
-        <v>7347962</v>
+        <v>7347855</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18263,10 +18263,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119646348</v>
+        <v>119646277</v>
       </c>
       <c r="B167" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18279,21 +18279,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18303,10 +18303,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>834547</v>
+        <v>834168</v>
       </c>
       <c r="R167" t="n">
-        <v>7347954</v>
+        <v>7347981</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18369,10 +18369,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119646316</v>
+        <v>119646295</v>
       </c>
       <c r="B168" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18385,21 +18385,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18409,10 +18409,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>834547</v>
+        <v>834273</v>
       </c>
       <c r="R168" t="n">
-        <v>7347865</v>
+        <v>7348017</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18475,7 +18475,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119646334</v>
+        <v>119646345</v>
       </c>
       <c r="B169" t="n">
         <v>91840</v>
@@ -18515,10 +18515,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>834152</v>
+        <v>834499</v>
       </c>
       <c r="R169" t="n">
-        <v>7347973</v>
+        <v>7347865</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119646377</v>
+        <v>119646365</v>
       </c>
       <c r="B170" t="n">
         <v>91834</v>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>834324</v>
+        <v>834185</v>
       </c>
       <c r="R170" t="n">
-        <v>7347850</v>
+        <v>7347929</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18687,10 +18687,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119646290</v>
+        <v>119646403</v>
       </c>
       <c r="B171" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18703,21 +18703,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18727,10 +18727,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>834218</v>
+        <v>834495</v>
       </c>
       <c r="R171" t="n">
-        <v>7347851</v>
+        <v>7347844</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18793,7 +18793,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119646398</v>
+        <v>119646371</v>
       </c>
       <c r="B172" t="n">
         <v>91834</v>
@@ -18833,10 +18833,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>834549</v>
+        <v>834172</v>
       </c>
       <c r="R172" t="n">
-        <v>7347890</v>
+        <v>7347857</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18899,7 +18899,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119646403</v>
+        <v>119646367</v>
       </c>
       <c r="B173" t="n">
         <v>91834</v>
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>834495</v>
+        <v>834202</v>
       </c>
       <c r="R173" t="n">
-        <v>7347844</v>
+        <v>7347880</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19005,10 +19005,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119646266</v>
+        <v>119646401</v>
       </c>
       <c r="B174" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19017,25 +19017,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19045,10 +19045,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>834206</v>
+        <v>834496</v>
       </c>
       <c r="R174" t="n">
-        <v>7348051</v>
+        <v>7347857</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19111,10 +19111,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119646287</v>
+        <v>119646278</v>
       </c>
       <c r="B175" t="n">
-        <v>91828</v>
+        <v>91463</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19123,25 +19123,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>149</v>
+        <v>4745</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19151,10 +19151,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>834497</v>
+        <v>834144</v>
       </c>
       <c r="R175" t="n">
-        <v>7347854</v>
+        <v>7348044</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19217,10 +19217,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119646283</v>
+        <v>119646334</v>
       </c>
       <c r="B176" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19229,25 +19229,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19257,10 +19257,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>834500</v>
+        <v>834152</v>
       </c>
       <c r="R176" t="n">
-        <v>7347836</v>
+        <v>7347973</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19323,7 +19323,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119646345</v>
+        <v>119646328</v>
       </c>
       <c r="B177" t="n">
         <v>91840</v>
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>834499</v>
+        <v>834265</v>
       </c>
       <c r="R177" t="n">
-        <v>7347865</v>
+        <v>7348012</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19429,10 +19429,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119646282</v>
+        <v>119646289</v>
       </c>
       <c r="B178" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19441,25 +19441,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>834143</v>
+        <v>834286</v>
       </c>
       <c r="R178" t="n">
-        <v>7348013</v>
+        <v>7348064</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19535,10 +19535,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119646390</v>
+        <v>119646288</v>
       </c>
       <c r="B179" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19551,21 +19551,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>834574</v>
+        <v>834457</v>
       </c>
       <c r="R179" t="n">
-        <v>7347790</v>
+        <v>7347962</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119646374</v>
+        <v>119646337</v>
       </c>
       <c r="B180" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19653,25 +19653,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19681,10 +19681,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>834296</v>
+        <v>834262</v>
       </c>
       <c r="R180" t="n">
-        <v>7347848</v>
+        <v>7347868</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19747,10 +19747,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119646350</v>
+        <v>119646338</v>
       </c>
       <c r="B181" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19759,25 +19759,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19787,10 +19787,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>834516</v>
+        <v>834346</v>
       </c>
       <c r="R181" t="n">
-        <v>7347965</v>
+        <v>7347844</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19853,7 +19853,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119646322</v>
+        <v>119646310</v>
       </c>
       <c r="B182" t="n">
         <v>91832</v>
@@ -19893,10 +19893,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>834535</v>
+        <v>834330</v>
       </c>
       <c r="R182" t="n">
-        <v>7347891</v>
+        <v>7347843</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119646341</v>
+        <v>119646388</v>
       </c>
       <c r="B183" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19971,25 +19971,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>834561</v>
+        <v>834594</v>
       </c>
       <c r="R183" t="n">
-        <v>7347875</v>
+        <v>7347747</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20065,7 +20065,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119646384</v>
+        <v>119646348</v>
       </c>
       <c r="B184" t="n">
         <v>91834</v>
@@ -20105,10 +20105,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>834524</v>
+        <v>834547</v>
       </c>
       <c r="R184" t="n">
-        <v>7347806</v>
+        <v>7347954</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20171,10 +20171,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119646311</v>
+        <v>119646259</v>
       </c>
       <c r="B185" t="n">
-        <v>91832</v>
+        <v>91836</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20183,25 +20183,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4361</v>
+        <v>4363</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>834340</v>
+        <v>834292</v>
       </c>
       <c r="R185" t="n">
-        <v>7347841</v>
+        <v>7348037</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20277,7 +20277,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119646401</v>
+        <v>119646369</v>
       </c>
       <c r="B186" t="n">
         <v>91834</v>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>834496</v>
+        <v>834190</v>
       </c>
       <c r="R186" t="n">
-        <v>7347857</v>
+        <v>7347887</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20383,10 +20383,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119646300</v>
+        <v>119646353</v>
       </c>
       <c r="B187" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20395,25 +20395,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20423,10 +20423,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>834203</v>
+        <v>834186</v>
       </c>
       <c r="R187" t="n">
-        <v>7347849</v>
+        <v>7348079</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20489,10 +20489,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119646399</v>
+        <v>119646311</v>
       </c>
       <c r="B188" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20505,21 +20505,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>834512</v>
+        <v>834340</v>
       </c>
       <c r="R188" t="n">
-        <v>7347879</v>
+        <v>7347841</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20595,10 +20595,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119646295</v>
+        <v>119646380</v>
       </c>
       <c r="B189" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20611,21 +20611,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>834273</v>
+        <v>834492</v>
       </c>
       <c r="R189" t="n">
-        <v>7348017</v>
+        <v>7347839</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20701,7 +20701,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119646380</v>
+        <v>119646377</v>
       </c>
       <c r="B190" t="n">
         <v>91834</v>
@@ -20741,10 +20741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>834492</v>
+        <v>834324</v>
       </c>
       <c r="R190" t="n">
-        <v>7347839</v>
+        <v>7347850</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20807,10 +20807,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119646289</v>
+        <v>119646308</v>
       </c>
       <c r="B191" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20823,21 +20823,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>834286</v>
+        <v>834229</v>
       </c>
       <c r="R191" t="n">
-        <v>7348064</v>
+        <v>7347852</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20913,7 +20913,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119646267</v>
+        <v>119646269</v>
       </c>
       <c r="B192" t="n">
         <v>89275</v>
@@ -20953,10 +20953,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>834333</v>
+        <v>834531</v>
       </c>
       <c r="R192" t="n">
-        <v>7347848</v>
+        <v>7347887</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21019,10 +21019,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119646286</v>
+        <v>119646266</v>
       </c>
       <c r="B193" t="n">
-        <v>91828</v>
+        <v>89275</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21035,21 +21035,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>149</v>
+        <v>6286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21059,10 +21059,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>834520</v>
+        <v>834206</v>
       </c>
       <c r="R193" t="n">
-        <v>7347876</v>
+        <v>7348051</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21125,10 +21125,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119646263</v>
+        <v>119646300</v>
       </c>
       <c r="B194" t="n">
-        <v>86412</v>
+        <v>91852</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21137,25 +21137,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21165,10 +21165,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>834530</v>
+        <v>834203</v>
       </c>
       <c r="R194" t="n">
-        <v>7347888</v>
+        <v>7347849</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21231,7 +21231,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119646337</v>
+        <v>119646331</v>
       </c>
       <c r="B195" t="n">
         <v>91840</v>
@@ -21271,10 +21271,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>834262</v>
+        <v>834170</v>
       </c>
       <c r="R195" t="n">
-        <v>7347868</v>
+        <v>7348003</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21337,10 +21337,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646279</v>
+        <v>119646340</v>
       </c>
       <c r="B196" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834196</v>
+        <v>834444</v>
       </c>
       <c r="R196" t="n">
-        <v>7347922</v>
+        <v>7347855</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,7 +21443,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646365</v>
+        <v>119646372</v>
       </c>
       <c r="B197" t="n">
         <v>91834</v>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834185</v>
+        <v>834274</v>
       </c>
       <c r="R197" t="n">
-        <v>7347929</v>
+        <v>7347868</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646301</v>
+        <v>119646322</v>
       </c>
       <c r="B198" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21561,25 +21561,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834209</v>
+        <v>834535</v>
       </c>
       <c r="R198" t="n">
-        <v>7347855</v>
+        <v>7347891</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646308</v>
+        <v>119646282</v>
       </c>
       <c r="B199" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21667,25 +21667,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834229</v>
+        <v>834143</v>
       </c>
       <c r="R199" t="n">
-        <v>7347852</v>
+        <v>7348013</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646396</v>
+        <v>119646275</v>
       </c>
       <c r="B200" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834563</v>
+        <v>834351</v>
       </c>
       <c r="R200" t="n">
-        <v>7347883</v>
+        <v>7347847</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,10 +21867,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646372</v>
+        <v>119646290</v>
       </c>
       <c r="B201" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21883,21 +21883,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834274</v>
+        <v>834218</v>
       </c>
       <c r="R201" t="n">
-        <v>7347868</v>
+        <v>7347851</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21973,10 +21973,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119646259</v>
+        <v>119646399</v>
       </c>
       <c r="B202" t="n">
-        <v>91836</v>
+        <v>91834</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21985,25 +21985,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4363</v>
+        <v>4362</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22013,10 +22013,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>834292</v>
+        <v>834512</v>
       </c>
       <c r="R202" t="n">
-        <v>7348037</v>
+        <v>7347879</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22079,10 +22079,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119646315</v>
+        <v>119646287</v>
       </c>
       <c r="B203" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22091,25 +22091,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>834573</v>
+        <v>834497</v>
       </c>
       <c r="R203" t="n">
-        <v>7347882</v>
+        <v>7347854</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22185,10 +22185,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119646320</v>
+        <v>119646375</v>
       </c>
       <c r="B204" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22201,21 +22201,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22225,10 +22225,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>834545</v>
+        <v>834313</v>
       </c>
       <c r="R204" t="n">
-        <v>7347891</v>
+        <v>7347844</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119646261</v>
+        <v>119646390</v>
       </c>
       <c r="B205" t="n">
-        <v>79115</v>
+        <v>91834</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22307,21 +22307,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>834404</v>
+        <v>834574</v>
       </c>
       <c r="R205" t="n">
-        <v>7347982</v>
+        <v>7347790</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22397,10 +22397,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119646382</v>
+        <v>119646313</v>
       </c>
       <c r="B206" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22413,21 +22413,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22437,10 +22437,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>834509</v>
+        <v>834549</v>
       </c>
       <c r="R206" t="n">
-        <v>7347828</v>
+        <v>7347855</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22503,10 +22503,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119646277</v>
+        <v>119646303</v>
       </c>
       <c r="B207" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22519,21 +22519,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>834168</v>
+        <v>834528</v>
       </c>
       <c r="R207" t="n">
-        <v>7347981</v>
+        <v>7347966</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22609,10 +22609,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119646319</v>
+        <v>119646281</v>
       </c>
       <c r="B208" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22625,21 +22625,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22649,10 +22649,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>834543</v>
+        <v>834185</v>
       </c>
       <c r="R208" t="n">
-        <v>7347875</v>
+        <v>7347860</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22715,7 +22715,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119646367</v>
+        <v>119646385</v>
       </c>
       <c r="B209" t="n">
         <v>91834</v>
@@ -22755,10 +22755,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>834202</v>
+        <v>834545</v>
       </c>
       <c r="R209" t="n">
-        <v>7347880</v>
+        <v>7347772</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22821,10 +22821,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119646353</v>
+        <v>119646262</v>
       </c>
       <c r="B210" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22837,21 +22837,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>834186</v>
+        <v>834493</v>
       </c>
       <c r="R210" t="n">
-        <v>7348079</v>
+        <v>7347964</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22927,10 +22927,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119646268</v>
+        <v>119646263</v>
       </c>
       <c r="B211" t="n">
-        <v>89275</v>
+        <v>86412</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22939,25 +22939,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22967,10 +22967,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>834339</v>
+        <v>834530</v>
       </c>
       <c r="R211" t="n">
-        <v>7347842</v>
+        <v>7347888</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23033,10 +23033,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119646388</v>
+        <v>119646335</v>
       </c>
       <c r="B212" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23045,25 +23045,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>834594</v>
+        <v>834188</v>
       </c>
       <c r="R212" t="n">
-        <v>7347747</v>
+        <v>7347887</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23139,10 +23139,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119646360</v>
+        <v>119646330</v>
       </c>
       <c r="B213" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23151,25 +23151,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23179,10 +23179,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>834135</v>
+        <v>834475</v>
       </c>
       <c r="R213" t="n">
-        <v>7347955</v>
+        <v>7347966</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23245,10 +23245,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119646359</v>
+        <v>119646319</v>
       </c>
       <c r="B214" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23261,21 +23261,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23285,10 +23285,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>834110</v>
+        <v>834543</v>
       </c>
       <c r="R214" t="n">
-        <v>7348050</v>
+        <v>7347875</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -4370,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626557</v>
+        <v>119626521</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>834308</v>
+        <v>834220</v>
       </c>
       <c r="R36" t="n">
-        <v>7347903</v>
+        <v>7347890</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119626552</v>
+        <v>119626557</v>
       </c>
       <c r="B37" t="n">
         <v>91834</v>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>834354</v>
+        <v>834308</v>
       </c>
       <c r="R37" t="n">
-        <v>7347911</v>
+        <v>7347903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119626521</v>
+        <v>119626552</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>834220</v>
+        <v>834354</v>
       </c>
       <c r="R38" t="n">
-        <v>7347890</v>
+        <v>7347911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119626481</v>
+        <v>119626510</v>
       </c>
       <c r="B39" t="n">
-        <v>91856</v>
+        <v>57421</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>834455</v>
+        <v>834118</v>
       </c>
       <c r="R39" t="n">
-        <v>7347890</v>
+        <v>7347885</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119626537</v>
+        <v>119626456</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4810,21 +4810,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>834282</v>
+        <v>834204</v>
       </c>
       <c r="R40" t="n">
-        <v>7347983</v>
+        <v>7347855</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626442</v>
+        <v>119626481</v>
       </c>
       <c r="B41" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4916,21 +4916,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834160</v>
+        <v>834455</v>
       </c>
       <c r="R41" t="n">
-        <v>7347864</v>
+        <v>7347890</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626440</v>
+        <v>119626537</v>
       </c>
       <c r="B42" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834041</v>
+        <v>834282</v>
       </c>
       <c r="R42" t="n">
-        <v>7347837</v>
+        <v>7347983</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626456</v>
+        <v>119626442</v>
       </c>
       <c r="B43" t="n">
-        <v>91883</v>
+        <v>91463</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,21 +5128,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834204</v>
+        <v>834160</v>
       </c>
       <c r="R43" t="n">
-        <v>7347855</v>
+        <v>7347864</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119626510</v>
+        <v>119626440</v>
       </c>
       <c r="B44" t="n">
-        <v>57421</v>
+        <v>91463</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5230,25 +5230,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>834118</v>
+        <v>834041</v>
       </c>
       <c r="R44" t="n">
-        <v>7347885</v>
+        <v>7347837</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119626555</v>
+        <v>119626522</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7032,25 +7032,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>834442</v>
+        <v>834086</v>
       </c>
       <c r="R61" t="n">
-        <v>7347879</v>
+        <v>7347878</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119626522</v>
+        <v>119626433</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7138,25 +7138,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>834086</v>
+        <v>834169</v>
       </c>
       <c r="R62" t="n">
-        <v>7347878</v>
+        <v>7347940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119626433</v>
+        <v>119626439</v>
       </c>
       <c r="B63" t="n">
         <v>91463</v>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>834169</v>
+        <v>834018</v>
       </c>
       <c r="R63" t="n">
-        <v>7347940</v>
+        <v>7347852</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7338,10 +7338,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119626439</v>
+        <v>119626555</v>
       </c>
       <c r="B64" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>834018</v>
+        <v>834442</v>
       </c>
       <c r="R64" t="n">
-        <v>7347852</v>
+        <v>7347879</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8505,10 +8505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119626423</v>
+        <v>119626523</v>
       </c>
       <c r="B75" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8521,21 +8521,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>834319</v>
+        <v>834210</v>
       </c>
       <c r="R75" t="n">
-        <v>7347861</v>
+        <v>7347853</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8611,10 +8611,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119626460</v>
+        <v>119626532</v>
       </c>
       <c r="B76" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8623,25 +8623,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>834295</v>
+        <v>834192</v>
       </c>
       <c r="R76" t="n">
-        <v>7347970</v>
+        <v>7347888</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8717,10 +8717,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119626465</v>
+        <v>119626409</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8729,25 +8729,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>834267</v>
+        <v>834121</v>
       </c>
       <c r="R77" t="n">
-        <v>7347889</v>
+        <v>7348010</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8823,10 +8823,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119626409</v>
+        <v>119626520</v>
       </c>
       <c r="B78" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8835,25 +8835,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>834121</v>
+        <v>834276</v>
       </c>
       <c r="R78" t="n">
-        <v>7348010</v>
+        <v>7347908</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119626497</v>
+        <v>119626528</v>
       </c>
       <c r="B79" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8945,21 +8945,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8969,10 +8969,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>834121</v>
+        <v>834454</v>
       </c>
       <c r="R79" t="n">
-        <v>7347872</v>
+        <v>7347886</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,10 +9035,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119626520</v>
+        <v>119626556</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9047,25 +9047,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>834276</v>
+        <v>834453</v>
       </c>
       <c r="R80" t="n">
-        <v>7347908</v>
+        <v>7347884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9141,10 +9141,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119626528</v>
+        <v>119626501</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9153,25 +9153,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>834454</v>
+        <v>834207</v>
       </c>
       <c r="R81" t="n">
-        <v>7347886</v>
+        <v>7347898</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9247,10 +9247,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119626556</v>
+        <v>119626460</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9263,21 +9263,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>834453</v>
+        <v>834295</v>
       </c>
       <c r="R82" t="n">
-        <v>7347884</v>
+        <v>7347970</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119626523</v>
+        <v>119626465</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9365,25 +9365,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9393,10 +9393,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>834210</v>
+        <v>834267</v>
       </c>
       <c r="R83" t="n">
-        <v>7347853</v>
+        <v>7347889</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626532</v>
+        <v>119626423</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9475,21 +9475,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834192</v>
+        <v>834319</v>
       </c>
       <c r="R84" t="n">
-        <v>7347888</v>
+        <v>7347861</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626501</v>
+        <v>119626497</v>
       </c>
       <c r="B85" t="n">
-        <v>91832</v>
+        <v>96868</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9577,25 +9577,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834207</v>
+        <v>834121</v>
       </c>
       <c r="R85" t="n">
-        <v>7347898</v>
+        <v>7347872</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -13069,10 +13069,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626477</v>
+        <v>119626450</v>
       </c>
       <c r="B118" t="n">
-        <v>91856</v>
+        <v>91828</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13081,25 +13081,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13109,10 +13109,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834287</v>
+        <v>834442</v>
       </c>
       <c r="R118" t="n">
-        <v>7348033</v>
+        <v>7347873</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626536</v>
+        <v>119626477</v>
       </c>
       <c r="B119" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13191,21 +13191,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13215,10 +13215,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834190</v>
+        <v>834287</v>
       </c>
       <c r="R119" t="n">
-        <v>7347950</v>
+        <v>7348033</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13281,10 +13281,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626450</v>
+        <v>119626536</v>
       </c>
       <c r="B120" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13293,25 +13293,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834442</v>
+        <v>834190</v>
       </c>
       <c r="R120" t="n">
-        <v>7347873</v>
+        <v>7347950</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13917,10 +13917,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626499</v>
+        <v>119626544</v>
       </c>
       <c r="B126" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13933,21 +13933,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834153</v>
+        <v>834331</v>
       </c>
       <c r="R126" t="n">
-        <v>7347952</v>
+        <v>7347868</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626544</v>
+        <v>119626499</v>
       </c>
       <c r="B127" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14039,21 +14039,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834331</v>
+        <v>834153</v>
       </c>
       <c r="R127" t="n">
-        <v>7347868</v>
+        <v>7347952</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119646394</v>
+        <v>119646296</v>
       </c>
       <c r="B129" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14251,21 +14251,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>834555</v>
+        <v>834546</v>
       </c>
       <c r="R129" t="n">
-        <v>7347854</v>
+        <v>7347860</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,10 +14341,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119646276</v>
+        <v>119646394</v>
       </c>
       <c r="B130" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14357,21 +14357,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14381,10 +14381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>834519</v>
+        <v>834555</v>
       </c>
       <c r="R130" t="n">
-        <v>7347875</v>
+        <v>7347854</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14553,10 +14553,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119646296</v>
+        <v>119646362</v>
       </c>
       <c r="B132" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14569,21 +14569,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>834546</v>
+        <v>834150</v>
       </c>
       <c r="R132" t="n">
-        <v>7347860</v>
+        <v>7347951</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14659,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119646362</v>
+        <v>119646276</v>
       </c>
       <c r="B133" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14675,21 +14675,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>834150</v>
+        <v>834519</v>
       </c>
       <c r="R133" t="n">
-        <v>7347951</v>
+        <v>7347875</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646268</v>
+        <v>119646271</v>
       </c>
       <c r="B151" t="n">
-        <v>89275</v>
+        <v>91826</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16579,25 +16579,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6286</v>
+        <v>3100</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834339</v>
+        <v>834478</v>
       </c>
       <c r="R151" t="n">
-        <v>7347842</v>
+        <v>7347964</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646341</v>
+        <v>119646268</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834561</v>
+        <v>834339</v>
       </c>
       <c r="R152" t="n">
-        <v>7347875</v>
+        <v>7347842</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646396</v>
+        <v>119646341</v>
       </c>
       <c r="B153" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834563</v>
+        <v>834561</v>
       </c>
       <c r="R153" t="n">
-        <v>7347883</v>
+        <v>7347875</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646356</v>
+        <v>119646396</v>
       </c>
       <c r="B154" t="n">
         <v>91834</v>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834132</v>
+        <v>834563</v>
       </c>
       <c r="R154" t="n">
-        <v>7348055</v>
+        <v>7347883</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16991,10 +16991,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119646271</v>
+        <v>119646356</v>
       </c>
       <c r="B155" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17007,21 +17007,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>834478</v>
+        <v>834132</v>
       </c>
       <c r="R155" t="n">
-        <v>7347964</v>
+        <v>7348055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -21231,10 +21231,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119646331</v>
+        <v>119646282</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21243,25 +21243,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21271,10 +21271,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>834170</v>
+        <v>834143</v>
       </c>
       <c r="R195" t="n">
-        <v>7348003</v>
+        <v>7348013</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21337,7 +21337,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646340</v>
+        <v>119646331</v>
       </c>
       <c r="B196" t="n">
         <v>91840</v>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834444</v>
+        <v>834170</v>
       </c>
       <c r="R196" t="n">
-        <v>7347855</v>
+        <v>7348003</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,10 +21443,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646372</v>
+        <v>119646340</v>
       </c>
       <c r="B197" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21455,25 +21455,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834274</v>
+        <v>834444</v>
       </c>
       <c r="R197" t="n">
-        <v>7347868</v>
+        <v>7347855</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646322</v>
+        <v>119646275</v>
       </c>
       <c r="B198" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21565,21 +21565,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834535</v>
+        <v>834351</v>
       </c>
       <c r="R198" t="n">
-        <v>7347891</v>
+        <v>7347847</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646282</v>
+        <v>119646290</v>
       </c>
       <c r="B199" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21667,25 +21667,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834143</v>
+        <v>834218</v>
       </c>
       <c r="R199" t="n">
-        <v>7348013</v>
+        <v>7347851</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646275</v>
+        <v>119646372</v>
       </c>
       <c r="B200" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834351</v>
+        <v>834274</v>
       </c>
       <c r="R200" t="n">
-        <v>7347847</v>
+        <v>7347868</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,10 +21867,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646290</v>
+        <v>119646322</v>
       </c>
       <c r="B201" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21883,21 +21883,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834218</v>
+        <v>834535</v>
       </c>
       <c r="R201" t="n">
-        <v>7347851</v>
+        <v>7347891</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22397,10 +22397,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119646313</v>
+        <v>119646385</v>
       </c>
       <c r="B206" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22413,21 +22413,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22437,10 +22437,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>834549</v>
+        <v>834545</v>
       </c>
       <c r="R206" t="n">
-        <v>7347855</v>
+        <v>7347772</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22503,7 +22503,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119646303</v>
+        <v>119646313</v>
       </c>
       <c r="B207" t="n">
         <v>91832</v>
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>834528</v>
+        <v>834549</v>
       </c>
       <c r="R207" t="n">
-        <v>7347966</v>
+        <v>7347855</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22609,10 +22609,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119646281</v>
+        <v>119646303</v>
       </c>
       <c r="B208" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22625,21 +22625,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22649,10 +22649,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>834185</v>
+        <v>834528</v>
       </c>
       <c r="R208" t="n">
-        <v>7347860</v>
+        <v>7347966</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22715,10 +22715,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119646385</v>
+        <v>119646281</v>
       </c>
       <c r="B209" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22731,21 +22731,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22755,10 +22755,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>834545</v>
+        <v>834185</v>
       </c>
       <c r="R209" t="n">
-        <v>7347772</v>
+        <v>7347860</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119626479</v>
+        <v>119626448</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>91828</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3746,25 +3746,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>834177</v>
+        <v>834184</v>
       </c>
       <c r="R30" t="n">
-        <v>7347881</v>
+        <v>7347877</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119626517</v>
+        <v>119626515</v>
       </c>
       <c r="B31" t="n">
         <v>91825</v>
@@ -3883,7 +3883,7 @@
         <v>834243</v>
       </c>
       <c r="R31" t="n">
-        <v>7347862</v>
+        <v>7348008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119626436</v>
+        <v>119626432</v>
       </c>
       <c r="B32" t="n">
-        <v>91463</v>
+        <v>91826</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>834236</v>
+        <v>834167</v>
       </c>
       <c r="R32" t="n">
-        <v>7347993</v>
+        <v>7348024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119626444</v>
+        <v>119626520</v>
       </c>
       <c r="B33" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>834154</v>
+        <v>834276</v>
       </c>
       <c r="R33" t="n">
-        <v>7347884</v>
+        <v>7347908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119626545</v>
+        <v>119626505</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>834320</v>
+        <v>834329</v>
       </c>
       <c r="R34" t="n">
-        <v>7347855</v>
+        <v>7347858</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119626526</v>
+        <v>119626540</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>834382</v>
+        <v>834166</v>
       </c>
       <c r="R35" t="n">
-        <v>7347924</v>
+        <v>7347884</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626521</v>
+        <v>119626477</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>834220</v>
+        <v>834287</v>
       </c>
       <c r="R36" t="n">
-        <v>7347890</v>
+        <v>7348033</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119626557</v>
+        <v>119626522</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>834308</v>
+        <v>834086</v>
       </c>
       <c r="R37" t="n">
-        <v>7347903</v>
+        <v>7347878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119626552</v>
+        <v>119626483</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>834354</v>
+        <v>834080</v>
       </c>
       <c r="R38" t="n">
-        <v>7347911</v>
+        <v>7347837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119626510</v>
+        <v>119626534</v>
       </c>
       <c r="B39" t="n">
-        <v>57421</v>
+        <v>91834</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>834118</v>
+        <v>834168</v>
       </c>
       <c r="R39" t="n">
-        <v>7347885</v>
+        <v>7347939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119626456</v>
+        <v>119626440</v>
       </c>
       <c r="B40" t="n">
-        <v>91883</v>
+        <v>91463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4810,21 +4810,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>4745</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>834204</v>
+        <v>834041</v>
       </c>
       <c r="R40" t="n">
-        <v>7347855</v>
+        <v>7347837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626481</v>
+        <v>119626411</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,25 +4912,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834455</v>
+        <v>834141</v>
       </c>
       <c r="R41" t="n">
-        <v>7347890</v>
+        <v>7348021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626537</v>
+        <v>119626498</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,25 +5018,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834282</v>
+        <v>834053</v>
       </c>
       <c r="R42" t="n">
-        <v>7347983</v>
+        <v>7347834</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626442</v>
+        <v>119626497</v>
       </c>
       <c r="B43" t="n">
-        <v>91463</v>
+        <v>96868</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5124,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834160</v>
+        <v>834121</v>
       </c>
       <c r="R43" t="n">
-        <v>7347864</v>
+        <v>7347872</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119626440</v>
+        <v>119626406</v>
       </c>
       <c r="B44" t="n">
-        <v>91463</v>
+        <v>89633</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>834041</v>
+        <v>834121</v>
       </c>
       <c r="R44" t="n">
-        <v>7347837</v>
+        <v>7348010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,12 +5296,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5324,10 +5330,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119626405</v>
+        <v>119626506</v>
       </c>
       <c r="B45" t="n">
-        <v>86412</v>
+        <v>91832</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5340,21 +5346,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5364,10 +5370,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>834216</v>
+        <v>834322</v>
       </c>
       <c r="R45" t="n">
-        <v>7347860</v>
+        <v>7347857</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5430,10 +5436,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119626473</v>
+        <v>119626544</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5446,21 +5452,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5470,13 +5476,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>834384</v>
+        <v>834331</v>
       </c>
       <c r="R46" t="n">
-        <v>7347916</v>
+        <v>7347868</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5536,10 +5542,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119626535</v>
+        <v>119626465</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,21 +5558,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5576,10 +5582,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>834187</v>
+        <v>834267</v>
       </c>
       <c r="R47" t="n">
-        <v>7347944</v>
+        <v>7347889</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,10 +5648,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119626504</v>
+        <v>119626416</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5654,25 +5660,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5682,10 +5688,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>834309</v>
+        <v>834434</v>
       </c>
       <c r="R48" t="n">
-        <v>7347875</v>
+        <v>7347883</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,10 +5754,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119626533</v>
+        <v>119626528</v>
       </c>
       <c r="B49" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5760,25 +5766,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5794,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>834153</v>
+        <v>834454</v>
       </c>
       <c r="R49" t="n">
-        <v>7347932</v>
+        <v>7347886</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5854,10 +5860,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626437</v>
+        <v>119626525</v>
       </c>
       <c r="B50" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5866,25 +5872,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5900,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>834288</v>
+        <v>834253</v>
       </c>
       <c r="R50" t="n">
-        <v>7347985</v>
+        <v>7347885</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5960,10 +5966,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626507</v>
+        <v>119626450</v>
       </c>
       <c r="B51" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5972,25 +5978,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6000,10 +6006,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>834277</v>
+        <v>834442</v>
       </c>
       <c r="R51" t="n">
-        <v>7347848</v>
+        <v>7347873</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6066,10 +6072,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119626503</v>
+        <v>119626431</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6082,21 +6088,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6106,10 +6112,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>834159</v>
+        <v>834318</v>
       </c>
       <c r="R52" t="n">
-        <v>7347856</v>
+        <v>7347852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6172,10 +6178,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119626408</v>
+        <v>119626554</v>
       </c>
       <c r="B53" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6188,21 +6194,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6212,10 +6218,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>834123</v>
+        <v>834433</v>
       </c>
       <c r="R53" t="n">
-        <v>7347975</v>
+        <v>7347878</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119626416</v>
+        <v>119626547</v>
       </c>
       <c r="B54" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6290,25 +6296,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6318,10 +6324,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>834434</v>
+        <v>834115</v>
       </c>
       <c r="R54" t="n">
-        <v>7347883</v>
+        <v>7347875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6384,10 +6390,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119626463</v>
+        <v>119626499</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6400,21 +6406,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6430,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>834272</v>
+        <v>834153</v>
       </c>
       <c r="R55" t="n">
-        <v>7347885</v>
+        <v>7347952</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6490,10 +6496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119626452</v>
+        <v>119626537</v>
       </c>
       <c r="B56" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6502,25 +6508,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6530,10 +6536,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>834454</v>
+        <v>834282</v>
       </c>
       <c r="R56" t="n">
-        <v>7347892</v>
+        <v>7347983</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,10 +6602,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119626505</v>
+        <v>119626543</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6612,21 +6618,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6636,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>834329</v>
+        <v>834275</v>
       </c>
       <c r="R57" t="n">
-        <v>7347858</v>
+        <v>7347856</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6702,10 +6708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119626551</v>
+        <v>119626418</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6714,25 +6720,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6742,10 +6748,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>834249</v>
+        <v>834185</v>
       </c>
       <c r="R58" t="n">
-        <v>7347880</v>
+        <v>7347878</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6808,10 +6814,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119626539</v>
+        <v>119626510</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>57421</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6820,25 +6826,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6854,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>834204</v>
+        <v>834118</v>
       </c>
       <c r="R59" t="n">
-        <v>7347896</v>
+        <v>7347885</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6914,10 +6920,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119626446</v>
+        <v>119626501</v>
       </c>
       <c r="B60" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6930,21 +6936,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6954,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>834267</v>
+        <v>834207</v>
       </c>
       <c r="R60" t="n">
-        <v>7347889</v>
+        <v>7347898</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7020,10 +7026,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119626522</v>
+        <v>119626409</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7032,25 +7038,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,10 +7066,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>834086</v>
+        <v>834121</v>
       </c>
       <c r="R61" t="n">
-        <v>7347878</v>
+        <v>7348010</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7126,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119626433</v>
+        <v>119626548</v>
       </c>
       <c r="B62" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7142,21 +7148,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7166,10 +7172,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>834169</v>
+        <v>834151</v>
       </c>
       <c r="R62" t="n">
-        <v>7347940</v>
+        <v>7347881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7232,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119626439</v>
+        <v>119626523</v>
       </c>
       <c r="B63" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7244,25 +7250,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>834018</v>
+        <v>834210</v>
       </c>
       <c r="R63" t="n">
-        <v>7347852</v>
+        <v>7347853</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7338,10 +7344,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119626555</v>
+        <v>119626519</v>
       </c>
       <c r="B64" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7350,25 +7356,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7378,10 +7384,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>834442</v>
+        <v>834148</v>
       </c>
       <c r="R64" t="n">
-        <v>7347879</v>
+        <v>7347973</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7444,7 +7450,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119626500</v>
+        <v>119626508</v>
       </c>
       <c r="B65" t="n">
         <v>91832</v>
@@ -7484,10 +7490,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>834227</v>
+        <v>834325</v>
       </c>
       <c r="R65" t="n">
-        <v>7347892</v>
+        <v>7347870</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7550,10 +7556,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119626531</v>
+        <v>119626460</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7562,25 +7568,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7590,10 +7596,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>834282</v>
+        <v>834295</v>
       </c>
       <c r="R66" t="n">
-        <v>7347898</v>
+        <v>7347970</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7656,10 +7662,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119626483</v>
+        <v>119626436</v>
       </c>
       <c r="B67" t="n">
-        <v>91852</v>
+        <v>91463</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7668,25 +7674,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7696,10 +7702,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>834080</v>
+        <v>834236</v>
       </c>
       <c r="R67" t="n">
-        <v>7347837</v>
+        <v>7347993</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7762,10 +7768,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119626525</v>
+        <v>119626420</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7774,25 +7780,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7802,10 +7808,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>834253</v>
+        <v>834252</v>
       </c>
       <c r="R68" t="n">
-        <v>7347885</v>
+        <v>7347884</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7868,10 +7874,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119626404</v>
+        <v>119626423</v>
       </c>
       <c r="B69" t="n">
-        <v>86412</v>
+        <v>56522</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7880,25 +7886,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3690</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7908,10 +7914,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>834430</v>
+        <v>834319</v>
       </c>
       <c r="R69" t="n">
-        <v>7347886</v>
+        <v>7347861</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7952,7 +7958,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7975,10 +7980,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119626453</v>
+        <v>119626404</v>
       </c>
       <c r="B70" t="n">
-        <v>91463</v>
+        <v>86412</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7991,21 +7996,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8015,10 +8020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>834124</v>
+        <v>834430</v>
       </c>
       <c r="R70" t="n">
-        <v>7347874</v>
+        <v>7347886</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8059,6 +8064,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8081,10 +8087,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119626495</v>
+        <v>119626542</v>
       </c>
       <c r="B71" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8093,25 +8099,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8121,10 +8127,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>834287</v>
+        <v>834148</v>
       </c>
       <c r="R71" t="n">
-        <v>7347954</v>
+        <v>7347880</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8187,10 +8193,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119626516</v>
+        <v>119626539</v>
       </c>
       <c r="B72" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8203,21 +8209,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8227,10 +8233,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>834083</v>
+        <v>834204</v>
       </c>
       <c r="R72" t="n">
-        <v>7347877</v>
+        <v>7347896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8293,10 +8299,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119626542</v>
+        <v>119626521</v>
       </c>
       <c r="B73" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8305,25 +8311,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8333,10 +8339,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>834148</v>
+        <v>834220</v>
       </c>
       <c r="R73" t="n">
-        <v>7347880</v>
+        <v>7347890</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8399,10 +8405,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119626420</v>
+        <v>119626421</v>
       </c>
       <c r="B74" t="n">
-        <v>89275</v>
+        <v>56522</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8411,25 +8417,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6286</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8439,10 +8445,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>834252</v>
+        <v>834160</v>
       </c>
       <c r="R74" t="n">
-        <v>7347884</v>
+        <v>7347850</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8505,10 +8511,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119626523</v>
+        <v>119626455</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8517,25 +8523,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8545,10 +8551,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>834210</v>
+        <v>834288</v>
       </c>
       <c r="R75" t="n">
-        <v>7347853</v>
+        <v>7347877</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8611,10 +8617,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119626532</v>
+        <v>119626467</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8623,25 +8629,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8651,10 +8657,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>834192</v>
+        <v>834310</v>
       </c>
       <c r="R76" t="n">
-        <v>7347888</v>
+        <v>7347899</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8717,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119626409</v>
+        <v>119626557</v>
       </c>
       <c r="B77" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8729,25 +8735,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8757,10 +8763,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>834121</v>
+        <v>834308</v>
       </c>
       <c r="R77" t="n">
-        <v>7348010</v>
+        <v>7347903</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8823,10 +8829,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119626520</v>
+        <v>119626538</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8835,25 +8841,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8863,10 +8869,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>834276</v>
+        <v>834292</v>
       </c>
       <c r="R78" t="n">
-        <v>7347908</v>
+        <v>7347968</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8929,10 +8935,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119626528</v>
+        <v>119626545</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8941,25 +8947,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8969,10 +8975,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>834454</v>
+        <v>834320</v>
       </c>
       <c r="R79" t="n">
-        <v>7347886</v>
+        <v>7347855</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9035,10 +9041,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119626556</v>
+        <v>119626531</v>
       </c>
       <c r="B80" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9047,25 +9053,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9075,10 +9081,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>834453</v>
+        <v>834282</v>
       </c>
       <c r="R80" t="n">
-        <v>7347884</v>
+        <v>7347898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9141,10 +9147,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119626501</v>
+        <v>119626446</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9157,21 +9163,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9181,10 +9187,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>834207</v>
+        <v>834267</v>
       </c>
       <c r="R81" t="n">
-        <v>7347898</v>
+        <v>7347889</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9247,10 +9253,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119626460</v>
+        <v>119626433</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9263,21 +9269,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9287,10 +9293,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>834295</v>
+        <v>834169</v>
       </c>
       <c r="R82" t="n">
-        <v>7347970</v>
+        <v>7347940</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9353,10 +9359,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119626465</v>
+        <v>119626414</v>
       </c>
       <c r="B83" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9365,25 +9371,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9393,10 +9399,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>834267</v>
+        <v>834252</v>
       </c>
       <c r="R83" t="n">
-        <v>7347889</v>
+        <v>7347893</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9459,10 +9465,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626423</v>
+        <v>119626481</v>
       </c>
       <c r="B84" t="n">
-        <v>56522</v>
+        <v>91856</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9471,25 +9477,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9499,10 +9505,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834319</v>
+        <v>834455</v>
       </c>
       <c r="R84" t="n">
-        <v>7347861</v>
+        <v>7347890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,10 +9571,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626497</v>
+        <v>119626551</v>
       </c>
       <c r="B85" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9577,25 +9583,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9605,10 +9611,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834121</v>
+        <v>834249</v>
       </c>
       <c r="R85" t="n">
-        <v>7347872</v>
+        <v>7347880</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9671,10 +9677,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119626519</v>
+        <v>119626535</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9683,25 +9689,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9711,10 +9717,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>834148</v>
+        <v>834187</v>
       </c>
       <c r="R86" t="n">
-        <v>7347973</v>
+        <v>7347944</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9777,10 +9783,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119626553</v>
+        <v>119626437</v>
       </c>
       <c r="B87" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9793,21 +9799,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9817,10 +9823,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>834388</v>
+        <v>834288</v>
       </c>
       <c r="R87" t="n">
-        <v>7347909</v>
+        <v>7347985</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9883,10 +9889,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119626540</v>
+        <v>119626473</v>
       </c>
       <c r="B88" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9899,21 +9905,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9923,13 +9929,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>834166</v>
+        <v>834384</v>
       </c>
       <c r="R88" t="n">
-        <v>7347884</v>
+        <v>7347916</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9989,10 +9995,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119626527</v>
+        <v>119626550</v>
       </c>
       <c r="B89" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10001,25 +10007,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10029,10 +10035,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>834435</v>
+        <v>834212</v>
       </c>
       <c r="R89" t="n">
-        <v>7347869</v>
+        <v>7347855</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10095,10 +10101,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119626434</v>
+        <v>119626533</v>
       </c>
       <c r="B90" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10111,21 +10117,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10141,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>834189</v>
+        <v>834153</v>
       </c>
       <c r="R90" t="n">
-        <v>7347957</v>
+        <v>7347932</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10201,7 +10207,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119626455</v>
+        <v>119626444</v>
       </c>
       <c r="B91" t="n">
         <v>91463</v>
@@ -10241,10 +10247,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>834288</v>
+        <v>834154</v>
       </c>
       <c r="R91" t="n">
-        <v>7347877</v>
+        <v>7347884</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10307,10 +10313,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119626430</v>
+        <v>119626408</v>
       </c>
       <c r="B92" t="n">
-        <v>91826</v>
+        <v>89633</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10323,21 +10329,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10347,10 +10353,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>834295</v>
+        <v>834123</v>
       </c>
       <c r="R92" t="n">
-        <v>7348032</v>
+        <v>7347975</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10413,10 +10419,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119626428</v>
+        <v>119626405</v>
       </c>
       <c r="B93" t="n">
-        <v>91826</v>
+        <v>86412</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10429,21 +10435,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3100</v>
+        <v>3690</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10453,10 +10459,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>834149</v>
+        <v>834216</v>
       </c>
       <c r="R93" t="n">
-        <v>7347970</v>
+        <v>7347860</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10519,10 +10525,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119626475</v>
+        <v>119626503</v>
       </c>
       <c r="B94" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10535,21 +10541,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10559,10 +10565,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>834243</v>
+        <v>834159</v>
       </c>
       <c r="R94" t="n">
-        <v>7348008</v>
+        <v>7347856</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10625,10 +10631,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119626554</v>
+        <v>119626434</v>
       </c>
       <c r="B95" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10641,21 +10647,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10665,10 +10671,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>834433</v>
+        <v>834189</v>
       </c>
       <c r="R95" t="n">
-        <v>7347878</v>
+        <v>7347957</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,10 +10737,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119626550</v>
+        <v>119626517</v>
       </c>
       <c r="B96" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10747,21 +10753,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10771,10 +10777,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>834212</v>
+        <v>834243</v>
       </c>
       <c r="R96" t="n">
-        <v>7347855</v>
+        <v>7347862</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10837,10 +10843,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119626534</v>
+        <v>119626507</v>
       </c>
       <c r="B97" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10853,21 +10859,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10877,10 +10883,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>834168</v>
+        <v>834277</v>
       </c>
       <c r="R97" t="n">
-        <v>7347939</v>
+        <v>7347848</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10943,7 +10949,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119626549</v>
+        <v>119626556</v>
       </c>
       <c r="B98" t="n">
         <v>91834</v>
@@ -10983,10 +10989,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>834196</v>
+        <v>834453</v>
       </c>
       <c r="R98" t="n">
-        <v>7347874</v>
+        <v>7347884</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11049,10 +11055,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119626432</v>
+        <v>119626509</v>
       </c>
       <c r="B99" t="n">
-        <v>91826</v>
+        <v>91863</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11065,21 +11071,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11089,10 +11095,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>834167</v>
+        <v>834244</v>
       </c>
       <c r="R99" t="n">
-        <v>7348024</v>
+        <v>7347889</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11155,10 +11161,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119626509</v>
+        <v>119626462</v>
       </c>
       <c r="B100" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11171,21 +11177,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11195,10 +11201,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>834244</v>
+        <v>834252</v>
       </c>
       <c r="R100" t="n">
-        <v>7347889</v>
+        <v>7347832</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11261,10 +11267,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119626412</v>
+        <v>119626529</v>
       </c>
       <c r="B101" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11273,25 +11279,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11301,10 +11307,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>834267</v>
+        <v>834467</v>
       </c>
       <c r="R101" t="n">
-        <v>7347984</v>
+        <v>7347889</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11367,10 +11373,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119626458</v>
+        <v>119626527</v>
       </c>
       <c r="B102" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11379,25 +11385,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11407,10 +11413,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>834214</v>
+        <v>834435</v>
       </c>
       <c r="R102" t="n">
-        <v>7347853</v>
+        <v>7347869</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11473,10 +11479,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119626462</v>
+        <v>119626452</v>
       </c>
       <c r="B103" t="n">
-        <v>91884</v>
+        <v>91828</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11485,25 +11491,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11513,10 +11519,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>834252</v>
+        <v>834454</v>
       </c>
       <c r="R103" t="n">
-        <v>7347832</v>
+        <v>7347892</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11579,10 +11585,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119626529</v>
+        <v>119626458</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11591,25 +11597,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11619,10 +11625,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>834467</v>
+        <v>834214</v>
       </c>
       <c r="R104" t="n">
-        <v>7347889</v>
+        <v>7347853</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11685,10 +11691,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119626411</v>
+        <v>119626463</v>
       </c>
       <c r="B105" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11697,25 +11703,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11725,10 +11731,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>834141</v>
+        <v>834272</v>
       </c>
       <c r="R105" t="n">
-        <v>7348021</v>
+        <v>7347885</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11791,10 +11797,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119626414</v>
+        <v>119626443</v>
       </c>
       <c r="B106" t="n">
-        <v>89275</v>
+        <v>91463</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11803,25 +11809,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11831,10 +11837,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>834252</v>
+        <v>834325</v>
       </c>
       <c r="R106" t="n">
-        <v>7347893</v>
+        <v>7347874</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,10 +11903,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626448</v>
+        <v>119626500</v>
       </c>
       <c r="B107" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11909,25 +11915,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11937,10 +11943,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>834184</v>
+        <v>834227</v>
       </c>
       <c r="R107" t="n">
-        <v>7347877</v>
+        <v>7347892</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12003,10 +12009,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626406</v>
+        <v>119626532</v>
       </c>
       <c r="B108" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12015,25 +12021,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12043,10 +12049,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>834121</v>
+        <v>834192</v>
       </c>
       <c r="R108" t="n">
-        <v>7348010</v>
+        <v>7347888</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12081,18 +12087,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119626543</v>
+        <v>119626475</v>
       </c>
       <c r="B109" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12131,21 +12131,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12155,10 +12155,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>834275</v>
+        <v>834243</v>
       </c>
       <c r="R109" t="n">
-        <v>7347856</v>
+        <v>7348008</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12221,10 +12221,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119626486</v>
+        <v>119626428</v>
       </c>
       <c r="B110" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12233,25 +12233,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12261,10 +12261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>834186</v>
+        <v>834149</v>
       </c>
       <c r="R110" t="n">
-        <v>7347942</v>
+        <v>7347970</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119626515</v>
+        <v>119626549</v>
       </c>
       <c r="B111" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12343,21 +12343,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>834243</v>
+        <v>834196</v>
       </c>
       <c r="R111" t="n">
-        <v>7348008</v>
+        <v>7347874</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12433,10 +12433,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119626548</v>
+        <v>119626430</v>
       </c>
       <c r="B112" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>834151</v>
+        <v>834295</v>
       </c>
       <c r="R112" t="n">
-        <v>7347881</v>
+        <v>7348032</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119626538</v>
+        <v>119626530</v>
       </c>
       <c r="B113" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12551,25 +12551,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>834292</v>
+        <v>834170</v>
       </c>
       <c r="R113" t="n">
-        <v>7347968</v>
+        <v>7347895</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12645,10 +12645,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119626530</v>
+        <v>119626552</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12657,25 +12657,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12685,10 +12685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>834170</v>
+        <v>834354</v>
       </c>
       <c r="R114" t="n">
-        <v>7347895</v>
+        <v>7347911</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119626508</v>
+        <v>119626412</v>
       </c>
       <c r="B115" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12763,25 +12763,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>834325</v>
+        <v>834267</v>
       </c>
       <c r="R115" t="n">
-        <v>7347870</v>
+        <v>7347984</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119626547</v>
+        <v>119626453</v>
       </c>
       <c r="B116" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12873,21 +12873,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12897,10 +12897,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>834115</v>
+        <v>834124</v>
       </c>
       <c r="R116" t="n">
-        <v>7347875</v>
+        <v>7347874</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12963,10 +12963,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119626421</v>
+        <v>119626439</v>
       </c>
       <c r="B117" t="n">
-        <v>56522</v>
+        <v>91463</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12975,25 +12975,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>834160</v>
+        <v>834018</v>
       </c>
       <c r="R117" t="n">
-        <v>7347850</v>
+        <v>7347852</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13069,10 +13069,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626450</v>
+        <v>119626456</v>
       </c>
       <c r="B118" t="n">
-        <v>91828</v>
+        <v>91883</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13081,25 +13081,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13109,10 +13109,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834442</v>
+        <v>834204</v>
       </c>
       <c r="R118" t="n">
-        <v>7347873</v>
+        <v>7347855</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626477</v>
+        <v>119626516</v>
       </c>
       <c r="B119" t="n">
-        <v>91856</v>
+        <v>91825</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13191,21 +13191,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2059</v>
+        <v>1968</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13215,10 +13215,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834287</v>
+        <v>834083</v>
       </c>
       <c r="R119" t="n">
-        <v>7348033</v>
+        <v>7347877</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626536</v>
+        <v>119626553</v>
       </c>
       <c r="B120" t="n">
         <v>91834</v>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834190</v>
+        <v>834388</v>
       </c>
       <c r="R120" t="n">
-        <v>7347950</v>
+        <v>7347909</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119626506</v>
+        <v>119626526</v>
       </c>
       <c r="B121" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13399,25 +13399,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>834322</v>
+        <v>834382</v>
       </c>
       <c r="R121" t="n">
-        <v>7347857</v>
+        <v>7347924</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119626418</v>
+        <v>119626479</v>
       </c>
       <c r="B122" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13505,25 +13505,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>834185</v>
+        <v>834177</v>
       </c>
       <c r="R122" t="n">
-        <v>7347878</v>
+        <v>7347881</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119626467</v>
+        <v>119626504</v>
       </c>
       <c r="B123" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13615,21 +13615,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13639,10 +13639,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>834310</v>
+        <v>834309</v>
       </c>
       <c r="R123" t="n">
-        <v>7347899</v>
+        <v>7347875</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119626443</v>
+        <v>119626536</v>
       </c>
       <c r="B124" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13721,21 +13721,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>834325</v>
+        <v>834190</v>
       </c>
       <c r="R124" t="n">
-        <v>7347874</v>
+        <v>7347950</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119626431</v>
+        <v>119626486</v>
       </c>
       <c r="B125" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13823,25 +13823,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>834318</v>
+        <v>834186</v>
       </c>
       <c r="R125" t="n">
-        <v>7347852</v>
+        <v>7347942</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13917,7 +13917,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626544</v>
+        <v>119626555</v>
       </c>
       <c r="B126" t="n">
         <v>91834</v>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834331</v>
+        <v>834442</v>
       </c>
       <c r="R126" t="n">
-        <v>7347868</v>
+        <v>7347879</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626499</v>
+        <v>119626442</v>
       </c>
       <c r="B127" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14039,21 +14039,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834153</v>
+        <v>834160</v>
       </c>
       <c r="R127" t="n">
-        <v>7347952</v>
+        <v>7347864</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14129,7 +14129,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119626498</v>
+        <v>119626495</v>
       </c>
       <c r="B128" t="n">
         <v>96868</v>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>834053</v>
+        <v>834287</v>
       </c>
       <c r="R128" t="n">
-        <v>7347834</v>
+        <v>7347954</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119646296</v>
+        <v>119646276</v>
       </c>
       <c r="B129" t="n">
-        <v>91856</v>
+        <v>91826</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14251,21 +14251,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>834546</v>
+        <v>834519</v>
       </c>
       <c r="R129" t="n">
-        <v>7347860</v>
+        <v>7347875</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,10 +14341,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119646394</v>
+        <v>119646287</v>
       </c>
       <c r="B130" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14353,25 +14353,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14381,7 +14381,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>834555</v>
+        <v>834497</v>
       </c>
       <c r="R130" t="n">
         <v>7347854</v>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119646286</v>
+        <v>119646348</v>
       </c>
       <c r="B131" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14459,25 +14459,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>834520</v>
+        <v>834547</v>
       </c>
       <c r="R131" t="n">
-        <v>7347876</v>
+        <v>7347954</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119646362</v>
+        <v>119646382</v>
       </c>
       <c r="B132" t="n">
         <v>91834</v>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>834150</v>
+        <v>834509</v>
       </c>
       <c r="R132" t="n">
-        <v>7347951</v>
+        <v>7347828</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14659,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119646276</v>
+        <v>119646262</v>
       </c>
       <c r="B133" t="n">
-        <v>91826</v>
+        <v>86412</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14675,21 +14675,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3100</v>
+        <v>3690</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>834519</v>
+        <v>834493</v>
       </c>
       <c r="R133" t="n">
-        <v>7347875</v>
+        <v>7347964</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14765,10 +14765,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119646343</v>
+        <v>119646305</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14777,25 +14777,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14805,10 +14805,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>834547</v>
+        <v>834295</v>
       </c>
       <c r="R134" t="n">
-        <v>7347878</v>
+        <v>7348050</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119646387</v>
+        <v>119646319</v>
       </c>
       <c r="B135" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>834581</v>
+        <v>834543</v>
       </c>
       <c r="R135" t="n">
-        <v>7347739</v>
+        <v>7347875</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14977,10 +14977,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119646272</v>
+        <v>119646362</v>
       </c>
       <c r="B136" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14993,21 +14993,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15017,10 +15017,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>834136</v>
+        <v>834150</v>
       </c>
       <c r="R136" t="n">
-        <v>7348051</v>
+        <v>7347951</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15083,10 +15083,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119646267</v>
+        <v>119646330</v>
       </c>
       <c r="B137" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15095,25 +15095,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>834333</v>
+        <v>834475</v>
       </c>
       <c r="R137" t="n">
-        <v>7347848</v>
+        <v>7347966</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119646279</v>
+        <v>119646316</v>
       </c>
       <c r="B138" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15205,21 +15205,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>834196</v>
+        <v>834547</v>
       </c>
       <c r="R138" t="n">
-        <v>7347922</v>
+        <v>7347865</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15295,7 +15295,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119646391</v>
+        <v>119646359</v>
       </c>
       <c r="B139" t="n">
         <v>91834</v>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>834547</v>
+        <v>834110</v>
       </c>
       <c r="R139" t="n">
-        <v>7347853</v>
+        <v>7348050</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15401,10 +15401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119646326</v>
+        <v>119646288</v>
       </c>
       <c r="B140" t="n">
-        <v>91825</v>
+        <v>91884</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1968</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>834160</v>
+        <v>834457</v>
       </c>
       <c r="R140" t="n">
-        <v>7347971</v>
+        <v>7347962</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119646374</v>
+        <v>119646398</v>
       </c>
       <c r="B141" t="n">
         <v>91834</v>
@@ -15547,10 +15547,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>834296</v>
+        <v>834549</v>
       </c>
       <c r="R141" t="n">
-        <v>7347848</v>
+        <v>7347890</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119646398</v>
+        <v>119646371</v>
       </c>
       <c r="B142" t="n">
         <v>91834</v>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>834549</v>
+        <v>834172</v>
       </c>
       <c r="R142" t="n">
-        <v>7347890</v>
+        <v>7347857</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15719,10 +15719,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119646384</v>
+        <v>119646315</v>
       </c>
       <c r="B143" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15735,21 +15735,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>834524</v>
+        <v>834573</v>
       </c>
       <c r="R143" t="n">
-        <v>7347806</v>
+        <v>7347882</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119646261</v>
+        <v>119646300</v>
       </c>
       <c r="B144" t="n">
-        <v>79115</v>
+        <v>91852</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15837,25 +15837,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>834404</v>
+        <v>834203</v>
       </c>
       <c r="R144" t="n">
-        <v>7347982</v>
+        <v>7347849</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119646283</v>
+        <v>119646326</v>
       </c>
       <c r="B145" t="n">
-        <v>91828</v>
+        <v>91825</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15943,25 +15943,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>149</v>
+        <v>1968</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>834500</v>
+        <v>834160</v>
       </c>
       <c r="R145" t="n">
-        <v>7347836</v>
+        <v>7347971</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16037,10 +16037,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119646382</v>
+        <v>119646334</v>
       </c>
       <c r="B146" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16049,25 +16049,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>834509</v>
+        <v>834152</v>
       </c>
       <c r="R146" t="n">
-        <v>7347828</v>
+        <v>7347973</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119646306</v>
+        <v>119646261</v>
       </c>
       <c r="B147" t="n">
-        <v>91832</v>
+        <v>79115</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16159,21 +16159,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>834178</v>
+        <v>834404</v>
       </c>
       <c r="R147" t="n">
-        <v>7348061</v>
+        <v>7347982</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16249,10 +16249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119646351</v>
+        <v>119646282</v>
       </c>
       <c r="B148" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16261,25 +16261,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>834272</v>
+        <v>834143</v>
       </c>
       <c r="R148" t="n">
-        <v>7348066</v>
+        <v>7348013</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16355,10 +16355,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119646360</v>
+        <v>119646306</v>
       </c>
       <c r="B149" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16371,21 +16371,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>834135</v>
+        <v>834178</v>
       </c>
       <c r="R149" t="n">
-        <v>7347955</v>
+        <v>7348061</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119646359</v>
+        <v>119646399</v>
       </c>
       <c r="B150" t="n">
         <v>91834</v>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>834110</v>
+        <v>834512</v>
       </c>
       <c r="R150" t="n">
-        <v>7348050</v>
+        <v>7347879</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646271</v>
+        <v>119646384</v>
       </c>
       <c r="B151" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16583,21 +16583,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834478</v>
+        <v>834524</v>
       </c>
       <c r="R151" t="n">
-        <v>7347964</v>
+        <v>7347806</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646268</v>
+        <v>119646328</v>
       </c>
       <c r="B152" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834339</v>
+        <v>834265</v>
       </c>
       <c r="R152" t="n">
-        <v>7347842</v>
+        <v>7348012</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646341</v>
+        <v>119646278</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834561</v>
+        <v>834144</v>
       </c>
       <c r="R153" t="n">
-        <v>7347875</v>
+        <v>7348044</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,10 +16885,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646396</v>
+        <v>119646295</v>
       </c>
       <c r="B154" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16901,21 +16901,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834563</v>
+        <v>834273</v>
       </c>
       <c r="R154" t="n">
-        <v>7347883</v>
+        <v>7348017</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16991,7 +16991,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119646356</v>
+        <v>119646367</v>
       </c>
       <c r="B155" t="n">
         <v>91834</v>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>834132</v>
+        <v>834202</v>
       </c>
       <c r="R155" t="n">
-        <v>7348055</v>
+        <v>7347880</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17097,7 +17097,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119646350</v>
+        <v>119646353</v>
       </c>
       <c r="B156" t="n">
         <v>91834</v>
@@ -17137,10 +17137,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>834516</v>
+        <v>834186</v>
       </c>
       <c r="R156" t="n">
-        <v>7347965</v>
+        <v>7348079</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17203,10 +17203,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119646293</v>
+        <v>119646356</v>
       </c>
       <c r="B157" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17215,25 +17215,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>834278</v>
+        <v>834132</v>
       </c>
       <c r="R157" t="n">
-        <v>7347848</v>
+        <v>7348055</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17309,10 +17309,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119646305</v>
+        <v>119646286</v>
       </c>
       <c r="B158" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17321,25 +17321,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>834295</v>
+        <v>834520</v>
       </c>
       <c r="R158" t="n">
-        <v>7348050</v>
+        <v>7347876</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17415,7 +17415,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119646315</v>
+        <v>119646313</v>
       </c>
       <c r="B159" t="n">
         <v>91832</v>
@@ -17455,10 +17455,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>834573</v>
+        <v>834549</v>
       </c>
       <c r="R159" t="n">
-        <v>7347882</v>
+        <v>7347855</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17521,7 +17521,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119646320</v>
+        <v>119646322</v>
       </c>
       <c r="B160" t="n">
         <v>91832</v>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>834545</v>
+        <v>834535</v>
       </c>
       <c r="R160" t="n">
         <v>7347891</v>
@@ -17627,7 +17627,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119646354</v>
+        <v>119646385</v>
       </c>
       <c r="B161" t="n">
         <v>91834</v>
@@ -17667,10 +17667,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>834171</v>
+        <v>834545</v>
       </c>
       <c r="R161" t="n">
-        <v>7348044</v>
+        <v>7347772</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119646357</v>
+        <v>119646263</v>
       </c>
       <c r="B162" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17749,21 +17749,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>834118</v>
+        <v>834530</v>
       </c>
       <c r="R162" t="n">
-        <v>7348065</v>
+        <v>7347888</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17839,10 +17839,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119646316</v>
+        <v>119646391</v>
       </c>
       <c r="B163" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17855,21 +17855,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17882,7 +17882,7 @@
         <v>834547</v>
       </c>
       <c r="R163" t="n">
-        <v>7347865</v>
+        <v>7347853</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17945,10 +17945,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119646378</v>
+        <v>119646335</v>
       </c>
       <c r="B164" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17957,25 +17957,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17985,10 +17985,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>834385</v>
+        <v>834188</v>
       </c>
       <c r="R164" t="n">
-        <v>7347840</v>
+        <v>7347887</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18051,10 +18051,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119646273</v>
+        <v>119646341</v>
       </c>
       <c r="B165" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18063,25 +18063,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>834143</v>
+        <v>834561</v>
       </c>
       <c r="R165" t="n">
-        <v>7348014</v>
+        <v>7347875</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18157,10 +18157,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119646301</v>
+        <v>119646390</v>
       </c>
       <c r="B166" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18169,25 +18169,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18197,10 +18197,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>834209</v>
+        <v>834574</v>
       </c>
       <c r="R166" t="n">
-        <v>7347855</v>
+        <v>7347790</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18263,10 +18263,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119646277</v>
+        <v>119646380</v>
       </c>
       <c r="B167" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18279,21 +18279,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18303,10 +18303,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>834168</v>
+        <v>834492</v>
       </c>
       <c r="R167" t="n">
-        <v>7347981</v>
+        <v>7347839</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18369,10 +18369,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119646295</v>
+        <v>119646360</v>
       </c>
       <c r="B168" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18385,21 +18385,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18409,10 +18409,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>834273</v>
+        <v>834135</v>
       </c>
       <c r="R168" t="n">
-        <v>7348017</v>
+        <v>7347955</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18475,7 +18475,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119646345</v>
+        <v>119646338</v>
       </c>
       <c r="B169" t="n">
         <v>91840</v>
@@ -18515,10 +18515,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>834499</v>
+        <v>834346</v>
       </c>
       <c r="R169" t="n">
-        <v>7347865</v>
+        <v>7347844</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18581,10 +18581,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119646365</v>
+        <v>119646340</v>
       </c>
       <c r="B170" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18593,25 +18593,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>834185</v>
+        <v>834444</v>
       </c>
       <c r="R170" t="n">
-        <v>7347929</v>
+        <v>7347855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18687,10 +18687,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119646403</v>
+        <v>119646266</v>
       </c>
       <c r="B171" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18699,25 +18699,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18727,10 +18727,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>834495</v>
+        <v>834206</v>
       </c>
       <c r="R171" t="n">
-        <v>7347844</v>
+        <v>7348051</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18793,10 +18793,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119646371</v>
+        <v>119646268</v>
       </c>
       <c r="B172" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18805,25 +18805,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18833,10 +18833,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>834172</v>
+        <v>834339</v>
       </c>
       <c r="R172" t="n">
-        <v>7347857</v>
+        <v>7347842</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18899,7 +18899,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119646367</v>
+        <v>119646372</v>
       </c>
       <c r="B173" t="n">
         <v>91834</v>
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>834202</v>
+        <v>834274</v>
       </c>
       <c r="R173" t="n">
-        <v>7347880</v>
+        <v>7347868</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19005,7 +19005,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119646401</v>
+        <v>119646375</v>
       </c>
       <c r="B174" t="n">
         <v>91834</v>
@@ -19045,10 +19045,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>834496</v>
+        <v>834313</v>
       </c>
       <c r="R174" t="n">
-        <v>7347857</v>
+        <v>7347844</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19111,10 +19111,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119646278</v>
+        <v>119646394</v>
       </c>
       <c r="B175" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19127,21 +19127,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19151,10 +19151,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>834144</v>
+        <v>834555</v>
       </c>
       <c r="R175" t="n">
-        <v>7348044</v>
+        <v>7347854</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19217,10 +19217,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119646334</v>
+        <v>119646369</v>
       </c>
       <c r="B176" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19229,25 +19229,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19257,10 +19257,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>834152</v>
+        <v>834190</v>
       </c>
       <c r="R176" t="n">
-        <v>7347973</v>
+        <v>7347887</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19323,10 +19323,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119646328</v>
+        <v>119646279</v>
       </c>
       <c r="B177" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19335,25 +19335,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>834265</v>
+        <v>834196</v>
       </c>
       <c r="R177" t="n">
-        <v>7348012</v>
+        <v>7347922</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19429,10 +19429,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119646289</v>
+        <v>119646277</v>
       </c>
       <c r="B178" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19445,21 +19445,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>834286</v>
+        <v>834168</v>
       </c>
       <c r="R178" t="n">
-        <v>7348064</v>
+        <v>7347981</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19535,10 +19535,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119646288</v>
+        <v>119646320</v>
       </c>
       <c r="B179" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19551,21 +19551,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>834457</v>
+        <v>834545</v>
       </c>
       <c r="R179" t="n">
-        <v>7347962</v>
+        <v>7347891</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119646337</v>
+        <v>119646272</v>
       </c>
       <c r="B180" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19653,25 +19653,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19681,10 +19681,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>834262</v>
+        <v>834136</v>
       </c>
       <c r="R180" t="n">
-        <v>7347868</v>
+        <v>7348051</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19747,7 +19747,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119646338</v>
+        <v>119646343</v>
       </c>
       <c r="B181" t="n">
         <v>91840</v>
@@ -19787,10 +19787,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>834346</v>
+        <v>834547</v>
       </c>
       <c r="R181" t="n">
-        <v>7347844</v>
+        <v>7347878</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19853,10 +19853,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119646310</v>
+        <v>119646365</v>
       </c>
       <c r="B182" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19869,21 +19869,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19893,10 +19893,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>834330</v>
+        <v>834185</v>
       </c>
       <c r="R182" t="n">
-        <v>7347843</v>
+        <v>7347929</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119646388</v>
+        <v>119646301</v>
       </c>
       <c r="B183" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19971,25 +19971,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>834594</v>
+        <v>834209</v>
       </c>
       <c r="R183" t="n">
-        <v>7347747</v>
+        <v>7347855</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20065,10 +20065,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119646348</v>
+        <v>119646331</v>
       </c>
       <c r="B184" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20077,25 +20077,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20105,10 +20105,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>834547</v>
+        <v>834170</v>
       </c>
       <c r="R184" t="n">
-        <v>7347954</v>
+        <v>7348003</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20171,10 +20171,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119646259</v>
+        <v>119646275</v>
       </c>
       <c r="B185" t="n">
-        <v>91836</v>
+        <v>91826</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20183,25 +20183,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4363</v>
+        <v>3100</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>834292</v>
+        <v>834351</v>
       </c>
       <c r="R185" t="n">
-        <v>7348037</v>
+        <v>7347847</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20277,10 +20277,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119646369</v>
+        <v>119646337</v>
       </c>
       <c r="B186" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20289,25 +20289,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>834190</v>
+        <v>834262</v>
       </c>
       <c r="R186" t="n">
-        <v>7347887</v>
+        <v>7347868</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20383,7 +20383,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119646353</v>
+        <v>119646350</v>
       </c>
       <c r="B187" t="n">
         <v>91834</v>
@@ -20423,10 +20423,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>834186</v>
+        <v>834516</v>
       </c>
       <c r="R187" t="n">
-        <v>7348079</v>
+        <v>7347965</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20489,10 +20489,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119646311</v>
+        <v>119646357</v>
       </c>
       <c r="B188" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20505,21 +20505,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>834340</v>
+        <v>834118</v>
       </c>
       <c r="R188" t="n">
-        <v>7347841</v>
+        <v>7348065</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20595,10 +20595,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119646380</v>
+        <v>119646345</v>
       </c>
       <c r="B189" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20607,25 +20607,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>834492</v>
+        <v>834499</v>
       </c>
       <c r="R189" t="n">
-        <v>7347839</v>
+        <v>7347865</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20701,10 +20701,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119646377</v>
+        <v>119646310</v>
       </c>
       <c r="B190" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20717,21 +20717,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20741,10 +20741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>834324</v>
+        <v>834330</v>
       </c>
       <c r="R190" t="n">
-        <v>7347850</v>
+        <v>7347843</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20807,10 +20807,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119646308</v>
+        <v>119646354</v>
       </c>
       <c r="B191" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20823,21 +20823,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>834229</v>
+        <v>834171</v>
       </c>
       <c r="R191" t="n">
-        <v>7347852</v>
+        <v>7348044</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20913,10 +20913,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119646269</v>
+        <v>119646290</v>
       </c>
       <c r="B192" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20925,25 +20925,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20953,10 +20953,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>834531</v>
+        <v>834218</v>
       </c>
       <c r="R192" t="n">
-        <v>7347887</v>
+        <v>7347851</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21019,10 +21019,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119646266</v>
+        <v>119646271</v>
       </c>
       <c r="B193" t="n">
-        <v>89275</v>
+        <v>91826</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21031,25 +21031,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6286</v>
+        <v>3100</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21059,10 +21059,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>834206</v>
+        <v>834478</v>
       </c>
       <c r="R193" t="n">
-        <v>7348051</v>
+        <v>7347964</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21125,10 +21125,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119646300</v>
+        <v>119646311</v>
       </c>
       <c r="B194" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21137,25 +21137,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21165,10 +21165,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>834203</v>
+        <v>834340</v>
       </c>
       <c r="R194" t="n">
-        <v>7347849</v>
+        <v>7347841</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21231,7 +21231,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119646282</v>
+        <v>119646283</v>
       </c>
       <c r="B195" t="n">
         <v>91828</v>
@@ -21271,10 +21271,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>834143</v>
+        <v>834500</v>
       </c>
       <c r="R195" t="n">
-        <v>7348013</v>
+        <v>7347836</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21337,10 +21337,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646331</v>
+        <v>119646396</v>
       </c>
       <c r="B196" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834170</v>
+        <v>834563</v>
       </c>
       <c r="R196" t="n">
-        <v>7348003</v>
+        <v>7347883</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,10 +21443,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646340</v>
+        <v>119646259</v>
       </c>
       <c r="B197" t="n">
-        <v>91840</v>
+        <v>91836</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21459,21 +21459,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834444</v>
+        <v>834292</v>
       </c>
       <c r="R197" t="n">
-        <v>7347855</v>
+        <v>7348037</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646275</v>
+        <v>119646351</v>
       </c>
       <c r="B198" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21565,21 +21565,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834351</v>
+        <v>834272</v>
       </c>
       <c r="R198" t="n">
-        <v>7347847</v>
+        <v>7348066</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646290</v>
+        <v>119646387</v>
       </c>
       <c r="B199" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21671,21 +21671,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834218</v>
+        <v>834581</v>
       </c>
       <c r="R199" t="n">
-        <v>7347851</v>
+        <v>7347739</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,7 +21761,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646372</v>
+        <v>119646388</v>
       </c>
       <c r="B200" t="n">
         <v>91834</v>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834274</v>
+        <v>834594</v>
       </c>
       <c r="R200" t="n">
-        <v>7347868</v>
+        <v>7347747</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,10 +21867,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646322</v>
+        <v>119646289</v>
       </c>
       <c r="B201" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21883,21 +21883,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834535</v>
+        <v>834286</v>
       </c>
       <c r="R201" t="n">
-        <v>7347891</v>
+        <v>7348064</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21973,10 +21973,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119646399</v>
+        <v>119646269</v>
       </c>
       <c r="B202" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21985,25 +21985,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22013,10 +22013,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>834512</v>
+        <v>834531</v>
       </c>
       <c r="R202" t="n">
-        <v>7347879</v>
+        <v>7347887</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22079,10 +22079,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119646287</v>
+        <v>119646296</v>
       </c>
       <c r="B203" t="n">
-        <v>91828</v>
+        <v>91856</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22091,25 +22091,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>834497</v>
+        <v>834546</v>
       </c>
       <c r="R203" t="n">
-        <v>7347854</v>
+        <v>7347860</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22185,7 +22185,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119646375</v>
+        <v>119646403</v>
       </c>
       <c r="B204" t="n">
         <v>91834</v>
@@ -22225,7 +22225,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>834313</v>
+        <v>834495</v>
       </c>
       <c r="R204" t="n">
         <v>7347844</v>
@@ -22291,7 +22291,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119646390</v>
+        <v>119646377</v>
       </c>
       <c r="B205" t="n">
         <v>91834</v>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>834574</v>
+        <v>834324</v>
       </c>
       <c r="R205" t="n">
-        <v>7347790</v>
+        <v>7347850</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22397,7 +22397,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119646385</v>
+        <v>119646401</v>
       </c>
       <c r="B206" t="n">
         <v>91834</v>
@@ -22437,10 +22437,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>834545</v>
+        <v>834496</v>
       </c>
       <c r="R206" t="n">
-        <v>7347772</v>
+        <v>7347857</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22503,10 +22503,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119646313</v>
+        <v>119646378</v>
       </c>
       <c r="B207" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22519,21 +22519,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>834549</v>
+        <v>834385</v>
       </c>
       <c r="R207" t="n">
-        <v>7347855</v>
+        <v>7347840</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22609,7 +22609,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119646303</v>
+        <v>119646308</v>
       </c>
       <c r="B208" t="n">
         <v>91832</v>
@@ -22649,10 +22649,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>834528</v>
+        <v>834229</v>
       </c>
       <c r="R208" t="n">
-        <v>7347966</v>
+        <v>7347852</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22715,10 +22715,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119646281</v>
+        <v>119646267</v>
       </c>
       <c r="B209" t="n">
-        <v>91463</v>
+        <v>89275</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22727,25 +22727,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4745</v>
+        <v>6286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22755,10 +22755,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>834185</v>
+        <v>834333</v>
       </c>
       <c r="R209" t="n">
-        <v>7347860</v>
+        <v>7347848</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22821,10 +22821,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119646262</v>
+        <v>119646374</v>
       </c>
       <c r="B210" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22837,21 +22837,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>834493</v>
+        <v>834296</v>
       </c>
       <c r="R210" t="n">
-        <v>7347964</v>
+        <v>7347848</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22927,10 +22927,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119646263</v>
+        <v>119646273</v>
       </c>
       <c r="B211" t="n">
-        <v>86412</v>
+        <v>91826</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22943,21 +22943,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>3690</v>
+        <v>3100</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22967,10 +22967,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>834530</v>
+        <v>834143</v>
       </c>
       <c r="R211" t="n">
-        <v>7347888</v>
+        <v>7348014</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23033,10 +23033,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119646335</v>
+        <v>119646293</v>
       </c>
       <c r="B212" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23045,25 +23045,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>834188</v>
+        <v>834278</v>
       </c>
       <c r="R212" t="n">
-        <v>7347887</v>
+        <v>7347848</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23139,10 +23139,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119646330</v>
+        <v>119646303</v>
       </c>
       <c r="B213" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23151,25 +23151,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23179,7 +23179,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>834475</v>
+        <v>834528</v>
       </c>
       <c r="R213" t="n">
         <v>7347966</v>
@@ -23245,10 +23245,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119646319</v>
+        <v>119646281</v>
       </c>
       <c r="B214" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23261,21 +23261,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23285,10 +23285,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>834543</v>
+        <v>834185</v>
       </c>
       <c r="R214" t="n">
-        <v>7347875</v>
+        <v>7347860</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -4370,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626477</v>
+        <v>119626498</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>96868</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>834287</v>
+        <v>834053</v>
       </c>
       <c r="R36" t="n">
-        <v>7348033</v>
+        <v>7347834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119626522</v>
+        <v>119626497</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>834086</v>
+        <v>834121</v>
       </c>
       <c r="R37" t="n">
-        <v>7347878</v>
+        <v>7347872</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119626483</v>
+        <v>119626477</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>834080</v>
+        <v>834287</v>
       </c>
       <c r="R38" t="n">
-        <v>7347837</v>
+        <v>7348033</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119626534</v>
+        <v>119626522</v>
       </c>
       <c r="B39" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>834168</v>
+        <v>834086</v>
       </c>
       <c r="R39" t="n">
-        <v>7347939</v>
+        <v>7347878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119626440</v>
+        <v>119626483</v>
       </c>
       <c r="B40" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,25 +4806,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>834041</v>
+        <v>834080</v>
       </c>
       <c r="R40" t="n">
         <v>7347837</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626411</v>
+        <v>119626534</v>
       </c>
       <c r="B41" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,25 +4912,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834141</v>
+        <v>834168</v>
       </c>
       <c r="R41" t="n">
-        <v>7348021</v>
+        <v>7347939</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626498</v>
+        <v>119626440</v>
       </c>
       <c r="B42" t="n">
-        <v>96868</v>
+        <v>91463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,25 +5018,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834053</v>
+        <v>834041</v>
       </c>
       <c r="R42" t="n">
-        <v>7347834</v>
+        <v>7347837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626497</v>
+        <v>119626411</v>
       </c>
       <c r="B43" t="n">
-        <v>96868</v>
+        <v>89275</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5124,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>6286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834121</v>
+        <v>834141</v>
       </c>
       <c r="R43" t="n">
-        <v>7347872</v>
+        <v>7348021</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626450</v>
+        <v>119626510</v>
       </c>
       <c r="B51" t="n">
-        <v>91828</v>
+        <v>57421</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5978,25 +5978,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>149</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>834442</v>
+        <v>834118</v>
       </c>
       <c r="R51" t="n">
-        <v>7347873</v>
+        <v>7347885</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119626431</v>
+        <v>119626450</v>
       </c>
       <c r="B52" t="n">
-        <v>91826</v>
+        <v>91828</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6084,25 +6084,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>834318</v>
+        <v>834442</v>
       </c>
       <c r="R52" t="n">
-        <v>7347852</v>
+        <v>7347873</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6178,10 +6178,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119626554</v>
+        <v>119626431</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6194,21 +6194,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>834433</v>
+        <v>834318</v>
       </c>
       <c r="R53" t="n">
-        <v>7347878</v>
+        <v>7347852</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119626547</v>
+        <v>119626554</v>
       </c>
       <c r="B54" t="n">
         <v>91834</v>
@@ -6324,10 +6324,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>834115</v>
+        <v>834433</v>
       </c>
       <c r="R54" t="n">
-        <v>7347875</v>
+        <v>7347878</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119626499</v>
+        <v>119626547</v>
       </c>
       <c r="B55" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>834153</v>
+        <v>834115</v>
       </c>
       <c r="R55" t="n">
-        <v>7347952</v>
+        <v>7347875</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119626537</v>
+        <v>119626499</v>
       </c>
       <c r="B56" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>834282</v>
+        <v>834153</v>
       </c>
       <c r="R56" t="n">
-        <v>7347983</v>
+        <v>7347952</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119626543</v>
+        <v>119626537</v>
       </c>
       <c r="B57" t="n">
         <v>91834</v>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>834275</v>
+        <v>834282</v>
       </c>
       <c r="R57" t="n">
-        <v>7347856</v>
+        <v>7347983</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119626418</v>
+        <v>119626543</v>
       </c>
       <c r="B58" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6720,25 +6720,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>834185</v>
+        <v>834275</v>
       </c>
       <c r="R58" t="n">
-        <v>7347878</v>
+        <v>7347856</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119626510</v>
+        <v>119626418</v>
       </c>
       <c r="B59" t="n">
-        <v>57421</v>
+        <v>89275</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103031</v>
+        <v>6286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>834118</v>
+        <v>834185</v>
       </c>
       <c r="R59" t="n">
-        <v>7347885</v>
+        <v>7347878</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -11161,10 +11161,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119626462</v>
+        <v>119626529</v>
       </c>
       <c r="B100" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11173,25 +11173,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>834252</v>
+        <v>834467</v>
       </c>
       <c r="R100" t="n">
-        <v>7347832</v>
+        <v>7347889</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11267,7 +11267,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119626529</v>
+        <v>119626527</v>
       </c>
       <c r="B101" t="n">
         <v>91840</v>
@@ -11307,10 +11307,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>834467</v>
+        <v>834435</v>
       </c>
       <c r="R101" t="n">
-        <v>7347889</v>
+        <v>7347869</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11373,10 +11373,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119626527</v>
+        <v>119626462</v>
       </c>
       <c r="B102" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11385,25 +11385,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>834435</v>
+        <v>834252</v>
       </c>
       <c r="R102" t="n">
-        <v>7347869</v>
+        <v>7347832</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11585,10 +11585,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119626458</v>
+        <v>119626500</v>
       </c>
       <c r="B104" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11601,21 +11601,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11625,10 +11625,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>834214</v>
+        <v>834227</v>
       </c>
       <c r="R104" t="n">
-        <v>7347853</v>
+        <v>7347892</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11691,10 +11691,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119626463</v>
+        <v>119626532</v>
       </c>
       <c r="B105" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11703,25 +11703,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>834272</v>
+        <v>834192</v>
       </c>
       <c r="R105" t="n">
-        <v>7347885</v>
+        <v>7347888</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11797,10 +11797,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119626443</v>
+        <v>119626458</v>
       </c>
       <c r="B106" t="n">
-        <v>91463</v>
+        <v>91883</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11813,21 +11813,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4745</v>
+        <v>5448</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>834325</v>
+        <v>834214</v>
       </c>
       <c r="R106" t="n">
-        <v>7347874</v>
+        <v>7347853</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626500</v>
+        <v>119626463</v>
       </c>
       <c r="B107" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11919,21 +11919,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>834227</v>
+        <v>834272</v>
       </c>
       <c r="R107" t="n">
-        <v>7347892</v>
+        <v>7347885</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12009,10 +12009,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626532</v>
+        <v>119626443</v>
       </c>
       <c r="B108" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12021,25 +12021,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>834192</v>
+        <v>834325</v>
       </c>
       <c r="R108" t="n">
-        <v>7347888</v>
+        <v>7347874</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119646316</v>
+        <v>119646288</v>
       </c>
       <c r="B138" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15205,21 +15205,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>834547</v>
+        <v>834457</v>
       </c>
       <c r="R138" t="n">
-        <v>7347865</v>
+        <v>7347962</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15295,10 +15295,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119646359</v>
+        <v>119646316</v>
       </c>
       <c r="B139" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15311,21 +15311,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>834110</v>
+        <v>834547</v>
       </c>
       <c r="R139" t="n">
-        <v>7348050</v>
+        <v>7347865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15401,10 +15401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119646288</v>
+        <v>119646359</v>
       </c>
       <c r="B140" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>834457</v>
+        <v>834110</v>
       </c>
       <c r="R140" t="n">
-        <v>7347962</v>
+        <v>7348050</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16037,10 +16037,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119646334</v>
+        <v>119646261</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16049,25 +16049,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>834152</v>
+        <v>834404</v>
       </c>
       <c r="R146" t="n">
-        <v>7347973</v>
+        <v>7347982</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119646261</v>
+        <v>119646334</v>
       </c>
       <c r="B147" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16155,25 +16155,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>834404</v>
+        <v>834152</v>
       </c>
       <c r="R147" t="n">
-        <v>7347982</v>
+        <v>7347973</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16249,10 +16249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119646282</v>
+        <v>119646306</v>
       </c>
       <c r="B148" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16261,25 +16261,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>834143</v>
+        <v>834178</v>
       </c>
       <c r="R148" t="n">
-        <v>7348013</v>
+        <v>7348061</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16355,10 +16355,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119646306</v>
+        <v>119646399</v>
       </c>
       <c r="B149" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16371,21 +16371,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>834178</v>
+        <v>834512</v>
       </c>
       <c r="R149" t="n">
-        <v>7348061</v>
+        <v>7347879</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119646399</v>
+        <v>119646384</v>
       </c>
       <c r="B150" t="n">
         <v>91834</v>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>834512</v>
+        <v>834524</v>
       </c>
       <c r="R150" t="n">
-        <v>7347879</v>
+        <v>7347806</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646384</v>
+        <v>119646328</v>
       </c>
       <c r="B151" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16579,25 +16579,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834524</v>
+        <v>834265</v>
       </c>
       <c r="R151" t="n">
-        <v>7347806</v>
+        <v>7348012</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646328</v>
+        <v>119646295</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834265</v>
+        <v>834273</v>
       </c>
       <c r="R152" t="n">
-        <v>7348012</v>
+        <v>7348017</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646278</v>
+        <v>119646282</v>
       </c>
       <c r="B153" t="n">
-        <v>91463</v>
+        <v>91828</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4745</v>
+        <v>149</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834144</v>
+        <v>834143</v>
       </c>
       <c r="R153" t="n">
-        <v>7348044</v>
+        <v>7348013</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,10 +16885,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646295</v>
+        <v>119646278</v>
       </c>
       <c r="B154" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16901,21 +16901,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834273</v>
+        <v>834144</v>
       </c>
       <c r="R154" t="n">
-        <v>7348017</v>
+        <v>7348044</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119626448</v>
+        <v>119626405</v>
       </c>
       <c r="B30" t="n">
-        <v>91828</v>
+        <v>86412</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3746,25 +3746,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>149</v>
+        <v>3690</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>834184</v>
+        <v>834216</v>
       </c>
       <c r="R30" t="n">
-        <v>7347877</v>
+        <v>7347860</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119626515</v>
+        <v>119626533</v>
       </c>
       <c r="B31" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>834243</v>
+        <v>834153</v>
       </c>
       <c r="R31" t="n">
-        <v>7348008</v>
+        <v>7347932</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119626432</v>
+        <v>119626462</v>
       </c>
       <c r="B32" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>834167</v>
+        <v>834252</v>
       </c>
       <c r="R32" t="n">
-        <v>7348024</v>
+        <v>7347832</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119626520</v>
+        <v>119626442</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>834276</v>
+        <v>834160</v>
       </c>
       <c r="R33" t="n">
-        <v>7347908</v>
+        <v>7347864</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119626505</v>
+        <v>119626495</v>
       </c>
       <c r="B34" t="n">
-        <v>91832</v>
+        <v>96868</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>834329</v>
+        <v>834287</v>
       </c>
       <c r="R34" t="n">
-        <v>7347858</v>
+        <v>7347954</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119626540</v>
+        <v>119626475</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>834166</v>
+        <v>834243</v>
       </c>
       <c r="R35" t="n">
-        <v>7347884</v>
+        <v>7348008</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626498</v>
+        <v>119626430</v>
       </c>
       <c r="B36" t="n">
-        <v>96868</v>
+        <v>91826</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>834053</v>
+        <v>834295</v>
       </c>
       <c r="R36" t="n">
-        <v>7347834</v>
+        <v>7348032</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119626497</v>
+        <v>119626508</v>
       </c>
       <c r="B37" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>834121</v>
+        <v>834325</v>
       </c>
       <c r="R37" t="n">
-        <v>7347872</v>
+        <v>7347870</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119626477</v>
+        <v>119626428</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>91826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>834287</v>
+        <v>834149</v>
       </c>
       <c r="R38" t="n">
-        <v>7348033</v>
+        <v>7347970</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119626522</v>
+        <v>119626539</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>834086</v>
+        <v>834204</v>
       </c>
       <c r="R39" t="n">
-        <v>7347878</v>
+        <v>7347896</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119626483</v>
+        <v>119626479</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,25 +4806,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>834080</v>
+        <v>834177</v>
       </c>
       <c r="R40" t="n">
-        <v>7347837</v>
+        <v>7347881</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119626534</v>
+        <v>119626527</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4912,25 +4912,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>834168</v>
+        <v>834435</v>
       </c>
       <c r="R41" t="n">
-        <v>7347939</v>
+        <v>7347869</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119626440</v>
+        <v>119626521</v>
       </c>
       <c r="B42" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,25 +5018,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>834041</v>
+        <v>834220</v>
       </c>
       <c r="R42" t="n">
-        <v>7347837</v>
+        <v>7347890</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119626411</v>
+        <v>119626503</v>
       </c>
       <c r="B43" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5124,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>834141</v>
+        <v>834159</v>
       </c>
       <c r="R43" t="n">
-        <v>7348021</v>
+        <v>7347856</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119626406</v>
+        <v>119626505</v>
       </c>
       <c r="B44" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>834121</v>
+        <v>834329</v>
       </c>
       <c r="R44" t="n">
-        <v>7348010</v>
+        <v>7347858</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,18 +5296,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5330,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119626506</v>
+        <v>119626473</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5346,21 +5340,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5370,13 +5364,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>834322</v>
+        <v>834384</v>
       </c>
       <c r="R45" t="n">
-        <v>7347857</v>
+        <v>7347916</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5436,7 +5430,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119626544</v>
+        <v>119626553</v>
       </c>
       <c r="B46" t="n">
         <v>91834</v>
@@ -5476,10 +5470,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>834331</v>
+        <v>834388</v>
       </c>
       <c r="R46" t="n">
-        <v>7347868</v>
+        <v>7347909</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5542,10 +5536,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119626465</v>
+        <v>119626499</v>
       </c>
       <c r="B47" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5558,21 +5552,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5582,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>834267</v>
+        <v>834153</v>
       </c>
       <c r="R47" t="n">
-        <v>7347889</v>
+        <v>7347952</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5648,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119626416</v>
+        <v>119626506</v>
       </c>
       <c r="B48" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5660,25 +5654,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5688,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>834434</v>
+        <v>834322</v>
       </c>
       <c r="R48" t="n">
-        <v>7347883</v>
+        <v>7347857</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5754,10 +5748,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119626528</v>
+        <v>119626460</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5766,25 +5760,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5794,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>834454</v>
+        <v>834295</v>
       </c>
       <c r="R49" t="n">
-        <v>7347886</v>
+        <v>7347970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5860,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626525</v>
+        <v>119626554</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5872,25 +5866,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5900,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>834253</v>
+        <v>834433</v>
       </c>
       <c r="R50" t="n">
-        <v>7347885</v>
+        <v>7347878</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5966,10 +5960,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626510</v>
+        <v>119626520</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5982,21 +5976,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6006,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>834118</v>
+        <v>834276</v>
       </c>
       <c r="R51" t="n">
-        <v>7347885</v>
+        <v>7347908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6072,10 +6066,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119626450</v>
+        <v>119626516</v>
       </c>
       <c r="B52" t="n">
-        <v>91828</v>
+        <v>91825</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6084,25 +6078,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>149</v>
+        <v>1968</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6112,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>834442</v>
+        <v>834083</v>
       </c>
       <c r="R52" t="n">
-        <v>7347873</v>
+        <v>7347877</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6178,10 +6172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119626431</v>
+        <v>119626543</v>
       </c>
       <c r="B53" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6194,21 +6188,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6218,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>834318</v>
+        <v>834275</v>
       </c>
       <c r="R53" t="n">
-        <v>7347852</v>
+        <v>7347856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6284,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119626554</v>
+        <v>119626526</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6296,25 +6290,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6324,10 +6318,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>834433</v>
+        <v>834382</v>
       </c>
       <c r="R54" t="n">
-        <v>7347878</v>
+        <v>7347924</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6390,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119626547</v>
+        <v>119626436</v>
       </c>
       <c r="B55" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6406,21 +6400,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6430,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>834115</v>
+        <v>834236</v>
       </c>
       <c r="R55" t="n">
-        <v>7347875</v>
+        <v>7347993</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6496,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119626499</v>
+        <v>119626530</v>
       </c>
       <c r="B56" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6508,25 +6502,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6536,10 +6530,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>834153</v>
+        <v>834170</v>
       </c>
       <c r="R56" t="n">
-        <v>7347952</v>
+        <v>7347895</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6602,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119626537</v>
+        <v>119626446</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6618,21 +6612,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6642,10 +6636,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>834282</v>
+        <v>834267</v>
       </c>
       <c r="R57" t="n">
-        <v>7347983</v>
+        <v>7347889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,10 +6702,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119626543</v>
+        <v>119626456</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,21 +6718,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6748,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>834275</v>
+        <v>834204</v>
       </c>
       <c r="R58" t="n">
-        <v>7347856</v>
+        <v>7347855</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,10 +6808,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119626418</v>
+        <v>119626555</v>
       </c>
       <c r="B59" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6826,25 +6820,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6854,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>834185</v>
+        <v>834442</v>
       </c>
       <c r="R59" t="n">
-        <v>7347878</v>
+        <v>7347879</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119626501</v>
+        <v>119626542</v>
       </c>
       <c r="B60" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6936,21 +6930,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6954,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>834207</v>
+        <v>834148</v>
       </c>
       <c r="R60" t="n">
-        <v>7347898</v>
+        <v>7347880</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7026,10 +7020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119626409</v>
+        <v>119626545</v>
       </c>
       <c r="B61" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7038,25 +7032,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7066,10 +7060,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>834121</v>
+        <v>834320</v>
       </c>
       <c r="R61" t="n">
-        <v>7348010</v>
+        <v>7347855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7132,10 +7126,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119626548</v>
+        <v>119626523</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7144,25 +7138,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7172,10 +7166,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>834151</v>
+        <v>834210</v>
       </c>
       <c r="R62" t="n">
-        <v>7347881</v>
+        <v>7347853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7238,10 +7232,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119626523</v>
+        <v>119626535</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7250,25 +7244,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>834210</v>
+        <v>834187</v>
       </c>
       <c r="R63" t="n">
-        <v>7347853</v>
+        <v>7347944</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7344,10 +7338,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119626519</v>
+        <v>119626540</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7356,25 +7350,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7384,10 +7378,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>834148</v>
+        <v>834166</v>
       </c>
       <c r="R64" t="n">
-        <v>7347973</v>
+        <v>7347884</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7450,10 +7444,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119626508</v>
+        <v>119626529</v>
       </c>
       <c r="B65" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7462,25 +7456,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7490,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>834325</v>
+        <v>834467</v>
       </c>
       <c r="R65" t="n">
-        <v>7347870</v>
+        <v>7347889</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7556,7 +7550,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119626460</v>
+        <v>119626463</v>
       </c>
       <c r="B66" t="n">
         <v>91884</v>
@@ -7596,10 +7590,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>834295</v>
+        <v>834272</v>
       </c>
       <c r="R66" t="n">
-        <v>7347970</v>
+        <v>7347885</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7662,7 +7656,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119626436</v>
+        <v>119626453</v>
       </c>
       <c r="B67" t="n">
         <v>91463</v>
@@ -7702,10 +7696,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>834236</v>
+        <v>834124</v>
       </c>
       <c r="R67" t="n">
-        <v>7347993</v>
+        <v>7347874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7768,10 +7762,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119626420</v>
+        <v>119626444</v>
       </c>
       <c r="B68" t="n">
-        <v>89275</v>
+        <v>91463</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7780,25 +7774,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7808,7 +7802,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>834252</v>
+        <v>834154</v>
       </c>
       <c r="R68" t="n">
         <v>7347884</v>
@@ -7874,10 +7868,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119626423</v>
+        <v>119626517</v>
       </c>
       <c r="B69" t="n">
-        <v>56522</v>
+        <v>91825</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7886,25 +7880,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>1968</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7914,10 +7908,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>834319</v>
+        <v>834243</v>
       </c>
       <c r="R69" t="n">
-        <v>7347861</v>
+        <v>7347862</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7980,10 +7974,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119626404</v>
+        <v>119626550</v>
       </c>
       <c r="B70" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7996,21 +7990,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8020,10 +8014,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>834430</v>
+        <v>834212</v>
       </c>
       <c r="R70" t="n">
-        <v>7347886</v>
+        <v>7347855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8064,7 +8058,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8087,7 +8080,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119626542</v>
+        <v>119626544</v>
       </c>
       <c r="B71" t="n">
         <v>91834</v>
@@ -8127,10 +8120,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>834148</v>
+        <v>834331</v>
       </c>
       <c r="R71" t="n">
-        <v>7347880</v>
+        <v>7347868</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8193,10 +8186,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119626539</v>
+        <v>119626408</v>
       </c>
       <c r="B72" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8209,21 +8202,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8233,10 +8226,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>834204</v>
+        <v>834123</v>
       </c>
       <c r="R72" t="n">
-        <v>7347896</v>
+        <v>7347975</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,10 +8292,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119626521</v>
+        <v>119626510</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>57421</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8315,21 +8308,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8339,10 +8332,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>834220</v>
+        <v>834118</v>
       </c>
       <c r="R73" t="n">
-        <v>7347890</v>
+        <v>7347885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8405,10 +8398,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119626421</v>
+        <v>119626497</v>
       </c>
       <c r="B74" t="n">
-        <v>56522</v>
+        <v>96868</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8421,21 +8414,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8445,10 +8438,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>834160</v>
+        <v>834121</v>
       </c>
       <c r="R74" t="n">
-        <v>7347850</v>
+        <v>7347872</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8511,10 +8504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119626455</v>
+        <v>119626538</v>
       </c>
       <c r="B75" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8527,21 +8520,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8551,10 +8544,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>834288</v>
+        <v>834292</v>
       </c>
       <c r="R75" t="n">
-        <v>7347877</v>
+        <v>7347968</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8617,10 +8610,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119626467</v>
+        <v>119626439</v>
       </c>
       <c r="B76" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8633,21 +8626,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8657,10 +8650,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>834310</v>
+        <v>834018</v>
       </c>
       <c r="R76" t="n">
-        <v>7347899</v>
+        <v>7347852</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8723,10 +8716,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119626557</v>
+        <v>119626434</v>
       </c>
       <c r="B77" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8739,21 +8732,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8763,10 +8756,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>834308</v>
+        <v>834189</v>
       </c>
       <c r="R77" t="n">
-        <v>7347903</v>
+        <v>7347957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8829,10 +8822,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119626538</v>
+        <v>119626500</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8845,21 +8838,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8869,10 +8862,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>834292</v>
+        <v>834227</v>
       </c>
       <c r="R78" t="n">
-        <v>7347968</v>
+        <v>7347892</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8935,7 +8928,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119626545</v>
+        <v>119626537</v>
       </c>
       <c r="B79" t="n">
         <v>91834</v>
@@ -8975,10 +8968,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>834320</v>
+        <v>834282</v>
       </c>
       <c r="R79" t="n">
-        <v>7347855</v>
+        <v>7347983</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9041,10 +9034,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119626531</v>
+        <v>119626551</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9053,25 +9046,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9081,10 +9074,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>834282</v>
+        <v>834249</v>
       </c>
       <c r="R80" t="n">
-        <v>7347898</v>
+        <v>7347880</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9147,10 +9140,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119626446</v>
+        <v>119626486</v>
       </c>
       <c r="B81" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9159,25 +9152,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9187,10 +9180,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>834267</v>
+        <v>834186</v>
       </c>
       <c r="R81" t="n">
-        <v>7347889</v>
+        <v>7347942</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9253,10 +9246,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119626433</v>
+        <v>119626467</v>
       </c>
       <c r="B82" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9269,21 +9262,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9293,10 +9286,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>834169</v>
+        <v>834310</v>
       </c>
       <c r="R82" t="n">
-        <v>7347940</v>
+        <v>7347899</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9359,10 +9352,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119626414</v>
+        <v>119626509</v>
       </c>
       <c r="B83" t="n">
-        <v>89275</v>
+        <v>91863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9371,25 +9364,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9399,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>834252</v>
+        <v>834244</v>
       </c>
       <c r="R83" t="n">
-        <v>7347893</v>
+        <v>7347889</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9465,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626481</v>
+        <v>119626420</v>
       </c>
       <c r="B84" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9477,25 +9470,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9505,10 +9498,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>834455</v>
+        <v>834252</v>
       </c>
       <c r="R84" t="n">
-        <v>7347890</v>
+        <v>7347884</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9571,10 +9564,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626551</v>
+        <v>119626418</v>
       </c>
       <c r="B85" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9583,25 +9576,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9611,10 +9604,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>834249</v>
+        <v>834185</v>
       </c>
       <c r="R85" t="n">
-        <v>7347880</v>
+        <v>7347878</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9677,10 +9670,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119626535</v>
+        <v>119626501</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9693,21 +9686,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9717,10 +9710,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>834187</v>
+        <v>834207</v>
       </c>
       <c r="R86" t="n">
-        <v>7347944</v>
+        <v>7347898</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9783,10 +9776,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119626437</v>
+        <v>119626549</v>
       </c>
       <c r="B87" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9799,21 +9792,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9823,10 +9816,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>834288</v>
+        <v>834196</v>
       </c>
       <c r="R87" t="n">
-        <v>7347985</v>
+        <v>7347874</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9889,10 +9882,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119626473</v>
+        <v>119626440</v>
       </c>
       <c r="B88" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9905,21 +9898,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9929,13 +9922,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>834384</v>
+        <v>834041</v>
       </c>
       <c r="R88" t="n">
-        <v>7347916</v>
+        <v>7347837</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9995,10 +9988,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119626550</v>
+        <v>119626443</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10011,21 +10004,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10035,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>834212</v>
+        <v>834325</v>
       </c>
       <c r="R89" t="n">
-        <v>7347855</v>
+        <v>7347874</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10101,10 +10094,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119626533</v>
+        <v>119626433</v>
       </c>
       <c r="B90" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10117,21 +10110,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10141,10 +10134,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>834153</v>
+        <v>834169</v>
       </c>
       <c r="R90" t="n">
-        <v>7347932</v>
+        <v>7347940</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10207,10 +10200,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119626444</v>
+        <v>119626483</v>
       </c>
       <c r="B91" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10219,25 +10212,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10247,10 +10240,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>834154</v>
+        <v>834080</v>
       </c>
       <c r="R91" t="n">
-        <v>7347884</v>
+        <v>7347837</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10313,10 +10306,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119626408</v>
+        <v>119626557</v>
       </c>
       <c r="B92" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10329,21 +10322,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10353,10 +10346,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>834123</v>
+        <v>834308</v>
       </c>
       <c r="R92" t="n">
-        <v>7347975</v>
+        <v>7347903</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10419,10 +10412,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119626405</v>
+        <v>119626507</v>
       </c>
       <c r="B93" t="n">
-        <v>86412</v>
+        <v>91832</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10435,21 +10428,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10459,10 +10452,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>834216</v>
+        <v>834277</v>
       </c>
       <c r="R93" t="n">
-        <v>7347860</v>
+        <v>7347848</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10525,10 +10518,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119626503</v>
+        <v>119626465</v>
       </c>
       <c r="B94" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10541,21 +10534,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10565,10 +10558,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>834159</v>
+        <v>834267</v>
       </c>
       <c r="R94" t="n">
-        <v>7347856</v>
+        <v>7347889</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10631,7 +10624,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119626434</v>
+        <v>119626455</v>
       </c>
       <c r="B95" t="n">
         <v>91463</v>
@@ -10671,10 +10664,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>834189</v>
+        <v>834288</v>
       </c>
       <c r="R95" t="n">
-        <v>7347957</v>
+        <v>7347877</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10737,10 +10730,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119626517</v>
+        <v>119626458</v>
       </c>
       <c r="B96" t="n">
-        <v>91825</v>
+        <v>91883</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10753,21 +10746,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1968</v>
+        <v>5448</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10777,10 +10770,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>834243</v>
+        <v>834214</v>
       </c>
       <c r="R96" t="n">
-        <v>7347862</v>
+        <v>7347853</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,10 +10836,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119626507</v>
+        <v>119626414</v>
       </c>
       <c r="B97" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10855,25 +10848,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10883,10 +10876,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>834277</v>
+        <v>834252</v>
       </c>
       <c r="R97" t="n">
-        <v>7347848</v>
+        <v>7347893</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119626556</v>
+        <v>119626532</v>
       </c>
       <c r="B98" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10961,25 +10954,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10989,10 +10982,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>834453</v>
+        <v>834192</v>
       </c>
       <c r="R98" t="n">
-        <v>7347884</v>
+        <v>7347888</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11055,10 +11048,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119626509</v>
+        <v>119626525</v>
       </c>
       <c r="B99" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11067,25 +11060,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11095,10 +11088,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>834244</v>
+        <v>834253</v>
       </c>
       <c r="R99" t="n">
-        <v>7347889</v>
+        <v>7347885</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11161,10 +11154,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119626529</v>
+        <v>119626498</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11177,21 +11170,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11201,10 +11194,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>834467</v>
+        <v>834053</v>
       </c>
       <c r="R100" t="n">
-        <v>7347889</v>
+        <v>7347834</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11267,10 +11260,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119626527</v>
+        <v>119626477</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11279,25 +11272,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11307,10 +11300,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>834435</v>
+        <v>834287</v>
       </c>
       <c r="R101" t="n">
-        <v>7347869</v>
+        <v>7348033</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11373,10 +11366,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119626462</v>
+        <v>119626411</v>
       </c>
       <c r="B102" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11385,25 +11378,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11413,10 +11406,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>834252</v>
+        <v>834141</v>
       </c>
       <c r="R102" t="n">
-        <v>7347832</v>
+        <v>7348021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11479,10 +11472,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119626452</v>
+        <v>119626431</v>
       </c>
       <c r="B103" t="n">
-        <v>91828</v>
+        <v>91826</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11491,25 +11484,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11519,10 +11512,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>834454</v>
+        <v>834318</v>
       </c>
       <c r="R103" t="n">
-        <v>7347892</v>
+        <v>7347852</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11585,10 +11578,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119626500</v>
+        <v>119626519</v>
       </c>
       <c r="B104" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11597,25 +11590,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11625,10 +11618,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>834227</v>
+        <v>834148</v>
       </c>
       <c r="R104" t="n">
-        <v>7347892</v>
+        <v>7347973</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11691,10 +11684,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119626532</v>
+        <v>119626448</v>
       </c>
       <c r="B105" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11703,25 +11696,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11731,10 +11724,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>834192</v>
+        <v>834184</v>
       </c>
       <c r="R105" t="n">
-        <v>7347888</v>
+        <v>7347877</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11797,10 +11790,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119626458</v>
+        <v>119626481</v>
       </c>
       <c r="B106" t="n">
-        <v>91883</v>
+        <v>91856</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11813,21 +11806,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11837,10 +11830,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>834214</v>
+        <v>834455</v>
       </c>
       <c r="R106" t="n">
-        <v>7347853</v>
+        <v>7347890</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11903,10 +11896,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626463</v>
+        <v>119626406</v>
       </c>
       <c r="B107" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11919,21 +11912,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11943,10 +11936,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>834272</v>
+        <v>834121</v>
       </c>
       <c r="R107" t="n">
-        <v>7347885</v>
+        <v>7348010</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11981,12 +11974,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12009,10 +12008,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626443</v>
+        <v>119626547</v>
       </c>
       <c r="B108" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12025,21 +12024,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12049,10 +12048,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>834325</v>
+        <v>834115</v>
       </c>
       <c r="R108" t="n">
-        <v>7347874</v>
+        <v>7347875</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12115,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119626475</v>
+        <v>119626528</v>
       </c>
       <c r="B109" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12127,25 +12126,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12155,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>834243</v>
+        <v>834454</v>
       </c>
       <c r="R109" t="n">
-        <v>7348008</v>
+        <v>7347886</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12221,10 +12220,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119626428</v>
+        <v>119626522</v>
       </c>
       <c r="B110" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12233,25 +12232,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12261,10 +12260,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>834149</v>
+        <v>834086</v>
       </c>
       <c r="R110" t="n">
-        <v>7347970</v>
+        <v>7347878</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12327,10 +12326,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119626549</v>
+        <v>119626412</v>
       </c>
       <c r="B111" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12339,25 +12338,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12367,10 +12366,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>834196</v>
+        <v>834267</v>
       </c>
       <c r="R111" t="n">
-        <v>7347874</v>
+        <v>7347984</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12433,10 +12432,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119626430</v>
+        <v>119626531</v>
       </c>
       <c r="B112" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12445,25 +12444,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12473,10 +12472,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>834295</v>
+        <v>834282</v>
       </c>
       <c r="R112" t="n">
-        <v>7348032</v>
+        <v>7347898</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12539,10 +12538,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119626530</v>
+        <v>119626452</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12551,25 +12550,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12579,10 +12578,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>834170</v>
+        <v>834454</v>
       </c>
       <c r="R113" t="n">
-        <v>7347895</v>
+        <v>7347892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12645,7 +12644,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119626552</v>
+        <v>119626556</v>
       </c>
       <c r="B114" t="n">
         <v>91834</v>
@@ -12685,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>834354</v>
+        <v>834453</v>
       </c>
       <c r="R114" t="n">
-        <v>7347911</v>
+        <v>7347884</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12750,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119626412</v>
+        <v>119626437</v>
       </c>
       <c r="B115" t="n">
-        <v>89275</v>
+        <v>91463</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12763,25 +12762,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12790,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>834267</v>
+        <v>834288</v>
       </c>
       <c r="R115" t="n">
-        <v>7347984</v>
+        <v>7347985</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12857,10 +12856,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119626453</v>
+        <v>119626421</v>
       </c>
       <c r="B116" t="n">
-        <v>91463</v>
+        <v>56522</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12869,25 +12868,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4745</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12897,10 +12896,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>834124</v>
+        <v>834160</v>
       </c>
       <c r="R116" t="n">
-        <v>7347874</v>
+        <v>7347850</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12963,10 +12962,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119626439</v>
+        <v>119626515</v>
       </c>
       <c r="B117" t="n">
-        <v>91463</v>
+        <v>91825</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12979,21 +12978,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4745</v>
+        <v>1968</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13003,10 +13002,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>834018</v>
+        <v>834243</v>
       </c>
       <c r="R117" t="n">
-        <v>7347852</v>
+        <v>7348008</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13069,10 +13068,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626456</v>
+        <v>119626416</v>
       </c>
       <c r="B118" t="n">
-        <v>91883</v>
+        <v>89275</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13081,25 +13080,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5448</v>
+        <v>6286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13109,10 +13108,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834204</v>
+        <v>834434</v>
       </c>
       <c r="R118" t="n">
-        <v>7347855</v>
+        <v>7347883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13175,10 +13174,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626516</v>
+        <v>119626404</v>
       </c>
       <c r="B119" t="n">
-        <v>91825</v>
+        <v>86412</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13191,21 +13190,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1968</v>
+        <v>3690</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13215,10 +13214,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834083</v>
+        <v>834430</v>
       </c>
       <c r="R119" t="n">
-        <v>7347877</v>
+        <v>7347886</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13259,6 +13258,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626553</v>
+        <v>119626548</v>
       </c>
       <c r="B120" t="n">
         <v>91834</v>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834388</v>
+        <v>834151</v>
       </c>
       <c r="R120" t="n">
-        <v>7347909</v>
+        <v>7347881</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119626526</v>
+        <v>119626409</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13399,25 +13399,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>834382</v>
+        <v>834121</v>
       </c>
       <c r="R121" t="n">
-        <v>7347924</v>
+        <v>7348010</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13493,10 +13493,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119626479</v>
+        <v>119626504</v>
       </c>
       <c r="B122" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13509,21 +13509,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>834177</v>
+        <v>834309</v>
       </c>
       <c r="R122" t="n">
-        <v>7347881</v>
+        <v>7347875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13599,10 +13599,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119626504</v>
+        <v>119626536</v>
       </c>
       <c r="B123" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13615,21 +13615,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13639,10 +13639,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>834309</v>
+        <v>834190</v>
       </c>
       <c r="R123" t="n">
-        <v>7347875</v>
+        <v>7347950</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13705,7 +13705,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119626536</v>
+        <v>119626552</v>
       </c>
       <c r="B124" t="n">
         <v>91834</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>834190</v>
+        <v>834354</v>
       </c>
       <c r="R124" t="n">
-        <v>7347950</v>
+        <v>7347911</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119626486</v>
+        <v>119626534</v>
       </c>
       <c r="B125" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13823,25 +13823,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>834186</v>
+        <v>834168</v>
       </c>
       <c r="R125" t="n">
-        <v>7347942</v>
+        <v>7347939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13917,10 +13917,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626555</v>
+        <v>119626423</v>
       </c>
       <c r="B126" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13929,25 +13929,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834442</v>
+        <v>834319</v>
       </c>
       <c r="R126" t="n">
-        <v>7347879</v>
+        <v>7347861</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626442</v>
+        <v>119626450</v>
       </c>
       <c r="B127" t="n">
-        <v>91463</v>
+        <v>91828</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14035,25 +14035,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4745</v>
+        <v>149</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834160</v>
+        <v>834442</v>
       </c>
       <c r="R127" t="n">
-        <v>7347864</v>
+        <v>7347873</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14129,10 +14129,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119626495</v>
+        <v>119626432</v>
       </c>
       <c r="B128" t="n">
-        <v>96868</v>
+        <v>91826</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14141,25 +14141,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14169,10 +14169,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>834287</v>
+        <v>834167</v>
       </c>
       <c r="R128" t="n">
-        <v>7347954</v>
+        <v>7348024</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119646276</v>
+        <v>119646385</v>
       </c>
       <c r="B129" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14251,21 +14251,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>834519</v>
+        <v>834545</v>
       </c>
       <c r="R129" t="n">
-        <v>7347875</v>
+        <v>7347772</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,10 +14341,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119646287</v>
+        <v>119646378</v>
       </c>
       <c r="B130" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14353,25 +14353,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14381,10 +14381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>834497</v>
+        <v>834385</v>
       </c>
       <c r="R130" t="n">
-        <v>7347854</v>
+        <v>7347840</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119646348</v>
+        <v>119646278</v>
       </c>
       <c r="B131" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14463,21 +14463,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>834547</v>
+        <v>834144</v>
       </c>
       <c r="R131" t="n">
-        <v>7347954</v>
+        <v>7348044</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14553,10 +14553,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119646382</v>
+        <v>119646326</v>
       </c>
       <c r="B132" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14569,21 +14569,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>834509</v>
+        <v>834160</v>
       </c>
       <c r="R132" t="n">
-        <v>7347828</v>
+        <v>7347971</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14659,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119646262</v>
+        <v>119646382</v>
       </c>
       <c r="B133" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14675,21 +14675,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>834493</v>
+        <v>834509</v>
       </c>
       <c r="R133" t="n">
-        <v>7347964</v>
+        <v>7347828</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14765,10 +14765,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119646305</v>
+        <v>119646369</v>
       </c>
       <c r="B134" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14781,21 +14781,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14805,10 +14805,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>834295</v>
+        <v>834190</v>
       </c>
       <c r="R134" t="n">
-        <v>7348050</v>
+        <v>7347887</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119646319</v>
+        <v>119646356</v>
       </c>
       <c r="B135" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>834543</v>
+        <v>834132</v>
       </c>
       <c r="R135" t="n">
-        <v>7347875</v>
+        <v>7348055</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14977,10 +14977,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119646362</v>
+        <v>119646266</v>
       </c>
       <c r="B136" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14989,25 +14989,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15017,10 +15017,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>834150</v>
+        <v>834206</v>
       </c>
       <c r="R136" t="n">
-        <v>7347951</v>
+        <v>7348051</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15083,10 +15083,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119646330</v>
+        <v>119646295</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15095,25 +15095,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>834475</v>
+        <v>834273</v>
       </c>
       <c r="R137" t="n">
-        <v>7347966</v>
+        <v>7348017</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119646288</v>
+        <v>119646267</v>
       </c>
       <c r="B138" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15201,25 +15201,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>834457</v>
+        <v>834333</v>
       </c>
       <c r="R138" t="n">
-        <v>7347962</v>
+        <v>7347848</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15295,10 +15295,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119646316</v>
+        <v>119646398</v>
       </c>
       <c r="B139" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15311,21 +15311,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15335,10 +15335,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>834547</v>
+        <v>834549</v>
       </c>
       <c r="R139" t="n">
-        <v>7347865</v>
+        <v>7347890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15401,10 +15401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119646359</v>
+        <v>119646322</v>
       </c>
       <c r="B140" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15417,21 +15417,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>834110</v>
+        <v>834535</v>
       </c>
       <c r="R140" t="n">
-        <v>7348050</v>
+        <v>7347891</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119646398</v>
+        <v>119646403</v>
       </c>
       <c r="B141" t="n">
         <v>91834</v>
@@ -15547,10 +15547,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>834549</v>
+        <v>834495</v>
       </c>
       <c r="R141" t="n">
-        <v>7347890</v>
+        <v>7347844</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119646371</v>
+        <v>119646377</v>
       </c>
       <c r="B142" t="n">
         <v>91834</v>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>834172</v>
+        <v>834324</v>
       </c>
       <c r="R142" t="n">
-        <v>7347857</v>
+        <v>7347850</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15719,10 +15719,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119646315</v>
+        <v>119646372</v>
       </c>
       <c r="B143" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15735,21 +15735,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>834573</v>
+        <v>834274</v>
       </c>
       <c r="R143" t="n">
-        <v>7347882</v>
+        <v>7347868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119646300</v>
+        <v>119646316</v>
       </c>
       <c r="B144" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15837,25 +15837,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>834203</v>
+        <v>834547</v>
       </c>
       <c r="R144" t="n">
-        <v>7347849</v>
+        <v>7347865</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119646326</v>
+        <v>119646384</v>
       </c>
       <c r="B145" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15947,21 +15947,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>834160</v>
+        <v>834524</v>
       </c>
       <c r="R145" t="n">
-        <v>7347971</v>
+        <v>7347806</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16037,10 +16037,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119646261</v>
+        <v>119646374</v>
       </c>
       <c r="B146" t="n">
-        <v>79115</v>
+        <v>91834</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16053,21 +16053,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>834404</v>
+        <v>834296</v>
       </c>
       <c r="R146" t="n">
-        <v>7347982</v>
+        <v>7347848</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16143,10 +16143,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119646334</v>
+        <v>119646362</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16155,25 +16155,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16183,10 +16183,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>834152</v>
+        <v>834150</v>
       </c>
       <c r="R147" t="n">
-        <v>7347973</v>
+        <v>7347951</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16249,10 +16249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119646306</v>
+        <v>119646371</v>
       </c>
       <c r="B148" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16265,21 +16265,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>834178</v>
+        <v>834172</v>
       </c>
       <c r="R148" t="n">
-        <v>7348061</v>
+        <v>7347857</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16355,7 +16355,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119646399</v>
+        <v>119646357</v>
       </c>
       <c r="B149" t="n">
         <v>91834</v>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>834512</v>
+        <v>834118</v>
       </c>
       <c r="R149" t="n">
-        <v>7347879</v>
+        <v>7348065</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16461,10 +16461,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119646384</v>
+        <v>119646303</v>
       </c>
       <c r="B150" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16477,21 +16477,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>834524</v>
+        <v>834528</v>
       </c>
       <c r="R150" t="n">
-        <v>7347806</v>
+        <v>7347966</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119646328</v>
+        <v>119646287</v>
       </c>
       <c r="B151" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16579,25 +16579,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>834265</v>
+        <v>834497</v>
       </c>
       <c r="R151" t="n">
-        <v>7348012</v>
+        <v>7347854</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646295</v>
+        <v>119646335</v>
       </c>
       <c r="B152" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834273</v>
+        <v>834188</v>
       </c>
       <c r="R152" t="n">
-        <v>7348017</v>
+        <v>7347887</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646282</v>
+        <v>119646290</v>
       </c>
       <c r="B153" t="n">
-        <v>91828</v>
+        <v>91884</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834143</v>
+        <v>834218</v>
       </c>
       <c r="R153" t="n">
-        <v>7348013</v>
+        <v>7347851</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16885,10 +16885,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119646278</v>
+        <v>119646276</v>
       </c>
       <c r="B154" t="n">
-        <v>91463</v>
+        <v>91826</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16901,21 +16901,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>834144</v>
+        <v>834519</v>
       </c>
       <c r="R154" t="n">
-        <v>7348044</v>
+        <v>7347875</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16991,7 +16991,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119646367</v>
+        <v>119646359</v>
       </c>
       <c r="B155" t="n">
         <v>91834</v>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>834202</v>
+        <v>834110</v>
       </c>
       <c r="R155" t="n">
-        <v>7347880</v>
+        <v>7348050</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17203,10 +17203,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119646356</v>
+        <v>119646277</v>
       </c>
       <c r="B157" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17219,21 +17219,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>834132</v>
+        <v>834168</v>
       </c>
       <c r="R157" t="n">
-        <v>7348055</v>
+        <v>7347981</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17309,10 +17309,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119646286</v>
+        <v>119646396</v>
       </c>
       <c r="B158" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17321,25 +17321,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>834520</v>
+        <v>834563</v>
       </c>
       <c r="R158" t="n">
-        <v>7347876</v>
+        <v>7347883</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17415,10 +17415,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119646313</v>
+        <v>119646272</v>
       </c>
       <c r="B159" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17431,21 +17431,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17455,10 +17455,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>834549</v>
+        <v>834136</v>
       </c>
       <c r="R159" t="n">
-        <v>7347855</v>
+        <v>7348051</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17521,10 +17521,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119646322</v>
+        <v>119646259</v>
       </c>
       <c r="B160" t="n">
-        <v>91832</v>
+        <v>91836</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17533,25 +17533,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4361</v>
+        <v>4363</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17561,10 +17561,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>834535</v>
+        <v>834292</v>
       </c>
       <c r="R160" t="n">
-        <v>7347891</v>
+        <v>7348037</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17627,10 +17627,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119646385</v>
+        <v>119646273</v>
       </c>
       <c r="B161" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17643,21 +17643,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17667,10 +17667,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>834545</v>
+        <v>834143</v>
       </c>
       <c r="R161" t="n">
-        <v>7347772</v>
+        <v>7348014</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17733,10 +17733,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119646263</v>
+        <v>119646293</v>
       </c>
       <c r="B162" t="n">
-        <v>86412</v>
+        <v>91844</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17745,25 +17745,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3690</v>
+        <v>4365</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>834530</v>
+        <v>834278</v>
       </c>
       <c r="R162" t="n">
-        <v>7347888</v>
+        <v>7347848</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17839,10 +17839,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119646391</v>
+        <v>119646286</v>
       </c>
       <c r="B163" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17851,25 +17851,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>834547</v>
+        <v>834520</v>
       </c>
       <c r="R163" t="n">
-        <v>7347853</v>
+        <v>7347876</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17945,7 +17945,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119646335</v>
+        <v>119646337</v>
       </c>
       <c r="B164" t="n">
         <v>91840</v>
@@ -17985,10 +17985,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>834188</v>
+        <v>834262</v>
       </c>
       <c r="R164" t="n">
-        <v>7347887</v>
+        <v>7347868</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18051,10 +18051,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119646341</v>
+        <v>119646394</v>
       </c>
       <c r="B165" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18063,25 +18063,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18091,10 +18091,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>834561</v>
+        <v>834555</v>
       </c>
       <c r="R165" t="n">
-        <v>7347875</v>
+        <v>7347854</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18157,7 +18157,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119646390</v>
+        <v>119646388</v>
       </c>
       <c r="B166" t="n">
         <v>91834</v>
@@ -18197,10 +18197,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>834574</v>
+        <v>834594</v>
       </c>
       <c r="R166" t="n">
-        <v>7347790</v>
+        <v>7347747</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18263,7 +18263,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119646380</v>
+        <v>119646350</v>
       </c>
       <c r="B167" t="n">
         <v>91834</v>
@@ -18303,10 +18303,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>834492</v>
+        <v>834516</v>
       </c>
       <c r="R167" t="n">
-        <v>7347839</v>
+        <v>7347965</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18369,10 +18369,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119646360</v>
+        <v>119646338</v>
       </c>
       <c r="B168" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18381,25 +18381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18409,10 +18409,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>834135</v>
+        <v>834346</v>
       </c>
       <c r="R168" t="n">
-        <v>7347955</v>
+        <v>7347844</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18475,10 +18475,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119646338</v>
+        <v>119646391</v>
       </c>
       <c r="B169" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18487,25 +18487,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18515,10 +18515,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>834346</v>
+        <v>834547</v>
       </c>
       <c r="R169" t="n">
-        <v>7347844</v>
+        <v>7347853</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18581,10 +18581,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119646340</v>
+        <v>119646283</v>
       </c>
       <c r="B170" t="n">
-        <v>91840</v>
+        <v>91828</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18593,25 +18593,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>834444</v>
+        <v>834500</v>
       </c>
       <c r="R170" t="n">
-        <v>7347855</v>
+        <v>7347836</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18687,7 +18687,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119646266</v>
+        <v>119646268</v>
       </c>
       <c r="B171" t="n">
         <v>89275</v>
@@ -18727,10 +18727,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>834206</v>
+        <v>834339</v>
       </c>
       <c r="R171" t="n">
-        <v>7348051</v>
+        <v>7347842</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18793,10 +18793,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119646268</v>
+        <v>119646348</v>
       </c>
       <c r="B172" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18805,25 +18805,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18833,10 +18833,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>834339</v>
+        <v>834547</v>
       </c>
       <c r="R172" t="n">
-        <v>7347842</v>
+        <v>7347954</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18899,7 +18899,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119646372</v>
+        <v>119646399</v>
       </c>
       <c r="B173" t="n">
         <v>91834</v>
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>834274</v>
+        <v>834512</v>
       </c>
       <c r="R173" t="n">
-        <v>7347868</v>
+        <v>7347879</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19005,10 +19005,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119646375</v>
+        <v>119646320</v>
       </c>
       <c r="B174" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19021,21 +19021,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19045,10 +19045,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>834313</v>
+        <v>834545</v>
       </c>
       <c r="R174" t="n">
-        <v>7347844</v>
+        <v>7347891</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19111,10 +19111,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119646394</v>
+        <v>119646310</v>
       </c>
       <c r="B175" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19127,21 +19127,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19151,10 +19151,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>834555</v>
+        <v>834330</v>
       </c>
       <c r="R175" t="n">
-        <v>7347854</v>
+        <v>7347843</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19217,10 +19217,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119646369</v>
+        <v>119646308</v>
       </c>
       <c r="B176" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19233,21 +19233,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19257,10 +19257,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>834190</v>
+        <v>834229</v>
       </c>
       <c r="R176" t="n">
-        <v>7347887</v>
+        <v>7347852</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19323,10 +19323,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119646279</v>
+        <v>119646340</v>
       </c>
       <c r="B177" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19335,25 +19335,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>834196</v>
+        <v>834444</v>
       </c>
       <c r="R177" t="n">
-        <v>7347922</v>
+        <v>7347855</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19429,10 +19429,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119646277</v>
+        <v>119646300</v>
       </c>
       <c r="B178" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19441,25 +19441,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>834168</v>
+        <v>834203</v>
       </c>
       <c r="R178" t="n">
-        <v>7347981</v>
+        <v>7347849</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19535,10 +19535,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119646320</v>
+        <v>119646262</v>
       </c>
       <c r="B179" t="n">
-        <v>91832</v>
+        <v>86412</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19551,21 +19551,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>834545</v>
+        <v>834493</v>
       </c>
       <c r="R179" t="n">
-        <v>7347891</v>
+        <v>7347964</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119646272</v>
+        <v>119646288</v>
       </c>
       <c r="B180" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19657,21 +19657,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19681,10 +19681,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>834136</v>
+        <v>834457</v>
       </c>
       <c r="R180" t="n">
-        <v>7348051</v>
+        <v>7347962</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19747,10 +19747,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119646343</v>
+        <v>119646279</v>
       </c>
       <c r="B181" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19759,25 +19759,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19787,10 +19787,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>834547</v>
+        <v>834196</v>
       </c>
       <c r="R181" t="n">
-        <v>7347878</v>
+        <v>7347922</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19853,10 +19853,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119646365</v>
+        <v>119646306</v>
       </c>
       <c r="B182" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19869,21 +19869,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19893,10 +19893,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>834185</v>
+        <v>834178</v>
       </c>
       <c r="R182" t="n">
-        <v>7347929</v>
+        <v>7348061</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119646301</v>
+        <v>119646351</v>
       </c>
       <c r="B183" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19971,25 +19971,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>834209</v>
+        <v>834272</v>
       </c>
       <c r="R183" t="n">
-        <v>7347855</v>
+        <v>7348066</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20065,7 +20065,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119646331</v>
+        <v>119646330</v>
       </c>
       <c r="B184" t="n">
         <v>91840</v>
@@ -20105,10 +20105,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>834170</v>
+        <v>834475</v>
       </c>
       <c r="R184" t="n">
-        <v>7348003</v>
+        <v>7347966</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20171,10 +20171,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119646275</v>
+        <v>119646328</v>
       </c>
       <c r="B185" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20183,25 +20183,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>834351</v>
+        <v>834265</v>
       </c>
       <c r="R185" t="n">
-        <v>7347847</v>
+        <v>7348012</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20277,10 +20277,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119646337</v>
+        <v>119646375</v>
       </c>
       <c r="B186" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20289,25 +20289,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>834262</v>
+        <v>834313</v>
       </c>
       <c r="R186" t="n">
-        <v>7347868</v>
+        <v>7347844</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20383,10 +20383,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119646350</v>
+        <v>119646341</v>
       </c>
       <c r="B187" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20395,25 +20395,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20423,10 +20423,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>834516</v>
+        <v>834561</v>
       </c>
       <c r="R187" t="n">
-        <v>7347965</v>
+        <v>7347875</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20489,10 +20489,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119646357</v>
+        <v>119646315</v>
       </c>
       <c r="B188" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20505,21 +20505,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>834118</v>
+        <v>834573</v>
       </c>
       <c r="R188" t="n">
-        <v>7348065</v>
+        <v>7347882</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20595,10 +20595,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119646345</v>
+        <v>119646311</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20607,25 +20607,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>834499</v>
+        <v>834340</v>
       </c>
       <c r="R189" t="n">
-        <v>7347865</v>
+        <v>7347841</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20701,10 +20701,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119646310</v>
+        <v>119646380</v>
       </c>
       <c r="B190" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20717,21 +20717,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20741,10 +20741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>834330</v>
+        <v>834492</v>
       </c>
       <c r="R190" t="n">
-        <v>7347843</v>
+        <v>7347839</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20807,10 +20807,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119646354</v>
+        <v>119646319</v>
       </c>
       <c r="B191" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20823,21 +20823,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>834171</v>
+        <v>834543</v>
       </c>
       <c r="R191" t="n">
-        <v>7348044</v>
+        <v>7347875</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20913,10 +20913,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119646290</v>
+        <v>119646367</v>
       </c>
       <c r="B192" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20929,21 +20929,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20953,10 +20953,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>834218</v>
+        <v>834202</v>
       </c>
       <c r="R192" t="n">
-        <v>7347851</v>
+        <v>7347880</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21019,10 +21019,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119646271</v>
+        <v>119646282</v>
       </c>
       <c r="B193" t="n">
-        <v>91826</v>
+        <v>91828</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21031,25 +21031,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21059,10 +21059,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>834478</v>
+        <v>834143</v>
       </c>
       <c r="R193" t="n">
-        <v>7347964</v>
+        <v>7348013</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21125,10 +21125,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119646311</v>
+        <v>119646343</v>
       </c>
       <c r="B194" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21137,25 +21137,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21165,10 +21165,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>834340</v>
+        <v>834547</v>
       </c>
       <c r="R194" t="n">
-        <v>7347841</v>
+        <v>7347878</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21231,10 +21231,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119646283</v>
+        <v>119646334</v>
       </c>
       <c r="B195" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21243,25 +21243,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21271,10 +21271,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>834500</v>
+        <v>834152</v>
       </c>
       <c r="R195" t="n">
-        <v>7347836</v>
+        <v>7347973</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21337,10 +21337,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646396</v>
+        <v>119646301</v>
       </c>
       <c r="B196" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834563</v>
+        <v>834209</v>
       </c>
       <c r="R196" t="n">
-        <v>7347883</v>
+        <v>7347855</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,10 +21443,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646259</v>
+        <v>119646281</v>
       </c>
       <c r="B197" t="n">
-        <v>91836</v>
+        <v>91463</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21455,25 +21455,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4363</v>
+        <v>4745</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834292</v>
+        <v>834185</v>
       </c>
       <c r="R197" t="n">
-        <v>7348037</v>
+        <v>7347860</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646351</v>
+        <v>119646261</v>
       </c>
       <c r="B198" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21565,21 +21565,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834272</v>
+        <v>834404</v>
       </c>
       <c r="R198" t="n">
-        <v>7348066</v>
+        <v>7347982</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646387</v>
+        <v>119646305</v>
       </c>
       <c r="B199" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21671,21 +21671,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834581</v>
+        <v>834295</v>
       </c>
       <c r="R199" t="n">
-        <v>7347739</v>
+        <v>7348050</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,7 +21761,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646388</v>
+        <v>119646390</v>
       </c>
       <c r="B200" t="n">
         <v>91834</v>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834594</v>
+        <v>834574</v>
       </c>
       <c r="R200" t="n">
-        <v>7347747</v>
+        <v>7347790</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21867,10 +21867,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119646289</v>
+        <v>119646269</v>
       </c>
       <c r="B201" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21879,25 +21879,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21907,10 +21907,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>834286</v>
+        <v>834531</v>
       </c>
       <c r="R201" t="n">
-        <v>7348064</v>
+        <v>7347887</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21973,10 +21973,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119646269</v>
+        <v>119646331</v>
       </c>
       <c r="B202" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21985,25 +21985,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22013,10 +22013,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>834531</v>
+        <v>834170</v>
       </c>
       <c r="R202" t="n">
-        <v>7347887</v>
+        <v>7348003</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22079,10 +22079,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119646296</v>
+        <v>119646354</v>
       </c>
       <c r="B203" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22095,21 +22095,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>834546</v>
+        <v>834171</v>
       </c>
       <c r="R203" t="n">
-        <v>7347860</v>
+        <v>7348044</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22185,10 +22185,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119646403</v>
+        <v>119646271</v>
       </c>
       <c r="B204" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22201,21 +22201,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22225,10 +22225,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>834495</v>
+        <v>834478</v>
       </c>
       <c r="R204" t="n">
-        <v>7347844</v>
+        <v>7347964</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119646377</v>
+        <v>119646313</v>
       </c>
       <c r="B205" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22307,21 +22307,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>834324</v>
+        <v>834549</v>
       </c>
       <c r="R205" t="n">
-        <v>7347850</v>
+        <v>7347855</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22397,10 +22397,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119646401</v>
+        <v>119646263</v>
       </c>
       <c r="B206" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22413,21 +22413,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22437,10 +22437,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>834496</v>
+        <v>834530</v>
       </c>
       <c r="R206" t="n">
-        <v>7347857</v>
+        <v>7347888</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22503,10 +22503,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119646378</v>
+        <v>119646345</v>
       </c>
       <c r="B207" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22515,25 +22515,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>834385</v>
+        <v>834499</v>
       </c>
       <c r="R207" t="n">
-        <v>7347840</v>
+        <v>7347865</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22609,10 +22609,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119646308</v>
+        <v>119646275</v>
       </c>
       <c r="B208" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22625,21 +22625,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22649,10 +22649,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>834229</v>
+        <v>834351</v>
       </c>
       <c r="R208" t="n">
-        <v>7347852</v>
+        <v>7347847</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22715,10 +22715,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119646267</v>
+        <v>119646401</v>
       </c>
       <c r="B209" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22727,25 +22727,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22755,10 +22755,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>834333</v>
+        <v>834496</v>
       </c>
       <c r="R209" t="n">
-        <v>7347848</v>
+        <v>7347857</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22821,7 +22821,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119646374</v>
+        <v>119646360</v>
       </c>
       <c r="B210" t="n">
         <v>91834</v>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>834296</v>
+        <v>834135</v>
       </c>
       <c r="R210" t="n">
-        <v>7347848</v>
+        <v>7347955</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22927,10 +22927,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119646273</v>
+        <v>119646296</v>
       </c>
       <c r="B211" t="n">
-        <v>91826</v>
+        <v>91856</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22943,21 +22943,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22967,10 +22967,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>834143</v>
+        <v>834546</v>
       </c>
       <c r="R211" t="n">
-        <v>7348014</v>
+        <v>7347860</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23033,10 +23033,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119646293</v>
+        <v>119646365</v>
       </c>
       <c r="B212" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23045,25 +23045,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>834278</v>
+        <v>834185</v>
       </c>
       <c r="R212" t="n">
-        <v>7347848</v>
+        <v>7347929</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23139,10 +23139,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119646303</v>
+        <v>119646387</v>
       </c>
       <c r="B213" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23155,21 +23155,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23179,10 +23179,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>834528</v>
+        <v>834581</v>
       </c>
       <c r="R213" t="n">
-        <v>7347966</v>
+        <v>7347739</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23245,10 +23245,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119646281</v>
+        <v>119646289</v>
       </c>
       <c r="B214" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23261,21 +23261,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23285,10 +23285,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>834185</v>
+        <v>834286</v>
       </c>
       <c r="R214" t="n">
-        <v>7347860</v>
+        <v>7348064</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626554</v>
+        <v>119626516</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5870,21 +5870,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>834433</v>
+        <v>834083</v>
       </c>
       <c r="R50" t="n">
-        <v>7347878</v>
+        <v>7347877</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5960,10 +5960,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626520</v>
+        <v>119626554</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5972,25 +5972,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>834276</v>
+        <v>834433</v>
       </c>
       <c r="R51" t="n">
-        <v>7347908</v>
+        <v>7347878</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119626516</v>
+        <v>119626520</v>
       </c>
       <c r="B52" t="n">
-        <v>91825</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6078,25 +6078,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>834083</v>
+        <v>834276</v>
       </c>
       <c r="R52" t="n">
-        <v>7347877</v>
+        <v>7347908</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -12750,10 +12750,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119626437</v>
+        <v>119626515</v>
       </c>
       <c r="B115" t="n">
-        <v>91463</v>
+        <v>91825</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12766,21 +12766,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4745</v>
+        <v>1968</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>834288</v>
+        <v>834243</v>
       </c>
       <c r="R115" t="n">
-        <v>7347985</v>
+        <v>7348008</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12856,10 +12856,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119626421</v>
+        <v>119626416</v>
       </c>
       <c r="B116" t="n">
-        <v>56522</v>
+        <v>89275</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12868,25 +12868,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>6286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>834160</v>
+        <v>834434</v>
       </c>
       <c r="R116" t="n">
-        <v>7347850</v>
+        <v>7347883</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12962,10 +12962,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119626515</v>
+        <v>119626404</v>
       </c>
       <c r="B117" t="n">
-        <v>91825</v>
+        <v>86412</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12978,21 +12978,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1968</v>
+        <v>3690</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>834243</v>
+        <v>834430</v>
       </c>
       <c r="R117" t="n">
-        <v>7348008</v>
+        <v>7347886</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13046,6 +13046,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13068,10 +13069,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119626416</v>
+        <v>119626548</v>
       </c>
       <c r="B118" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13080,25 +13081,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13108,10 +13109,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>834434</v>
+        <v>834151</v>
       </c>
       <c r="R118" t="n">
-        <v>7347883</v>
+        <v>7347881</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13174,10 +13175,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119626404</v>
+        <v>119626437</v>
       </c>
       <c r="B119" t="n">
-        <v>86412</v>
+        <v>91463</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13190,21 +13191,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13214,10 +13215,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>834430</v>
+        <v>834288</v>
       </c>
       <c r="R119" t="n">
-        <v>7347886</v>
+        <v>7347985</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13258,7 +13259,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13281,10 +13281,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119626548</v>
+        <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13293,25 +13293,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13321,10 +13321,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>834151</v>
+        <v>834160</v>
       </c>
       <c r="R120" t="n">
-        <v>7347881</v>
+        <v>7347850</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -23033,7 +23033,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119646365</v>
+        <v>119646387</v>
       </c>
       <c r="B212" t="n">
         <v>91834</v>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>834185</v>
+        <v>834581</v>
       </c>
       <c r="R212" t="n">
-        <v>7347929</v>
+        <v>7347739</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23139,7 +23139,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119646387</v>
+        <v>119646365</v>
       </c>
       <c r="B213" t="n">
         <v>91834</v>
@@ -23179,10 +23179,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>834581</v>
+        <v>834185</v>
       </c>
       <c r="R213" t="n">
-        <v>7347739</v>
+        <v>7347929</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119626405</v>
+        <v>119626475</v>
       </c>
       <c r="B30" t="n">
-        <v>86412</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3750,21 +3750,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>834216</v>
+        <v>834243</v>
       </c>
       <c r="R30" t="n">
-        <v>7347860</v>
+        <v>7348008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119626533</v>
+        <v>119626462</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>834153</v>
+        <v>834252</v>
       </c>
       <c r="R31" t="n">
-        <v>7347932</v>
+        <v>7347832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119626462</v>
+        <v>119626442</v>
       </c>
       <c r="B32" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>834252</v>
+        <v>834160</v>
       </c>
       <c r="R32" t="n">
-        <v>7347832</v>
+        <v>7347864</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119626442</v>
+        <v>119626405</v>
       </c>
       <c r="B33" t="n">
-        <v>91463</v>
+        <v>86412</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4068,21 +4068,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>834160</v>
+        <v>834216</v>
       </c>
       <c r="R33" t="n">
-        <v>7347864</v>
+        <v>7347860</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119626495</v>
+        <v>119626533</v>
       </c>
       <c r="B34" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>834287</v>
+        <v>834153</v>
       </c>
       <c r="R34" t="n">
-        <v>7347954</v>
+        <v>7347932</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119626475</v>
+        <v>119626495</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>96868</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>834243</v>
+        <v>834287</v>
       </c>
       <c r="R35" t="n">
-        <v>7348008</v>
+        <v>7347954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -8186,10 +8186,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119626408</v>
+        <v>119626510</v>
       </c>
       <c r="B72" t="n">
-        <v>89633</v>
+        <v>57421</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8198,25 +8198,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1962</v>
+        <v>103031</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>834123</v>
+        <v>834118</v>
       </c>
       <c r="R72" t="n">
-        <v>7347975</v>
+        <v>7347885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8292,10 +8292,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119626510</v>
+        <v>119626497</v>
       </c>
       <c r="B73" t="n">
-        <v>57421</v>
+        <v>96868</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8308,21 +8308,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>834118</v>
+        <v>834121</v>
       </c>
       <c r="R73" t="n">
-        <v>7347885</v>
+        <v>7347872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119626497</v>
+        <v>119626408</v>
       </c>
       <c r="B74" t="n">
-        <v>96868</v>
+        <v>89633</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8410,25 +8410,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8438,10 +8438,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>834121</v>
+        <v>834123</v>
       </c>
       <c r="R74" t="n">
-        <v>7347872</v>
+        <v>7347975</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119626431</v>
+        <v>119626448</v>
       </c>
       <c r="B103" t="n">
-        <v>91826</v>
+        <v>91828</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11484,25 +11484,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>834318</v>
+        <v>834184</v>
       </c>
       <c r="R103" t="n">
-        <v>7347852</v>
+        <v>7347877</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119626519</v>
+        <v>119626431</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11590,25 +11590,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>834148</v>
+        <v>834318</v>
       </c>
       <c r="R104" t="n">
-        <v>7347973</v>
+        <v>7347852</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11684,10 +11684,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119626448</v>
+        <v>119626519</v>
       </c>
       <c r="B105" t="n">
-        <v>91828</v>
+        <v>91840</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11696,25 +11696,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11724,10 +11724,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>834184</v>
+        <v>834148</v>
       </c>
       <c r="R105" t="n">
-        <v>7347877</v>
+        <v>7347973</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11790,10 +11790,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119626481</v>
+        <v>119626547</v>
       </c>
       <c r="B106" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11806,21 +11806,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>834455</v>
+        <v>834115</v>
       </c>
       <c r="R106" t="n">
-        <v>7347890</v>
+        <v>7347875</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11896,10 +11896,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626406</v>
+        <v>119626481</v>
       </c>
       <c r="B107" t="n">
-        <v>89633</v>
+        <v>91856</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11912,21 +11912,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>834121</v>
+        <v>834455</v>
       </c>
       <c r="R107" t="n">
-        <v>7348010</v>
+        <v>7347890</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11974,18 +11974,12 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Kollekt till Sten Svantesson.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12008,10 +12002,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626547</v>
+        <v>119626406</v>
       </c>
       <c r="B108" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12024,21 +12018,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12048,10 +12042,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>834115</v>
+        <v>834121</v>
       </c>
       <c r="R108" t="n">
-        <v>7347875</v>
+        <v>7348010</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12086,12 +12080,18 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Kollekt till Sten Svantesson.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13917,10 +13917,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119626423</v>
+        <v>119626450</v>
       </c>
       <c r="B126" t="n">
-        <v>56522</v>
+        <v>91828</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13929,25 +13929,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100138</v>
+        <v>149</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13957,10 +13957,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>834319</v>
+        <v>834442</v>
       </c>
       <c r="R126" t="n">
-        <v>7347861</v>
+        <v>7347873</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119626450</v>
+        <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>91828</v>
+        <v>56522</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14035,25 +14035,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>149</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>834442</v>
+        <v>834319</v>
       </c>
       <c r="R127" t="n">
-        <v>7347873</v>
+        <v>7347861</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14235,10 +14235,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119646385</v>
+        <v>119646326</v>
       </c>
       <c r="B129" t="n">
-        <v>91834</v>
+        <v>91825</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14251,21 +14251,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4362</v>
+        <v>1968</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>834545</v>
+        <v>834160</v>
       </c>
       <c r="R129" t="n">
-        <v>7347772</v>
+        <v>7347971</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14341,10 +14341,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119646378</v>
+        <v>119646278</v>
       </c>
       <c r="B130" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14357,21 +14357,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14381,10 +14381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>834385</v>
+        <v>834144</v>
       </c>
       <c r="R130" t="n">
-        <v>7347840</v>
+        <v>7348044</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119646278</v>
+        <v>119646385</v>
       </c>
       <c r="B131" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14463,21 +14463,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>834144</v>
+        <v>834545</v>
       </c>
       <c r="R131" t="n">
-        <v>7348044</v>
+        <v>7347772</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14553,10 +14553,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119646326</v>
+        <v>119646378</v>
       </c>
       <c r="B132" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14569,21 +14569,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>834160</v>
+        <v>834385</v>
       </c>
       <c r="R132" t="n">
-        <v>7347971</v>
+        <v>7347840</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15719,7 +15719,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119646372</v>
+        <v>119646384</v>
       </c>
       <c r="B143" t="n">
         <v>91834</v>
@@ -15759,10 +15759,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>834274</v>
+        <v>834524</v>
       </c>
       <c r="R143" t="n">
-        <v>7347868</v>
+        <v>7347806</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,10 +15825,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119646316</v>
+        <v>119646374</v>
       </c>
       <c r="B144" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15841,21 +15841,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>834547</v>
+        <v>834296</v>
       </c>
       <c r="R144" t="n">
-        <v>7347865</v>
+        <v>7347848</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15931,7 +15931,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119646384</v>
+        <v>119646372</v>
       </c>
       <c r="B145" t="n">
         <v>91834</v>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>834524</v>
+        <v>834274</v>
       </c>
       <c r="R145" t="n">
-        <v>7347806</v>
+        <v>7347868</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16037,10 +16037,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119646374</v>
+        <v>119646316</v>
       </c>
       <c r="B146" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16053,21 +16053,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16077,10 +16077,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>834296</v>
+        <v>834547</v>
       </c>
       <c r="R146" t="n">
-        <v>7347848</v>
+        <v>7347865</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646335</v>
+        <v>119646290</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834188</v>
+        <v>834218</v>
       </c>
       <c r="R152" t="n">
-        <v>7347887</v>
+        <v>7347851</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646290</v>
+        <v>119646335</v>
       </c>
       <c r="B153" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834218</v>
+        <v>834188</v>
       </c>
       <c r="R153" t="n">
-        <v>7347851</v>
+        <v>7347887</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -19747,10 +19747,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119646279</v>
+        <v>119646306</v>
       </c>
       <c r="B181" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19763,21 +19763,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19787,10 +19787,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>834196</v>
+        <v>834178</v>
       </c>
       <c r="R181" t="n">
-        <v>7347922</v>
+        <v>7348061</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19853,10 +19853,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119646306</v>
+        <v>119646351</v>
       </c>
       <c r="B182" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19869,21 +19869,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19893,10 +19893,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>834178</v>
+        <v>834272</v>
       </c>
       <c r="R182" t="n">
-        <v>7348061</v>
+        <v>7348066</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119646351</v>
+        <v>119646330</v>
       </c>
       <c r="B183" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19971,25 +19971,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>834272</v>
+        <v>834475</v>
       </c>
       <c r="R183" t="n">
-        <v>7348066</v>
+        <v>7347966</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20065,7 +20065,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119646330</v>
+        <v>119646328</v>
       </c>
       <c r="B184" t="n">
         <v>91840</v>
@@ -20105,10 +20105,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>834475</v>
+        <v>834265</v>
       </c>
       <c r="R184" t="n">
-        <v>7347966</v>
+        <v>7348012</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20171,10 +20171,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119646328</v>
+        <v>119646279</v>
       </c>
       <c r="B185" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20183,25 +20183,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>834265</v>
+        <v>834196</v>
       </c>
       <c r="R185" t="n">
-        <v>7348012</v>
+        <v>7347922</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21337,10 +21337,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646301</v>
+        <v>119646305</v>
       </c>
       <c r="B196" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834209</v>
+        <v>834295</v>
       </c>
       <c r="R196" t="n">
-        <v>7347855</v>
+        <v>7348050</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,10 +21443,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646281</v>
+        <v>119646390</v>
       </c>
       <c r="B197" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21459,21 +21459,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834185</v>
+        <v>834574</v>
       </c>
       <c r="R197" t="n">
-        <v>7347860</v>
+        <v>7347790</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646261</v>
+        <v>119646301</v>
       </c>
       <c r="B198" t="n">
-        <v>79115</v>
+        <v>91852</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21561,25 +21561,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834404</v>
+        <v>834209</v>
       </c>
       <c r="R198" t="n">
-        <v>7347982</v>
+        <v>7347855</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646305</v>
+        <v>119646281</v>
       </c>
       <c r="B199" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21671,21 +21671,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834295</v>
+        <v>834185</v>
       </c>
       <c r="R199" t="n">
-        <v>7348050</v>
+        <v>7347860</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646390</v>
+        <v>119646261</v>
       </c>
       <c r="B200" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834574</v>
+        <v>834404</v>
       </c>
       <c r="R200" t="n">
-        <v>7347790</v>
+        <v>7347982</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23033,7 +23033,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119646387</v>
+        <v>119646365</v>
       </c>
       <c r="B212" t="n">
         <v>91834</v>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>834581</v>
+        <v>834185</v>
       </c>
       <c r="R212" t="n">
-        <v>7347739</v>
+        <v>7347929</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23139,7 +23139,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119646365</v>
+        <v>119646387</v>
       </c>
       <c r="B213" t="n">
         <v>91834</v>
@@ -23179,10 +23179,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>834185</v>
+        <v>834581</v>
       </c>
       <c r="R213" t="n">
-        <v>7347929</v>
+        <v>7347739</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -16673,10 +16673,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119646290</v>
+        <v>119646335</v>
       </c>
       <c r="B152" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16685,25 +16685,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16713,10 +16713,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>834218</v>
+        <v>834188</v>
       </c>
       <c r="R152" t="n">
-        <v>7347851</v>
+        <v>7347887</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16779,10 +16779,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119646335</v>
+        <v>119646290</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>834188</v>
+        <v>834218</v>
       </c>
       <c r="R153" t="n">
-        <v>7347887</v>
+        <v>7347851</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -21337,10 +21337,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119646305</v>
+        <v>119646301</v>
       </c>
       <c r="B196" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>834295</v>
+        <v>834209</v>
       </c>
       <c r="R196" t="n">
-        <v>7348050</v>
+        <v>7347855</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21443,10 +21443,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119646390</v>
+        <v>119646281</v>
       </c>
       <c r="B197" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21459,21 +21459,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21483,10 +21483,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>834574</v>
+        <v>834185</v>
       </c>
       <c r="R197" t="n">
-        <v>7347790</v>
+        <v>7347860</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21549,10 +21549,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119646301</v>
+        <v>119646261</v>
       </c>
       <c r="B198" t="n">
-        <v>91852</v>
+        <v>79115</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21561,25 +21561,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21589,10 +21589,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>834209</v>
+        <v>834404</v>
       </c>
       <c r="R198" t="n">
-        <v>7347855</v>
+        <v>7347982</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21655,10 +21655,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119646281</v>
+        <v>119646305</v>
       </c>
       <c r="B199" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21671,21 +21671,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21695,10 +21695,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>834185</v>
+        <v>834295</v>
       </c>
       <c r="R199" t="n">
-        <v>7347860</v>
+        <v>7348050</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119646261</v>
+        <v>119646390</v>
       </c>
       <c r="B200" t="n">
-        <v>79115</v>
+        <v>91834</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21777,21 +21777,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21801,10 +21801,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>834404</v>
+        <v>834574</v>
       </c>
       <c r="R200" t="n">
-        <v>7347982</v>
+        <v>7347790</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -13284,7 +13284,7 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56522</v>
+        <v>56563</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13315,6 +13315,14 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
@@ -14026,7 +14034,7 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56522</v>
+        <v>56563</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14057,6 +14065,14 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lövberget, Nb</t>
@@ -16994,7 +17010,7 @@
         <v>119646359</v>
       </c>
       <c r="B155" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -22082,7 +22098,7 @@
         <v>119646354</v>
       </c>
       <c r="B203" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -13284,7 +13284,7 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -13284,7 +13284,7 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -13284,7 +13284,7 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -8189,11 +8189,11 @@
         <v>119626510</v>
       </c>
       <c r="B72" t="n">
-        <v>57421</v>
+        <v>57490</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8203,11 +8203,6 @@
       </c>
       <c r="E72" t="n">
         <v>103031</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -8189,7 +8189,7 @@
         <v>119626510</v>
       </c>
       <c r="B72" t="n">
-        <v>57490</v>
+        <v>57494</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8203,6 +8203,11 @@
       </c>
       <c r="E72" t="n">
         <v>103031</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -2097,11 +2097,11 @@
         <v>118218624</v>
       </c>
       <c r="B15" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3396,11 +3396,11 @@
         <v>118218627</v>
       </c>
       <c r="B27" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3511,11 +3511,11 @@
         <v>118218625</v>
       </c>
       <c r="B28" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13284,11 +13284,11 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56569</v>
+        <v>56593</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14034,11 +14034,11 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56569</v>
+        <v>56593</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -2097,11 +2097,11 @@
         <v>118218624</v>
       </c>
       <c r="B15" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3396,11 +3396,11 @@
         <v>118218627</v>
       </c>
       <c r="B27" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3511,11 +3511,11 @@
         <v>118218625</v>
       </c>
       <c r="B28" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13284,11 +13284,11 @@
         <v>119626421</v>
       </c>
       <c r="B120" t="n">
-        <v>56593</v>
+        <v>56569</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14034,11 +14034,11 @@
         <v>119626423</v>
       </c>
       <c r="B127" t="n">
-        <v>56593</v>
+        <v>56569</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -8189,7 +8189,7 @@
         <v>119626510</v>
       </c>
       <c r="B72" t="n">
-        <v>57494</v>
+        <v>57495</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY214"/>
+  <dimension ref="A1:AY215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23365,6 +23365,137 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>129820236</v>
+      </c>
+      <c r="B215" t="n">
+        <v>78089</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Gärsträsket1, Nb</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>834281</v>
+      </c>
+      <c r="R215" t="n">
+        <v>7348070</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Stump # sotad, 2,5m hög # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -23370,7 +23370,7 @@
         <v>129820236</v>
       </c>
       <c r="B215" t="n">
-        <v>78089</v>
+        <v>78092</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -23370,7 +23370,7 @@
         <v>129820236</v>
       </c>
       <c r="B215" t="n">
-        <v>78092</v>
+        <v>78095</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -23370,7 +23370,7 @@
         <v>129820236</v>
       </c>
       <c r="B215" t="n">
-        <v>78095</v>
+        <v>78096</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -23370,7 +23370,7 @@
         <v>129820236</v>
       </c>
       <c r="B215" t="n">
-        <v>78102</v>
+        <v>78187</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -23370,7 +23370,7 @@
         <v>129820236</v>
       </c>
       <c r="B215" t="n">
-        <v>78187</v>
+        <v>78102</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 23533-2024 artfynd.xlsx
+++ b/artfynd/A 23533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY210"/>
+  <dimension ref="A1:AZ210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646282</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646283</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646286</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626406</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626408</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626515</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626516</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626517</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646326</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,6 +2162,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626473</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626475</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626477</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626479</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2496,6 +2586,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626481</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646295</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2698,6 +2798,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646296</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2799,6 +2904,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626428</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626430</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3001,6 +3116,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626431</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626432</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646271</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3304,6 +3434,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646272</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3405,6 +3540,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646273</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3506,6 +3646,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646275</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3607,6 +3752,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646276</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3709,6 +3859,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626404</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3810,6 +3965,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626405</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3911,6 +4071,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646262</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4010,6 +4175,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646263</t>
         </is>
       </c>
     </row>
@@ -4118,6 +4288,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218659</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4224,6 +4399,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218660</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4330,6 +4510,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218661</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4436,6 +4621,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218662</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218663</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4643,6 +4838,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626499</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4744,6 +4944,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626500</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4845,6 +5050,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626501</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626503</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5047,6 +5262,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626504</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626505</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5249,6 +5474,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626506</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5350,6 +5580,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626507</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5451,6 +5686,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626508</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5552,6 +5792,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646303</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5653,6 +5898,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646305</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5754,6 +6004,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646306</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5855,6 +6110,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646308</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5956,6 +6216,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646310</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6057,6 +6322,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646311</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6158,6 +6428,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646313</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6259,6 +6534,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646315</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6360,6 +6640,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646316</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6461,6 +6746,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646319</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6562,6 +6852,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646320</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6661,6 +6956,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646322</t>
         </is>
       </c>
     </row>
@@ -6769,6 +7069,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218696</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6875,6 +7180,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218697</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6976,6 +7286,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626533</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7077,6 +7392,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626534</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7178,6 +7498,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626535</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7279,6 +7604,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626536</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7380,6 +7710,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626537</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7481,6 +7816,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626538</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7582,6 +7922,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626539</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7683,6 +8028,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626540</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7784,6 +8134,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626541</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7885,6 +8240,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626542</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7986,6 +8346,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626543</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8087,6 +8452,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626544</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8188,6 +8558,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626545</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8289,6 +8664,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626547</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8390,6 +8770,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626548</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8491,6 +8876,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626549</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8592,6 +8982,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626550</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8693,6 +9088,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626551</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8794,6 +9194,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626552</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8895,6 +9300,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626553</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8996,6 +9406,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626554</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9097,6 +9512,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626555</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9198,6 +9618,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626556</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9299,6 +9724,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626557</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9400,6 +9830,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646347</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9501,6 +9936,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646348</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9602,6 +10042,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646350</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9703,6 +10148,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646351</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9804,6 +10254,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646353</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9905,6 +10360,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646354</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10006,6 +10466,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646356</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10107,6 +10572,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646357</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10208,6 +10678,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646359</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10309,6 +10784,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646360</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10410,6 +10890,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646362</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10511,6 +10996,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646365</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10612,6 +11102,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646367</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10713,6 +11208,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646369</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10814,6 +11314,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646371</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10915,6 +11420,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646372</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11016,6 +11526,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646374</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11117,6 +11632,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646375</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11218,6 +11738,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646377</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11319,6 +11844,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646378</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11420,6 +11950,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646380</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11521,6 +12056,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646382</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11622,6 +12162,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646384</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11723,6 +12268,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646385</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11824,6 +12374,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646387</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11925,6 +12480,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646388</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12026,6 +12586,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646390</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12127,6 +12692,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646391</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12228,6 +12798,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646394</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12329,6 +12904,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646396</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12430,6 +13010,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646398</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12531,6 +13116,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646399</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12632,6 +13222,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646401</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12733,6 +13328,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646403</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12832,6 +13432,11 @@
       <c r="AY121" t="inlineStr">
         <is>
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646259</t>
         </is>
       </c>
     </row>
@@ -12940,6 +13545,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218691</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13046,6 +13656,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218692</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13152,6 +13767,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218695</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13253,6 +13873,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626519</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13354,6 +13979,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626520</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13455,6 +14085,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626521</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13556,6 +14191,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626522</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13657,6 +14297,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626523</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13758,6 +14403,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626525</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13859,6 +14509,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626526</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13960,6 +14615,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626527</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14061,6 +14721,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626528</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14162,6 +14827,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626529</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14263,6 +14933,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626530</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14364,6 +15039,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626531</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14465,6 +15145,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626532</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14566,6 +15251,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646328</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14667,6 +15357,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646330</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14768,6 +15463,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646331</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14869,6 +15569,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646334</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14970,6 +15675,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646335</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15071,6 +15781,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646337</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15172,6 +15887,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646338</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15273,6 +15993,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646340</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15374,6 +16099,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646341</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15475,6 +16205,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646343</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15576,6 +16311,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646345</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15677,6 +16417,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646293</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15778,6 +16523,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626483</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15879,6 +16629,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626486</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15980,6 +16735,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646298</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16081,6 +16841,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646300</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16182,6 +16947,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646301</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16284,6 +17054,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626471</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16385,6 +17160,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646291</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16486,6 +17266,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646292</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16587,6 +17372,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626433</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16688,6 +17478,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626434</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16789,6 +17584,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626436</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16890,6 +17690,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626437</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16991,6 +17796,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626438</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17092,6 +17902,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626439</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17193,6 +18008,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626440</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17294,6 +18114,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626442</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17395,6 +18220,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626443</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17496,6 +18326,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626444</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17597,6 +18432,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626446</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17698,6 +18538,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626453</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17799,6 +18644,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626455</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17900,6 +18750,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646277</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18001,6 +18856,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646278</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18102,6 +18962,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646279</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18203,6 +19068,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646280</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18304,6 +19174,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646281</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18401,6 +19276,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218620</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18502,6 +19382,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626456</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18603,6 +19488,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626458</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18704,6 +19594,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626509</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18805,6 +19700,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626409</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18906,6 +19806,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626411</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19007,6 +19912,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626412</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19108,6 +20018,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626414</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19209,6 +20124,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626416</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19310,6 +20230,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626418</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19411,6 +20336,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626420</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19512,6 +20442,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646266</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19613,6 +20548,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646267</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19714,6 +20654,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646268</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19815,6 +20760,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646269</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19912,6 +20862,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218690</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20043,6 +20998,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129820236</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20153,6 +21113,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218637</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20254,6 +21219,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626510</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20351,6 +21321,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218682</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20448,6 +21423,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218683</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20545,6 +21525,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218639</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20642,6 +21627,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218640</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20739,6 +21729,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218641</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20836,6 +21831,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218642</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20933,6 +21933,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218643</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21034,6 +22039,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626495</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21135,6 +22145,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626497</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21236,6 +22251,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119626498</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21334,6 +22354,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218638</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21435,6 +22460,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646261</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21532,6 +22562,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118218629</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21628,6 +22663,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646288</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21724,6 +22764,11 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646289</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21820,8 +22865,224 @@
           <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119646290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>